--- a/data/k-props/2026-08-21.xlsx
+++ b/data/k-props/2026-08-21.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
   <si>
     <t>date</t>
   </si>
@@ -142,76 +142,79 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
+    <t>Jesús Luzardo</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Mason Fluharty</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Jacob Misiorowski</t>
-  </si>
-  <si>
-    <t>Jesús Luzardo</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Brad Lord</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Freddy Peralta</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Trevor Rogers</t>
+  </si>
+  <si>
+    <t>Sean Manaea</t>
+  </si>
+  <si>
+    <t>New York Mets @ Chicago White Sox</t>
   </si>
   <si>
     <t>6-7</t>
-  </si>
-  <si>
-    <t>Mason Fluharty</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Brad Lord</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Freddy Peralta</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Trevor Rogers</t>
-  </si>
-  <si>
-    <t>Sean Manaea</t>
-  </si>
-  <si>
-    <t>New York Mets @ Chicago White Sox</t>
   </si>
   <si>
     <t>Sean Burke</t>
@@ -839,22 +842,22 @@
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.222</v>
+        <v>0.2301</v>
       </c>
       <c r="U2">
-        <v>0.2209</v>
+        <v>0.2196</v>
       </c>
       <c r="V2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W2">
         <v>0.2211</v>
       </c>
       <c r="X2">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y2">
-        <v>0.9994</v>
+        <v>0.9358</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -863,7 +866,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>7.9</v>
+        <v>7.65</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -872,13 +875,13 @@
         <v>0.3341</v>
       </c>
       <c r="AG2">
-        <v>1.0063</v>
+        <v>1.0409</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>7.9</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -931,10 +934,10 @@
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2448</v>
+        <v>0.235</v>
       </c>
       <c r="U3">
-        <v>0.2371</v>
+        <v>0.2294</v>
       </c>
       <c r="V3">
         <v>9</v>
@@ -943,10 +946,10 @@
         <v>0.2201</v>
       </c>
       <c r="X3">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y3">
-        <v>1.0244</v>
+        <v>1.0407</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -955,7 +958,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>10.48</v>
+        <v>10.2</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
@@ -964,13 +967,13 @@
         <v>0.4023</v>
       </c>
       <c r="AG3">
-        <v>1.1096</v>
+        <v>1.063</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>10.48</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1023,22 +1026,22 @@
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.1985</v>
+        <v>0.2205</v>
       </c>
       <c r="U4">
-        <v>0.1963</v>
+        <v>0.1899</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>0.1826</v>
       </c>
       <c r="X4">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y4">
-        <v>0.9875</v>
+        <v>0.9461</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1047,22 +1050,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>6.63</v>
+        <v>7.04</v>
       </c>
       <c r="AE4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF4">
         <v>0.3005</v>
       </c>
       <c r="AG4">
-        <v>0.8994</v>
+        <v>0.9973</v>
       </c>
       <c r="AH4">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>7.03</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1070,16 +1073,16 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
         <v>50</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
       </c>
       <c r="G5">
         <v>823510</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I5">
         <v>1.2</v>
@@ -1112,7 +1115,7 @@
         <v>0.078</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T5">
         <v>0.2707</v>
@@ -1127,7 +1130,7 @@
         <v>0.2489</v>
       </c>
       <c r="X5">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y5">
         <v>1.0065</v>
@@ -1148,7 +1151,7 @@
         <v>0.2607</v>
       </c>
       <c r="AG5">
-        <v>1.2269</v>
+        <v>1.2247</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1165,7 +1168,7 @@
         <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>823510</v>
@@ -1204,7 +1207,7 @@
         <v>0.361</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T6">
         <v>0.2061</v>
@@ -1219,7 +1222,7 @@
         <v>0.1899</v>
       </c>
       <c r="X6">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y6">
         <v>0.9895</v>
@@ -1231,7 +1234,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1240,13 +1243,13 @@
         <v>0.3412</v>
       </c>
       <c r="AG6">
-        <v>0.9341</v>
+        <v>0.9325</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1296,7 +1299,7 @@
         <v>0.379</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T7">
         <v>0.2045</v>
@@ -1311,7 +1314,7 @@
         <v>0.2153</v>
       </c>
       <c r="X7">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y7">
         <v>0.985</v>
@@ -1323,7 +1326,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="AE7" t="s">
         <v>53</v>
@@ -1332,13 +1335,13 @@
         <v>0.1996</v>
       </c>
       <c r="AG7">
-        <v>0.9269</v>
+        <v>0.9252</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1391,22 +1394,22 @@
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2194</v>
+        <v>0.2111</v>
       </c>
       <c r="U8">
-        <v>0.2094</v>
+        <v>0.2135</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>0.2042</v>
       </c>
       <c r="X8">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y8">
-        <v>0.9652</v>
+        <v>0.9508</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1415,7 +1418,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.82</v>
+        <v>4.56</v>
       </c>
       <c r="AE8" t="s">
         <v>53</v>
@@ -1424,13 +1427,13 @@
         <v>0.2154</v>
       </c>
       <c r="AG8">
-        <v>0.9943</v>
+        <v>0.9551</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.82</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1447,7 +1450,7 @@
         <v>823830</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9">
         <v>1.9</v>
@@ -1480,7 +1483,7 @@
         <v>0.127</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T9">
         <v>0.2277</v>
@@ -1495,7 +1498,7 @@
         <v>0.2126</v>
       </c>
       <c r="X9">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y9">
         <v>0.9476</v>
@@ -1516,7 +1519,7 @@
         <v>0.2113</v>
       </c>
       <c r="AG9">
-        <v>1.0319</v>
+        <v>1.03</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1572,7 +1575,7 @@
         <v>0.331</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T10">
         <v>0.2145</v>
@@ -1587,7 +1590,7 @@
         <v>0.2085</v>
       </c>
       <c r="X10">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y10">
         <v>0.9883</v>
@@ -1608,7 +1611,7 @@
         <v>0.2119</v>
       </c>
       <c r="AG10">
-        <v>0.9723</v>
+        <v>0.9705</v>
       </c>
       <c r="AH10">
         <v>0</v>
@@ -1664,7 +1667,7 @@
         <v>0.349</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T11">
         <v>0.266</v>
@@ -1679,7 +1682,7 @@
         <v>0.2383</v>
       </c>
       <c r="X11">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y11">
         <v>1.0264</v>
@@ -1691,7 +1694,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.72</v>
+        <v>5.71</v>
       </c>
       <c r="AE11" t="s">
         <v>53</v>
@@ -1700,13 +1703,13 @@
         <v>0.2017</v>
       </c>
       <c r="AG11">
-        <v>1.2054</v>
+        <v>1.2032</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.72</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1756,7 +1759,7 @@
         <v>0.375</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T12">
         <v>0.1703</v>
@@ -1771,7 +1774,7 @@
         <v>0.1849</v>
       </c>
       <c r="X12">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y12">
         <v>0.9069</v>
@@ -1792,7 +1795,7 @@
         <v>0.2245</v>
       </c>
       <c r="AG12">
-        <v>0.7716</v>
+        <v>0.7702</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -1848,7 +1851,7 @@
         <v>0.39</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T13">
         <v>0.2208</v>
@@ -1863,7 +1866,7 @@
         <v>0.2467</v>
       </c>
       <c r="X13">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y13">
         <v>1.0321</v>
@@ -1875,22 +1878,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="AE13" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="AF13">
         <v>0.2408</v>
       </c>
       <c r="AG13">
-        <v>1.0005</v>
+        <v>0.9988</v>
       </c>
       <c r="AH13">
         <v>0.4</v>
       </c>
       <c r="AM13">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1898,7 +1901,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" t="s">
         <v>66</v>
@@ -1940,7 +1943,7 @@
         <v>0.361</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T14">
         <v>0.2328</v>
@@ -1955,7 +1958,7 @@
         <v>0.2245</v>
       </c>
       <c r="X14">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y14">
         <v>0.9824</v>
@@ -1967,22 +1970,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="AE14" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="AF14">
         <v>0.281</v>
       </c>
       <c r="AG14">
-        <v>1.0551</v>
+        <v>1.0533</v>
       </c>
       <c r="AH14">
         <v>0.4</v>
       </c>
       <c r="AM14">
-        <v>6.9</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1990,10 +1993,10 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15">
         <v>824072</v>
@@ -2032,7 +2035,7 @@
         <v>0.369</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T15">
         <v>0.1823</v>
@@ -2047,7 +2050,7 @@
         <v>0.2092</v>
       </c>
       <c r="X15">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y15">
         <v>0.958</v>
@@ -2068,7 +2071,7 @@
         <v>0.2125</v>
       </c>
       <c r="AG15">
-        <v>0.8262</v>
+        <v>0.8248</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -2082,10 +2085,10 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
         <v>70</v>
-      </c>
-      <c r="F16" t="s">
-        <v>69</v>
       </c>
       <c r="G16">
         <v>824072</v>
@@ -2124,7 +2127,7 @@
         <v>0.399</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T16">
         <v>0.188</v>
@@ -2139,7 +2142,7 @@
         <v>0.2305</v>
       </c>
       <c r="X16">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y16">
         <v>0.9878</v>
@@ -2160,7 +2163,7 @@
         <v>0.2116</v>
       </c>
       <c r="AG16">
-        <v>0.852</v>
+        <v>0.8505</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2174,10 +2177,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G17">
         <v>824152</v>
@@ -2216,7 +2219,7 @@
         <v>0.379</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T17">
         <v>0.21</v>
@@ -2231,7 +2234,7 @@
         <v>0.2184</v>
       </c>
       <c r="X17">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y17">
         <v>0.956</v>
@@ -2243,7 +2246,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="AE17" t="s">
         <v>53</v>
@@ -2252,13 +2255,13 @@
         <v>0.2198</v>
       </c>
       <c r="AG17">
-        <v>0.9516</v>
+        <v>0.9499</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2266,10 +2269,10 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" t="s">
         <v>73</v>
-      </c>
-      <c r="F18" t="s">
-        <v>72</v>
       </c>
       <c r="G18">
         <v>824152</v>
@@ -2308,7 +2311,7 @@
         <v>0.322</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T18">
         <v>0.2428</v>
@@ -2323,7 +2326,7 @@
         <v>0.2117</v>
       </c>
       <c r="X18">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y18">
         <v>1.0315</v>
@@ -2335,7 +2338,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="AE18" t="s">
         <v>53</v>
@@ -2344,13 +2347,13 @@
         <v>0.1895</v>
       </c>
       <c r="AG18">
-        <v>1.1002</v>
+        <v>1.0982</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2358,10 +2361,10 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19">
         <v>822857</v>
@@ -2400,7 +2403,7 @@
         <v>0.344</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T19">
         <v>0.2098</v>
@@ -2415,7 +2418,7 @@
         <v>0.2456</v>
       </c>
       <c r="X19">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y19">
         <v>1.0269</v>
@@ -2427,7 +2430,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>7.02</v>
+        <v>7.01</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2436,13 +2439,13 @@
         <v>0.3104</v>
       </c>
       <c r="AG19">
-        <v>0.9509</v>
+        <v>0.9492</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>7.02</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2450,10 +2453,10 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" t="s">
         <v>76</v>
-      </c>
-      <c r="F20" t="s">
-        <v>75</v>
       </c>
       <c r="G20">
         <v>822857</v>
@@ -2492,7 +2495,7 @@
         <v>0.379</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T20">
         <v>0.268</v>
@@ -2507,7 +2510,7 @@
         <v>0.2537</v>
       </c>
       <c r="X20">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y20">
         <v>1.0378</v>
@@ -2519,7 +2522,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>7.51</v>
+        <v>7.5</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2528,13 +2531,13 @@
         <v>0.2596</v>
       </c>
       <c r="AG20">
-        <v>1.2148</v>
+        <v>1.2126</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>7.51</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2542,10 +2545,10 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21">
         <v>824317</v>
@@ -2584,7 +2587,7 @@
         <v>0.303</v>
       </c>
       <c r="S21" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T21">
         <v>0.2332</v>
@@ -2599,7 +2602,7 @@
         <v>0.2484</v>
       </c>
       <c r="X21">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y21">
         <v>1.0211</v>
@@ -2611,22 +2614,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="AE21" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="AF21">
         <v>0.2728</v>
       </c>
       <c r="AG21">
-        <v>1.0567</v>
+        <v>1.0548</v>
       </c>
       <c r="AH21">
         <v>0.4</v>
       </c>
       <c r="AM21">
-        <v>6.54</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2634,10 +2637,10 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" t="s">
         <v>79</v>
-      </c>
-      <c r="F22" t="s">
-        <v>78</v>
       </c>
       <c r="G22">
         <v>824317</v>
@@ -2676,7 +2679,7 @@
         <v>0.351</v>
       </c>
       <c r="S22" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T22">
         <v>0.2103</v>
@@ -2691,7 +2694,7 @@
         <v>0.2149</v>
       </c>
       <c r="X22">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y22">
         <v>0.9358</v>
@@ -2703,7 +2706,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="AE22" t="s">
         <v>53</v>
@@ -2712,13 +2715,13 @@
         <v>0.1842</v>
       </c>
       <c r="AG22">
-        <v>0.953</v>
+        <v>0.9513</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2726,10 +2729,10 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G23">
         <v>825045</v>
@@ -2768,7 +2771,7 @@
         <v>0.344</v>
       </c>
       <c r="S23" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T23">
         <v>0.1697</v>
@@ -2783,7 +2786,7 @@
         <v>0.1766</v>
       </c>
       <c r="X23">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y23">
         <v>0.9029</v>
@@ -2795,7 +2798,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AE23" t="s">
         <v>53</v>
@@ -2804,13 +2807,13 @@
         <v>0.1806</v>
       </c>
       <c r="AG23">
-        <v>0.7689</v>
+        <v>0.7675</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2818,10 +2821,10 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" t="s">
         <v>82</v>
-      </c>
-      <c r="F24" t="s">
-        <v>81</v>
       </c>
       <c r="G24">
         <v>825045</v>
@@ -2860,7 +2863,7 @@
         <v>0.403</v>
       </c>
       <c r="S24" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T24">
         <v>0.2792</v>
@@ -2875,7 +2878,7 @@
         <v>0.2527</v>
       </c>
       <c r="X24">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y24">
         <v>1.0529</v>
@@ -2887,7 +2890,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.71</v>
+        <v>5.7</v>
       </c>
       <c r="AE24" t="s">
         <v>53</v>
@@ -2896,13 +2899,13 @@
         <v>0.1749</v>
       </c>
       <c r="AG24">
-        <v>1.2655</v>
+        <v>1.2632</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>5.71</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2910,10 +2913,10 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25">
         <v>823262</v>
@@ -2952,7 +2955,7 @@
         <v>0.353</v>
       </c>
       <c r="S25" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T25">
         <v>0.1886</v>
@@ -2967,7 +2970,7 @@
         <v>0.2218</v>
       </c>
       <c r="X25">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y25">
         <v>0.9876</v>
@@ -2979,7 +2982,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="AE25" t="s">
         <v>53</v>
@@ -2988,13 +2991,13 @@
         <v>0.2531</v>
       </c>
       <c r="AG25">
-        <v>0.8547</v>
+        <v>0.8532</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3002,10 +3005,10 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G26">
         <v>823911</v>
@@ -3044,7 +3047,7 @@
         <v>0.349</v>
       </c>
       <c r="S26" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T26">
         <v>0.3045</v>
@@ -3059,7 +3062,7 @@
         <v>0.2057</v>
       </c>
       <c r="X26">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y26">
         <v>1.0045</v>
@@ -3071,22 +3074,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>6.33</v>
+        <v>6.32</v>
       </c>
       <c r="AE26" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="AF26">
         <v>0.2082</v>
       </c>
       <c r="AG26">
-        <v>1.3799</v>
+        <v>1.3774</v>
       </c>
       <c r="AH26">
         <v>0.4</v>
       </c>
       <c r="AM26">
-        <v>6.73</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3094,10 +3097,10 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" t="s">
         <v>87</v>
-      </c>
-      <c r="F27" t="s">
-        <v>86</v>
       </c>
       <c r="G27">
         <v>823911</v>
@@ -3136,7 +3139,7 @@
         <v>0.396</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T27">
         <v>0.2148</v>
@@ -3151,7 +3154,7 @@
         <v>0.2346</v>
       </c>
       <c r="X27">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y27">
         <v>1.0324</v>
@@ -3163,22 +3166,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>6.05</v>
+        <v>6.04</v>
       </c>
       <c r="AE27" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="AF27">
         <v>0.2384</v>
       </c>
       <c r="AG27">
-        <v>0.9733</v>
+        <v>0.9716</v>
       </c>
       <c r="AH27">
         <v>0.4</v>
       </c>
       <c r="AM27">
-        <v>6.45</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3186,10 +3189,10 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28">
         <v>823101</v>
@@ -3228,7 +3231,7 @@
         <v>0.407</v>
       </c>
       <c r="S28" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T28">
         <v>0.2335</v>
@@ -3243,7 +3246,7 @@
         <v>0.2425</v>
       </c>
       <c r="X28">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y28">
         <v>0.9904</v>
@@ -3255,7 +3258,7 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="AE28" t="s">
         <v>53</v>
@@ -3264,13 +3267,13 @@
         <v>0.1644</v>
       </c>
       <c r="AG28">
-        <v>1.058</v>
+        <v>1.0561</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3278,10 +3281,10 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" t="s">
         <v>90</v>
-      </c>
-      <c r="F29" t="s">
-        <v>89</v>
       </c>
       <c r="G29">
         <v>823101</v>
@@ -3320,7 +3323,7 @@
         <v>0.387</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="T29">
         <v>0.2255</v>
@@ -3335,7 +3338,7 @@
         <v>0.2183</v>
       </c>
       <c r="X29">
-        <v>0.2207</v>
+        <v>0.2211</v>
       </c>
       <c r="Y29">
         <v>0.9568</v>
@@ -3347,7 +3350,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="AE29" t="s">
         <v>53</v>
@@ -3356,13 +3359,13 @@
         <v>0.2182</v>
       </c>
       <c r="AG29">
-        <v>1.022</v>
+        <v>1.0202</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-21.xlsx
+++ b/data/k-props/2026-08-21.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="96">
   <si>
     <t>date</t>
   </si>
@@ -133,160 +133,172 @@
     <t>08/21/2026</t>
   </si>
   <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
     <t>Chris Sale</t>
   </si>
   <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Jacob Misiorowski</t>
+    <t>Hunter Dobbins</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Jesus Luzardo</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ New York Yankees</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>Brad Lord</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Freddy Peralta</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Trevor Rogers</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>New York Mets @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Sean Manaea</t>
+  </si>
+  <si>
+    <t>Hayden Wesneski</t>
+  </si>
+  <si>
+    <t>Athletics @ Houston Astros</t>
+  </si>
+  <si>
+    <t>JT Ginn</t>
+  </si>
+  <si>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Troy Melton</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>Tanner Gordon</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Randy Vasquez</t>
+  </si>
+  <si>
+    <t>Matthew Boyd</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Emerson Hancock</t>
+  </si>
+  <si>
+    <t>Yoshinobu Yamamoto</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
   </si>
   <si>
     <t>Jesús Luzardo</t>
   </si>
   <si>
-    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
-  </si>
-  <si>
     <t>Mason Fluharty</t>
   </si>
   <si>
-    <t>Toronto Blue Jays @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Brad Lord</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Freddy Peralta</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Trevor Rogers</t>
-  </si>
-  <si>
-    <t>Sean Manaea</t>
-  </si>
-  <si>
-    <t>New York Mets @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>Troy Melton</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Noah Cameron</t>
-  </si>
-  <si>
     <t>J.T. Ginn</t>
-  </si>
-  <si>
-    <t>Athletics @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Hayden Wesneski</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Joey Cantillo</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Tanner Gordon</t>
-  </si>
-  <si>
-    <t>Nick Lodolo</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Eduardo Rodriguez</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Yoshinobu Yamamoto</t>
-  </si>
-  <si>
-    <t>Matthew Boyd</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Emerson Hancock</t>
   </si>
 </sst>
 </file>
@@ -667,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM29"/>
+  <dimension ref="A1:AM33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -799,6 +811,15 @@
       <c r="B2" t="s">
         <v>40</v>
       </c>
+      <c r="C2">
+        <v>9.5</v>
+      </c>
+      <c r="D2">
+        <v>120</v>
+      </c>
+      <c r="E2">
+        <v>-142</v>
+      </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
@@ -809,7 +830,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -818,46 +839,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>0.3095</v>
+        <v>0.3985</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="P2">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="Q2">
-        <v>0.3772</v>
+        <v>0.4095</v>
       </c>
       <c r="R2">
-        <v>0.363</v>
+        <v>0.344</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2301</v>
+        <v>0.235</v>
       </c>
       <c r="U2">
-        <v>0.2196</v>
+        <v>0.2294</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2211</v>
+        <v>0.2201</v>
       </c>
       <c r="X2">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y2">
-        <v>0.9358</v>
+        <v>1.0407</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -866,22 +887,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>7.65</v>
+        <v>10.07</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.3341</v>
+        <v>0.4023</v>
       </c>
       <c r="AG2">
-        <v>1.0409</v>
+        <v>1.0501</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>7.65</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -891,6 +912,15 @@
       <c r="B3" t="s">
         <v>46</v>
       </c>
+      <c r="C3">
+        <v>7.5</v>
+      </c>
+      <c r="D3">
+        <v>-114</v>
+      </c>
+      <c r="E3">
+        <v>-109</v>
+      </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
@@ -901,55 +931,55 @@
         <v>42</v>
       </c>
       <c r="I3">
+        <v>5.9</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>6</v>
       </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
       <c r="M3">
-        <v>0.3985</v>
+        <v>0.3095</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="P3">
-        <v>3.79</v>
+        <v>4.01</v>
       </c>
       <c r="Q3">
-        <v>0.4095</v>
+        <v>0.3772</v>
       </c>
       <c r="R3">
-        <v>0.344</v>
+        <v>0.363</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.235</v>
+        <v>0.2301</v>
       </c>
       <c r="U3">
-        <v>0.2294</v>
+        <v>0.2196</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2201</v>
+        <v>0.2211</v>
       </c>
       <c r="X3">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y3">
-        <v>1.0407</v>
+        <v>0.9358</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -958,22 +988,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>10.2</v>
+        <v>7.55</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.4023</v>
+        <v>0.3341</v>
       </c>
       <c r="AG3">
-        <v>1.063</v>
+        <v>1.0283</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>10.2</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -983,6 +1013,15 @@
       <c r="B4" t="s">
         <v>47</v>
       </c>
+      <c r="C4">
+        <v>3.5</v>
+      </c>
+      <c r="D4">
+        <v>-127</v>
+      </c>
+      <c r="E4">
+        <v>110</v>
+      </c>
       <c r="F4" t="s">
         <v>48</v>
       </c>
@@ -993,55 +1032,55 @@
         <v>42</v>
       </c>
       <c r="I4">
+        <v>5.1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>6</v>
       </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
       <c r="M4">
-        <v>0.2979</v>
+        <v>0.2311</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="P4">
-        <v>4.13</v>
+        <v>4.24</v>
       </c>
       <c r="Q4">
-        <v>0.3043</v>
+        <v>0.2261</v>
       </c>
       <c r="R4">
-        <v>0.408</v>
+        <v>0.365</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2205</v>
+        <v>0.163</v>
       </c>
       <c r="U4">
-        <v>0.1899</v>
+        <v>0.1638</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.1826</v>
+        <v>0.2216</v>
       </c>
       <c r="X4">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y4">
-        <v>0.9461</v>
+        <v>0.922</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1050,22 +1089,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>7.04</v>
+        <v>3.36</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF4">
-        <v>0.3005</v>
+        <v>0.2293</v>
       </c>
       <c r="AG4">
-        <v>0.9973</v>
+        <v>0.7285</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>7.04</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1073,67 +1112,34 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="C5">
+        <v>7.5</v>
+      </c>
+      <c r="D5">
+        <v>115</v>
+      </c>
+      <c r="E5">
+        <v>-125</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5">
-        <v>823510</v>
+        <v>48</v>
+      </c>
+      <c r="G5" t="s">
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5">
-        <v>1.2</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0.2629</v>
-      </c>
-      <c r="N5">
-        <v>3</v>
-      </c>
-      <c r="O5">
-        <v>17</v>
-      </c>
-      <c r="P5">
-        <v>4.18</v>
-      </c>
-      <c r="Q5">
-        <v>0.2353</v>
-      </c>
-      <c r="R5">
-        <v>0.078</v>
+        <v>6</v>
       </c>
       <c r="S5" t="s">
-        <v>52</v>
-      </c>
-      <c r="T5">
-        <v>0.2707</v>
-      </c>
-      <c r="U5">
-        <v>0.269</v>
-      </c>
-      <c r="V5">
-        <v>9</v>
-      </c>
-      <c r="W5">
-        <v>0.2489</v>
-      </c>
-      <c r="X5">
-        <v>0.2211</v>
-      </c>
-      <c r="Y5">
-        <v>1.0065</v>
+        <v>44</v>
+      </c>
+      <c r="V5" t="s">
+        <v>44</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1141,23 +1147,8 @@
       <c r="AC5" t="s">
         <v>44</v>
       </c>
-      <c r="AD5">
-        <v>1.64</v>
-      </c>
       <c r="AE5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF5">
-        <v>0.2607</v>
-      </c>
-      <c r="AG5">
-        <v>1.2247</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>1.64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1165,10 +1156,19 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="C6">
+        <v>6.5</v>
+      </c>
+      <c r="D6">
+        <v>-111</v>
+      </c>
+      <c r="E6">
+        <v>-108</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>823510</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>0.314</v>
@@ -1207,7 +1207,7 @@
         <v>0.361</v>
       </c>
       <c r="S6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T6">
         <v>0.2061</v>
@@ -1222,7 +1222,7 @@
         <v>0.1899</v>
       </c>
       <c r="X6">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y6">
         <v>0.9895</v>
@@ -1234,7 +1234,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>7.29</v>
+        <v>7.2</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1243,13 +1243,13 @@
         <v>0.3412</v>
       </c>
       <c r="AG6">
-        <v>0.9325</v>
+        <v>0.9211</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>7.29</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1257,10 +1257,19 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>5.5</v>
+      </c>
+      <c r="D7">
+        <v>-104</v>
+      </c>
+      <c r="E7">
+        <v>-116</v>
+      </c>
+      <c r="F7" t="s">
         <v>55</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
       </c>
       <c r="G7">
         <v>824721</v>
@@ -1269,7 +1278,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1278,46 +1287,46 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>0.1964</v>
+        <v>0.2183</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="P7">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="Q7">
-        <v>0.2049</v>
+        <v>0.2109</v>
       </c>
       <c r="R7">
-        <v>0.379</v>
+        <v>0.39</v>
       </c>
       <c r="S7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2045</v>
+        <v>0.2111</v>
       </c>
       <c r="U7">
-        <v>0.1924</v>
+        <v>0.2135</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2153</v>
+        <v>0.2042</v>
       </c>
       <c r="X7">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y7">
-        <v>0.985</v>
+        <v>0.9508</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1326,22 +1335,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="AE7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF7">
-        <v>0.1996</v>
+        <v>0.2154</v>
       </c>
       <c r="AG7">
-        <v>0.9252</v>
+        <v>0.9436</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1349,10 +1358,19 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="C8">
+        <v>4.5</v>
+      </c>
+      <c r="D8">
+        <v>-105</v>
+      </c>
+      <c r="E8">
+        <v>-108</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>824721</v>
@@ -1361,7 +1379,7 @@
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1370,46 +1388,46 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>0.2183</v>
+        <v>0.1964</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="P8">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="Q8">
-        <v>0.2109</v>
+        <v>0.2049</v>
       </c>
       <c r="R8">
-        <v>0.39</v>
+        <v>0.379</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2111</v>
+        <v>0.1933</v>
       </c>
       <c r="U8">
-        <v>0.2135</v>
+        <v>0.1976</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2042</v>
+        <v>0.2153</v>
       </c>
       <c r="X8">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y8">
-        <v>0.9508</v>
+        <v>0.9943</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1418,22 +1436,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.56</v>
+        <v>4.37</v>
       </c>
       <c r="AE8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF8">
-        <v>0.2154</v>
+        <v>0.1996</v>
       </c>
       <c r="AG8">
-        <v>0.9551</v>
+        <v>0.8639</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.56</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1441,16 +1459,25 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9">
+        <v>2.5</v>
+      </c>
+      <c r="D9">
+        <v>-106</v>
+      </c>
+      <c r="E9">
+        <v>-110</v>
+      </c>
+      <c r="F9" t="s">
         <v>58</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
       </c>
       <c r="G9">
         <v>823830</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I9">
         <v>1.9</v>
@@ -1462,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>0.2119</v>
@@ -1483,13 +1510,13 @@
         <v>0.127</v>
       </c>
       <c r="S9" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2277</v>
+        <v>0.2444</v>
       </c>
       <c r="U9">
-        <v>0.2149</v>
+        <v>0.2296</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1498,10 +1525,10 @@
         <v>0.2126</v>
       </c>
       <c r="X9">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y9">
-        <v>0.9476</v>
+        <v>0.8899</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1510,22 +1537,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF9">
         <v>0.2113</v>
       </c>
       <c r="AG9">
-        <v>1.03</v>
+        <v>1.0923</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1535,8 +1562,17 @@
       <c r="B10" t="s">
         <v>60</v>
       </c>
+      <c r="C10">
+        <v>4.5</v>
+      </c>
+      <c r="D10">
+        <v>122</v>
+      </c>
+      <c r="E10">
+        <v>-152</v>
+      </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>823830</v>
@@ -1554,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>0.2068</v>
@@ -1575,7 +1611,7 @@
         <v>0.331</v>
       </c>
       <c r="S10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T10">
         <v>0.2145</v>
@@ -1590,7 +1626,7 @@
         <v>0.2085</v>
       </c>
       <c r="X10">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y10">
         <v>0.9883</v>
@@ -1602,22 +1638,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="AE10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF10">
         <v>0.2119</v>
       </c>
       <c r="AG10">
-        <v>0.9705</v>
+        <v>0.9588</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1627,6 +1663,15 @@
       <c r="B11" t="s">
         <v>62</v>
       </c>
+      <c r="C11">
+        <v>5.5</v>
+      </c>
+      <c r="D11">
+        <v>112</v>
+      </c>
+      <c r="E11">
+        <v>-133</v>
+      </c>
       <c r="F11" t="s">
         <v>63</v>
       </c>
@@ -1646,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>0.2147</v>
@@ -1667,7 +1712,7 @@
         <v>0.349</v>
       </c>
       <c r="S11" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T11">
         <v>0.266</v>
@@ -1682,10 +1727,10 @@
         <v>0.2383</v>
       </c>
       <c r="X11">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y11">
-        <v>1.0264</v>
+        <v>1.0527</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1694,22 +1739,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.71</v>
+        <v>5.79</v>
       </c>
       <c r="AE11" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF11">
         <v>0.2017</v>
       </c>
       <c r="AG11">
-        <v>1.2032</v>
+        <v>1.1886</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.71</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1719,6 +1764,15 @@
       <c r="B12" t="s">
         <v>64</v>
       </c>
+      <c r="C12">
+        <v>4.5</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>-115</v>
+      </c>
       <c r="F12" t="s">
         <v>63</v>
       </c>
@@ -1738,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>0.2042</v>
@@ -1759,7 +1813,7 @@
         <v>0.375</v>
       </c>
       <c r="S12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T12">
         <v>0.1703</v>
@@ -1774,7 +1828,7 @@
         <v>0.1849</v>
       </c>
       <c r="X12">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y12">
         <v>0.9069</v>
@@ -1786,22 +1840,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="AE12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF12">
         <v>0.2245</v>
       </c>
       <c r="AG12">
-        <v>0.7702</v>
+        <v>0.7608</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1811,6 +1865,15 @@
       <c r="B13" t="s">
         <v>65</v>
       </c>
+      <c r="C13">
+        <v>6.5</v>
+      </c>
+      <c r="D13">
+        <v>112</v>
+      </c>
+      <c r="E13">
+        <v>-135</v>
+      </c>
       <c r="F13" t="s">
         <v>66</v>
       </c>
@@ -1821,7 +1884,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1830,46 +1893,46 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>0.2349</v>
+        <v>0.2697</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="P13">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="Q13">
-        <v>0.25</v>
+        <v>0.3009</v>
       </c>
       <c r="R13">
-        <v>0.39</v>
+        <v>0.361</v>
       </c>
       <c r="S13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T13">
-        <v>0.2208</v>
+        <v>0.2328</v>
       </c>
       <c r="U13">
-        <v>0.2379</v>
+        <v>0.2359</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2467</v>
+        <v>0.2245</v>
       </c>
       <c r="X13">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y13">
-        <v>1.0321</v>
+        <v>0.9824</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1878,22 +1941,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>6.1</v>
+        <v>6.41</v>
       </c>
       <c r="AE13" t="s">
         <v>67</v>
       </c>
       <c r="AF13">
-        <v>0.2408</v>
+        <v>0.281</v>
       </c>
       <c r="AG13">
-        <v>0.9988</v>
+        <v>1.0405</v>
       </c>
       <c r="AH13">
         <v>0.4</v>
       </c>
       <c r="AM13">
-        <v>6.5</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1903,6 +1966,15 @@
       <c r="B14" t="s">
         <v>68</v>
       </c>
+      <c r="C14">
+        <v>5.5</v>
+      </c>
+      <c r="D14">
+        <v>-132</v>
+      </c>
+      <c r="E14">
+        <v>115</v>
+      </c>
       <c r="F14" t="s">
         <v>66</v>
       </c>
@@ -1913,7 +1985,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1922,46 +1994,46 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>0.2697</v>
+        <v>0.2349</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="P14">
-        <v>4.08</v>
+        <v>4.33</v>
       </c>
       <c r="Q14">
-        <v>0.3009</v>
+        <v>0.25</v>
       </c>
       <c r="R14">
-        <v>0.361</v>
+        <v>0.39</v>
       </c>
       <c r="S14" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2328</v>
+        <v>0.2529</v>
       </c>
       <c r="U14">
-        <v>0.2359</v>
+        <v>0.2556</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2245</v>
+        <v>0.2467</v>
       </c>
       <c r="X14">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y14">
-        <v>0.9824</v>
+        <v>1.1</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1970,22 +2042,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>6.49</v>
+        <v>7.35</v>
       </c>
       <c r="AE14" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.281</v>
+        <v>0.2408</v>
       </c>
       <c r="AG14">
-        <v>1.0533</v>
+        <v>1.13</v>
       </c>
       <c r="AH14">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>6.89</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1995,17 +2067,26 @@
       <c r="B15" t="s">
         <v>69</v>
       </c>
+      <c r="C15">
+        <v>4.5</v>
+      </c>
+      <c r="D15">
+        <v>-114</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
       <c r="F15" t="s">
         <v>70</v>
       </c>
       <c r="G15">
-        <v>824072</v>
+        <v>824152</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2014,46 +2095,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>0.2219</v>
+        <v>0.1895</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O15">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="P15">
-        <v>3.9</v>
+        <v>4.19</v>
       </c>
       <c r="Q15">
-        <v>0.1966</v>
+        <v>0.1895</v>
       </c>
       <c r="R15">
-        <v>0.369</v>
+        <v>0.322</v>
       </c>
       <c r="S15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T15">
-        <v>0.1823</v>
+        <v>0.2428</v>
       </c>
       <c r="U15">
-        <v>0.1931</v>
+        <v>0.2166</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2092</v>
+        <v>0.2117</v>
       </c>
       <c r="X15">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y15">
-        <v>0.958</v>
+        <v>1.0315</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2062,22 +2143,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.95</v>
+        <v>5.04</v>
       </c>
       <c r="AE15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF15">
-        <v>0.2125</v>
+        <v>0.1895</v>
       </c>
       <c r="AG15">
-        <v>0.8248</v>
+        <v>1.0849</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>3.95</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2087,65 +2168,32 @@
       <c r="B16" t="s">
         <v>71</v>
       </c>
+      <c r="C16">
+        <v>4.5</v>
+      </c>
+      <c r="D16">
+        <v>-119</v>
+      </c>
+      <c r="E16">
+        <v>-102</v>
+      </c>
       <c r="F16" t="s">
         <v>70</v>
       </c>
-      <c r="G16">
-        <v>824072</v>
+      <c r="G16" t="s">
+        <v>44</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16">
-        <v>5.7</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0.2172</v>
-      </c>
-      <c r="N16">
         <v>5</v>
       </c>
-      <c r="O16">
-        <v>133</v>
-      </c>
-      <c r="P16">
-        <v>4.19</v>
-      </c>
-      <c r="Q16">
-        <v>0.203</v>
-      </c>
-      <c r="R16">
-        <v>0.399</v>
-      </c>
       <c r="S16" t="s">
-        <v>52</v>
-      </c>
-      <c r="T16">
-        <v>0.188</v>
-      </c>
-      <c r="U16">
-        <v>0.1962</v>
-      </c>
-      <c r="V16">
-        <v>9</v>
-      </c>
-      <c r="W16">
-        <v>0.2305</v>
-      </c>
-      <c r="X16">
-        <v>0.2211</v>
-      </c>
-      <c r="Y16">
-        <v>0.9878</v>
+        <v>44</v>
+      </c>
+      <c r="V16" t="s">
+        <v>44</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2153,23 +2201,8 @@
       <c r="AC16" t="s">
         <v>44</v>
       </c>
-      <c r="AD16">
-        <v>4.26</v>
-      </c>
       <c r="AE16" t="s">
-        <v>53</v>
-      </c>
-      <c r="AF16">
-        <v>0.2116</v>
-      </c>
-      <c r="AG16">
-        <v>0.8505</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>4.26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2179,17 +2212,26 @@
       <c r="B17" t="s">
         <v>72</v>
       </c>
+      <c r="C17">
+        <v>5.5</v>
+      </c>
+      <c r="D17">
+        <v>110</v>
+      </c>
+      <c r="E17">
+        <v>-136</v>
+      </c>
       <c r="F17" t="s">
         <v>73</v>
       </c>
       <c r="G17">
-        <v>824152</v>
+        <v>824072</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2198,46 +2240,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2139</v>
+        <v>0.2172</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="P17">
         <v>4.19</v>
       </c>
       <c r="Q17">
-        <v>0.2295</v>
+        <v>0.203</v>
       </c>
       <c r="R17">
-        <v>0.379</v>
+        <v>0.399</v>
       </c>
       <c r="S17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T17">
-        <v>0.21</v>
+        <v>0.188</v>
       </c>
       <c r="U17">
-        <v>0.2016</v>
+        <v>0.1962</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2184</v>
+        <v>0.2305</v>
       </c>
       <c r="X17">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y17">
-        <v>0.956</v>
+        <v>0.9878</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2246,22 +2288,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.57</v>
+        <v>4.2</v>
       </c>
       <c r="AE17" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF17">
-        <v>0.2198</v>
+        <v>0.2116</v>
       </c>
       <c r="AG17">
-        <v>0.9499</v>
+        <v>0.8402</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.57</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2271,17 +2313,26 @@
       <c r="B18" t="s">
         <v>74</v>
       </c>
+      <c r="C18">
+        <v>4.5</v>
+      </c>
+      <c r="D18">
+        <v>-102</v>
+      </c>
+      <c r="E18">
+        <v>-118</v>
+      </c>
       <c r="F18" t="s">
         <v>73</v>
       </c>
       <c r="G18">
-        <v>824152</v>
+        <v>824072</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2290,46 +2341,46 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>0.1895</v>
+        <v>0.2219</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="P18">
-        <v>4.19</v>
+        <v>3.9</v>
       </c>
       <c r="Q18">
-        <v>0.1895</v>
+        <v>0.1966</v>
       </c>
       <c r="R18">
-        <v>0.322</v>
+        <v>0.369</v>
       </c>
       <c r="S18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T18">
-        <v>0.2428</v>
+        <v>0.1823</v>
       </c>
       <c r="U18">
-        <v>0.2166</v>
+        <v>0.1931</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2117</v>
+        <v>0.2092</v>
       </c>
       <c r="X18">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y18">
-        <v>1.0315</v>
+        <v>0.958</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2338,22 +2389,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="AE18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF18">
-        <v>0.1895</v>
+        <v>0.2125</v>
       </c>
       <c r="AG18">
-        <v>1.0982</v>
+        <v>0.8148</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2363,6 +2414,15 @@
       <c r="B19" t="s">
         <v>75</v>
       </c>
+      <c r="C19">
+        <v>6.5</v>
+      </c>
+      <c r="D19">
+        <v>-120</v>
+      </c>
+      <c r="E19">
+        <v>-103</v>
+      </c>
       <c r="F19" t="s">
         <v>76</v>
       </c>
@@ -2373,7 +2433,7 @@
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2382,46 +2442,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2884</v>
+        <v>0.258</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="P19">
-        <v>4.05</v>
+        <v>4.27</v>
       </c>
       <c r="Q19">
-        <v>0.3524</v>
+        <v>0.2623</v>
       </c>
       <c r="R19">
-        <v>0.344</v>
+        <v>0.379</v>
       </c>
       <c r="S19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T19">
-        <v>0.2098</v>
+        <v>0.268</v>
       </c>
       <c r="U19">
-        <v>0.237</v>
+        <v>0.2523</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2456</v>
+        <v>0.2537</v>
       </c>
       <c r="X19">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y19">
-        <v>1.0269</v>
+        <v>1.0378</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2430,22 +2490,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>7.01</v>
+        <v>7.41</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.3104</v>
+        <v>0.2596</v>
       </c>
       <c r="AG19">
-        <v>0.9492</v>
+        <v>1.1979</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>7.01</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2455,6 +2515,15 @@
       <c r="B20" t="s">
         <v>77</v>
       </c>
+      <c r="C20">
+        <v>6.5</v>
+      </c>
+      <c r="D20">
+        <v>102</v>
+      </c>
+      <c r="E20">
+        <v>-120</v>
+      </c>
       <c r="F20" t="s">
         <v>76</v>
       </c>
@@ -2465,7 +2534,7 @@
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2474,46 +2543,46 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>0.258</v>
+        <v>0.2884</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="P20">
-        <v>4.27</v>
+        <v>4.05</v>
       </c>
       <c r="Q20">
-        <v>0.2623</v>
+        <v>0.3524</v>
       </c>
       <c r="R20">
-        <v>0.379</v>
+        <v>0.344</v>
       </c>
       <c r="S20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T20">
-        <v>0.268</v>
+        <v>0.2098</v>
       </c>
       <c r="U20">
-        <v>0.2523</v>
+        <v>0.237</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2537</v>
+        <v>0.2456</v>
       </c>
       <c r="X20">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y20">
-        <v>1.0378</v>
+        <v>1.0269</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2522,22 +2591,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>7.5</v>
+        <v>6.92</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="AF20">
-        <v>0.2596</v>
+        <v>0.3104</v>
       </c>
       <c r="AG20">
-        <v>1.2126</v>
+        <v>0.9377</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM20">
-        <v>7.5</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2547,6 +2616,15 @@
       <c r="B21" t="s">
         <v>78</v>
       </c>
+      <c r="C21">
+        <v>2.5</v>
+      </c>
+      <c r="D21">
+        <v>-165</v>
+      </c>
+      <c r="E21">
+        <v>138</v>
+      </c>
       <c r="F21" t="s">
         <v>79</v>
       </c>
@@ -2557,7 +2635,7 @@
         <v>42</v>
       </c>
       <c r="I21">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2566,46 +2644,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>0.2565</v>
+        <v>0.1987</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="P21">
-        <v>4.31</v>
+        <v>4.37</v>
       </c>
       <c r="Q21">
-        <v>0.3103</v>
+        <v>0.1574</v>
       </c>
       <c r="R21">
-        <v>0.303</v>
+        <v>0.351</v>
       </c>
       <c r="S21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T21">
-        <v>0.2332</v>
+        <v>0.2103</v>
       </c>
       <c r="U21">
-        <v>0.2269</v>
+        <v>0.1891</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2484</v>
+        <v>0.2149</v>
       </c>
       <c r="X21">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y21">
-        <v>1.0211</v>
+        <v>0.9358</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2614,22 +2692,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>6.12</v>
+        <v>3.26</v>
       </c>
       <c r="AE21" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="AF21">
-        <v>0.2728</v>
+        <v>0.1842</v>
       </c>
       <c r="AG21">
-        <v>1.0548</v>
+        <v>0.9397</v>
       </c>
       <c r="AH21">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>6.52</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2639,6 +2717,15 @@
       <c r="B22" t="s">
         <v>80</v>
       </c>
+      <c r="C22">
+        <v>5.5</v>
+      </c>
+      <c r="D22">
+        <v>-115</v>
+      </c>
+      <c r="E22">
+        <v>-103</v>
+      </c>
       <c r="F22" t="s">
         <v>79</v>
       </c>
@@ -2649,7 +2736,7 @@
         <v>42</v>
       </c>
       <c r="I22">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2658,46 +2745,46 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>0.1987</v>
+        <v>0.2565</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="P22">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
       <c r="Q22">
-        <v>0.1574</v>
+        <v>0.3103</v>
       </c>
       <c r="R22">
-        <v>0.351</v>
+        <v>0.303</v>
       </c>
       <c r="S22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T22">
-        <v>0.2103</v>
+        <v>0.2332</v>
       </c>
       <c r="U22">
-        <v>0.1891</v>
+        <v>0.2269</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2149</v>
+        <v>0.2484</v>
       </c>
       <c r="X22">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y22">
-        <v>0.9358</v>
+        <v>1.0211</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2706,22 +2793,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>3.3</v>
+        <v>6.05</v>
       </c>
       <c r="AE22" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="AF22">
-        <v>0.1842</v>
+        <v>0.2728</v>
       </c>
       <c r="AG22">
-        <v>0.9513</v>
+        <v>1.042</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM22">
-        <v>3.3</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2731,6 +2818,15 @@
       <c r="B23" t="s">
         <v>81</v>
       </c>
+      <c r="C23">
+        <v>5.5</v>
+      </c>
+      <c r="D23">
+        <v>116</v>
+      </c>
+      <c r="E23">
+        <v>-139</v>
+      </c>
       <c r="F23" t="s">
         <v>82</v>
       </c>
@@ -2741,7 +2837,7 @@
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2750,46 +2846,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>0.1804</v>
+        <v>0.1729</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="P23">
-        <v>4.41</v>
+        <v>4.1</v>
       </c>
       <c r="Q23">
-        <v>0.181</v>
+        <v>0.1778</v>
       </c>
       <c r="R23">
-        <v>0.344</v>
+        <v>0.403</v>
       </c>
       <c r="S23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T23">
-        <v>0.1697</v>
+        <v>0.2792</v>
       </c>
       <c r="U23">
-        <v>0.1713</v>
+        <v>0.2791</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.1766</v>
+        <v>0.2527</v>
       </c>
       <c r="X23">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y23">
-        <v>0.9029</v>
+        <v>1.0529</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2798,22 +2894,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>2.82</v>
+        <v>5.63</v>
       </c>
       <c r="AE23" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF23">
-        <v>0.1806</v>
+        <v>0.1749</v>
       </c>
       <c r="AG23">
-        <v>0.7675</v>
+        <v>1.2479</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>2.82</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2823,6 +2919,15 @@
       <c r="B24" t="s">
         <v>83</v>
       </c>
+      <c r="C24">
+        <v>3.5</v>
+      </c>
+      <c r="D24">
+        <v>-122</v>
+      </c>
+      <c r="E24">
+        <v>105</v>
+      </c>
       <c r="F24" t="s">
         <v>82</v>
       </c>
@@ -2833,55 +2938,55 @@
         <v>42</v>
       </c>
       <c r="I24">
+        <v>5.1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>6</v>
       </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
       <c r="M24">
-        <v>0.1729</v>
+        <v>0.1804</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="P24">
-        <v>4.1</v>
+        <v>4.41</v>
       </c>
       <c r="Q24">
-        <v>0.1778</v>
+        <v>0.181</v>
       </c>
       <c r="R24">
-        <v>0.403</v>
+        <v>0.344</v>
       </c>
       <c r="S24" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2792</v>
+        <v>0.2135</v>
       </c>
       <c r="U24">
-        <v>0.2791</v>
+        <v>0.1753</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>0.2527</v>
+        <v>0.1766</v>
       </c>
       <c r="X24">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y24">
-        <v>1.0529</v>
+        <v>0.88</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2890,22 +2995,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.7</v>
+        <v>3.42</v>
       </c>
       <c r="AE24" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF24">
-        <v>0.1749</v>
+        <v>0.1806</v>
       </c>
       <c r="AG24">
-        <v>1.2632</v>
+        <v>0.9541</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>5.7</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2915,6 +3020,15 @@
       <c r="B25" t="s">
         <v>84</v>
       </c>
+      <c r="C25">
+        <v>5.5</v>
+      </c>
+      <c r="D25">
+        <v>126</v>
+      </c>
+      <c r="E25">
+        <v>-143</v>
+      </c>
       <c r="F25" t="s">
         <v>85</v>
       </c>
@@ -2934,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>0.2461</v>
@@ -2955,7 +3069,7 @@
         <v>0.353</v>
       </c>
       <c r="S25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T25">
         <v>0.1886</v>
@@ -2970,7 +3084,7 @@
         <v>0.2218</v>
       </c>
       <c r="X25">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y25">
         <v>0.9876</v>
@@ -2982,22 +3096,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.79</v>
+        <v>4.73</v>
       </c>
       <c r="AE25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF25">
         <v>0.2531</v>
       </c>
       <c r="AG25">
-        <v>0.8532</v>
+        <v>0.8428</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>4.79</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3007,65 +3121,32 @@
       <c r="B26" t="s">
         <v>86</v>
       </c>
+      <c r="C26">
+        <v>2.5</v>
+      </c>
+      <c r="D26">
+        <v>-160</v>
+      </c>
+      <c r="E26">
+        <v>129</v>
+      </c>
       <c r="F26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26">
-        <v>823911</v>
+        <v>85</v>
+      </c>
+      <c r="G26" t="s">
+        <v>44</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
-      </c>
-      <c r="I26">
-        <v>5</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0.2045</v>
-      </c>
-      <c r="N26">
-        <v>5</v>
-      </c>
-      <c r="O26">
-        <v>107</v>
-      </c>
-      <c r="P26">
-        <v>4.35</v>
-      </c>
-      <c r="Q26">
-        <v>0.215</v>
-      </c>
-      <c r="R26">
-        <v>0.349</v>
+        <v>3</v>
       </c>
       <c r="S26" t="s">
-        <v>52</v>
-      </c>
-      <c r="T26">
-        <v>0.3045</v>
-      </c>
-      <c r="U26">
-        <v>0.2034</v>
-      </c>
-      <c r="V26">
-        <v>9</v>
-      </c>
-      <c r="W26">
-        <v>0.2057</v>
-      </c>
-      <c r="X26">
-        <v>0.2211</v>
-      </c>
-      <c r="Y26">
-        <v>1.0045</v>
+        <v>44</v>
+      </c>
+      <c r="V26" t="s">
+        <v>44</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3073,23 +3154,8 @@
       <c r="AC26" t="s">
         <v>44</v>
       </c>
-      <c r="AD26">
-        <v>6.32</v>
-      </c>
       <c r="AE26" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF26">
-        <v>0.2082</v>
-      </c>
-      <c r="AG26">
-        <v>1.3774</v>
-      </c>
-      <c r="AH26">
-        <v>0.4</v>
-      </c>
-      <c r="AM26">
-        <v>6.72</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3097,19 +3163,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27">
+        <v>4.5</v>
+      </c>
+      <c r="D27">
+        <v>-135</v>
+      </c>
+      <c r="E27">
+        <v>108</v>
+      </c>
+      <c r="F27" t="s">
         <v>88</v>
       </c>
-      <c r="F27" t="s">
-        <v>87</v>
-      </c>
       <c r="G27">
-        <v>823911</v>
+        <v>823101</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3118,46 +3193,46 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>0.2446</v>
+        <v>0.1921</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="P27">
-        <v>3.83</v>
+        <v>4.16</v>
       </c>
       <c r="Q27">
-        <v>0.229</v>
+        <v>0.1241</v>
       </c>
       <c r="R27">
-        <v>0.396</v>
+        <v>0.407</v>
       </c>
       <c r="S27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T27">
-        <v>0.2148</v>
+        <v>0.2335</v>
       </c>
       <c r="U27">
-        <v>0.2153</v>
+        <v>0.2096</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2346</v>
+        <v>0.2425</v>
       </c>
       <c r="X27">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y27">
-        <v>1.0324</v>
+        <v>0.9904</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3166,22 +3241,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>6.04</v>
+        <v>4.01</v>
       </c>
       <c r="AE27" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="AF27">
-        <v>0.2384</v>
+        <v>0.1644</v>
       </c>
       <c r="AG27">
-        <v>0.9716</v>
+        <v>1.0433</v>
       </c>
       <c r="AH27">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>6.44</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3191,8 +3266,17 @@
       <c r="B28" t="s">
         <v>89</v>
       </c>
+      <c r="C28">
+        <v>4.5</v>
+      </c>
+      <c r="D28">
+        <v>-157</v>
+      </c>
+      <c r="E28">
+        <v>126</v>
+      </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G28">
         <v>823101</v>
@@ -3201,7 +3285,7 @@
         <v>42</v>
       </c>
       <c r="I28">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3210,46 +3294,46 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>0.1921</v>
+        <v>0.2306</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="P28">
-        <v>4.16</v>
+        <v>4.03</v>
       </c>
       <c r="Q28">
-        <v>0.1241</v>
+        <v>0.1984</v>
       </c>
       <c r="R28">
-        <v>0.407</v>
+        <v>0.387</v>
       </c>
       <c r="S28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T28">
-        <v>0.2335</v>
+        <v>0.2255</v>
       </c>
       <c r="U28">
-        <v>0.2096</v>
+        <v>0.2231</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2425</v>
+        <v>0.2183</v>
       </c>
       <c r="X28">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y28">
-        <v>0.9904</v>
+        <v>0.9568</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3258,22 +3342,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.06</v>
+        <v>4.72</v>
       </c>
       <c r="AE28" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AF28">
-        <v>0.1644</v>
+        <v>0.2182</v>
       </c>
       <c r="AG28">
-        <v>1.0561</v>
+        <v>1.0078</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.06</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3281,19 +3365,28 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29">
+        <v>7.5</v>
+      </c>
+      <c r="D29">
+        <v>125</v>
+      </c>
+      <c r="E29">
+        <v>-143</v>
+      </c>
+      <c r="F29" t="s">
         <v>91</v>
       </c>
-      <c r="F29" t="s">
-        <v>90</v>
-      </c>
       <c r="G29">
-        <v>823101</v>
+        <v>823911</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3302,46 +3395,46 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>0.2306</v>
+        <v>0.2446</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="P29">
-        <v>4.03</v>
+        <v>3.83</v>
       </c>
       <c r="Q29">
-        <v>0.1984</v>
+        <v>0.229</v>
       </c>
       <c r="R29">
-        <v>0.387</v>
+        <v>0.396</v>
       </c>
       <c r="S29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T29">
-        <v>0.2255</v>
+        <v>0.2148</v>
       </c>
       <c r="U29">
-        <v>0.2231</v>
+        <v>0.2153</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2183</v>
+        <v>0.2346</v>
       </c>
       <c r="X29">
-        <v>0.2211</v>
+        <v>0.2238</v>
       </c>
       <c r="Y29">
-        <v>0.9568</v>
+        <v>1.0324</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3350,22 +3443,399 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>4.78</v>
+        <v>5.97</v>
       </c>
       <c r="AE29" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF29">
+        <v>0.2384</v>
+      </c>
+      <c r="AG29">
+        <v>0.9598</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30">
+        <v>4.5</v>
+      </c>
+      <c r="D30">
+        <v>125</v>
+      </c>
+      <c r="E30">
+        <v>-143</v>
+      </c>
+      <c r="F30" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30">
+        <v>823911</v>
+      </c>
+      <c r="H30" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>6</v>
+      </c>
+      <c r="M30">
+        <v>0.2045</v>
+      </c>
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30">
+        <v>107</v>
+      </c>
+      <c r="P30">
+        <v>4.35</v>
+      </c>
+      <c r="Q30">
+        <v>0.215</v>
+      </c>
+      <c r="R30">
+        <v>0.349</v>
+      </c>
+      <c r="S30" t="s">
         <v>53</v>
       </c>
-      <c r="AF29">
-        <v>0.2182</v>
-      </c>
-      <c r="AG29">
-        <v>1.0202</v>
-      </c>
-      <c r="AH29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>4.78</v>
+      <c r="T30">
+        <v>0.3045</v>
+      </c>
+      <c r="U30">
+        <v>0.2034</v>
+      </c>
+      <c r="V30">
+        <v>9</v>
+      </c>
+      <c r="W30">
+        <v>0.2057</v>
+      </c>
+      <c r="X30">
+        <v>0.2238</v>
+      </c>
+      <c r="Y30">
+        <v>1.0045</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD30">
+        <v>6.24</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF30">
+        <v>0.2082</v>
+      </c>
+      <c r="AG30">
+        <v>1.3607</v>
+      </c>
+      <c r="AH30">
+        <v>0.4</v>
+      </c>
+      <c r="AM30">
+        <v>6.64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31">
+        <v>823420</v>
+      </c>
+      <c r="H31" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31">
+        <v>6</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0.2979</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31">
+        <v>138</v>
+      </c>
+      <c r="P31">
+        <v>4.13</v>
+      </c>
+      <c r="Q31">
+        <v>0.3043</v>
+      </c>
+      <c r="R31">
+        <v>0.408</v>
+      </c>
+      <c r="S31" t="s">
+        <v>43</v>
+      </c>
+      <c r="T31">
+        <v>0.2205</v>
+      </c>
+      <c r="U31">
+        <v>0.1899</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.1826</v>
+      </c>
+      <c r="X31">
+        <v>0.2238</v>
+      </c>
+      <c r="Y31">
+        <v>0.9461</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD31">
+        <v>6.96</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF31">
+        <v>0.3005</v>
+      </c>
+      <c r="AG31">
+        <v>0.9852</v>
+      </c>
+      <c r="AH31">
+        <v>0.4</v>
+      </c>
+      <c r="AM31">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32">
+        <v>823510</v>
+      </c>
+      <c r="H32" t="s">
+        <v>59</v>
+      </c>
+      <c r="I32">
+        <v>1.2</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0.2629</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32">
+        <v>17</v>
+      </c>
+      <c r="P32">
+        <v>4.18</v>
+      </c>
+      <c r="Q32">
+        <v>0.2353</v>
+      </c>
+      <c r="R32">
+        <v>0.078</v>
+      </c>
+      <c r="S32" t="s">
+        <v>53</v>
+      </c>
+      <c r="T32">
+        <v>0.2707</v>
+      </c>
+      <c r="U32">
+        <v>0.269</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
+        <v>0.2489</v>
+      </c>
+      <c r="X32">
+        <v>0.2238</v>
+      </c>
+      <c r="Y32">
+        <v>1.0065</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD32">
+        <v>1.62</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF32">
+        <v>0.2607</v>
+      </c>
+      <c r="AG32">
+        <v>1.2098</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33">
+        <v>824152</v>
+      </c>
+      <c r="H33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I33">
+        <v>5.5</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0.2139</v>
+      </c>
+      <c r="N33">
+        <v>5</v>
+      </c>
+      <c r="O33">
+        <v>122</v>
+      </c>
+      <c r="P33">
+        <v>4.19</v>
+      </c>
+      <c r="Q33">
+        <v>0.2295</v>
+      </c>
+      <c r="R33">
+        <v>0.379</v>
+      </c>
+      <c r="S33" t="s">
+        <v>53</v>
+      </c>
+      <c r="T33">
+        <v>0.21</v>
+      </c>
+      <c r="U33">
+        <v>0.2016</v>
+      </c>
+      <c r="V33">
+        <v>8</v>
+      </c>
+      <c r="W33">
+        <v>0.2184</v>
+      </c>
+      <c r="X33">
+        <v>0.2238</v>
+      </c>
+      <c r="Y33">
+        <v>0.956</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD33">
+        <v>4.51</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF33">
+        <v>0.2198</v>
+      </c>
+      <c r="AG33">
+        <v>0.9383</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>4.51</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-21.xlsx
+++ b/data/k-props/2026-08-21.xlsx
@@ -133,27 +133,27 @@
     <t>08/21/2026</t>
   </si>
   <si>
+    <t>Chris Sale</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
     <t>Jacob Misiorowski</t>
   </si>
   <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Chris Sale</t>
-  </si>
-  <si>
     <t>Hunter Dobbins</t>
   </si>
   <si>
@@ -163,142 +163,142 @@
     <t>&lt;6</t>
   </si>
   <si>
+    <t>Jesús Luzardo</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Mason Fluharty</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Brad Lord</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Freddy Peralta</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Trevor Rogers</t>
+  </si>
+  <si>
+    <t>Sean Manaea</t>
+  </si>
+  <si>
+    <t>New York Mets @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Troy Melton</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>J.T. Ginn</t>
+  </si>
+  <si>
+    <t>Athletics @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Hayden Wesneski</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Tanner Gordon</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Yoshinobu Yamamoto</t>
+  </si>
+  <si>
+    <t>Matthew Boyd</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Emerson Hancock</t>
+  </si>
+  <si>
     <t>Jesus Luzardo</t>
   </si>
   <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ New York Yankees</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>Brad Lord</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Freddy Peralta</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Trevor Rogers</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>New York Mets @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Sean Manaea</t>
-  </si>
-  <si>
-    <t>Hayden Wesneski</t>
-  </si>
-  <si>
-    <t>Athletics @ Houston Astros</t>
-  </si>
-  <si>
     <t>JT Ginn</t>
   </si>
   <si>
-    <t>Noah Cameron</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Troy Melton</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
-    <t>Tanner Gordon</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Joey Cantillo</t>
-  </si>
-  <si>
-    <t>Eduardo Rodriguez</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Nick Lodolo</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
     <t>Randy Vasquez</t>
-  </si>
-  <si>
-    <t>Matthew Boyd</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Emerson Hancock</t>
-  </si>
-  <si>
-    <t>Yoshinobu Yamamoto</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Jesús Luzardo</t>
-  </si>
-  <si>
-    <t>Mason Fluharty</t>
-  </si>
-  <si>
-    <t>J.T. Ginn</t>
   </si>
 </sst>
 </file>
@@ -812,13 +812,13 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="D2">
-        <v>120</v>
+        <v>-114</v>
       </c>
       <c r="E2">
-        <v>-142</v>
+        <v>-109</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -830,7 +830,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -842,43 +842,43 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.3985</v>
+        <v>0.3061</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="P2">
-        <v>3.79</v>
+        <v>4.02</v>
       </c>
       <c r="Q2">
-        <v>0.4095</v>
+        <v>0.3717</v>
       </c>
       <c r="R2">
-        <v>0.344</v>
+        <v>0.361</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.235</v>
+        <v>0.2301</v>
       </c>
       <c r="U2">
-        <v>0.2294</v>
+        <v>0.2196</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2201</v>
+        <v>0.2211</v>
       </c>
       <c r="X2">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y2">
-        <v>1.0407</v>
+        <v>0.9358</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -887,22 +887,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>10.07</v>
+        <v>7.33</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.4023</v>
+        <v>0.3298</v>
       </c>
       <c r="AG2">
-        <v>1.0501</v>
+        <v>1.014</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>10.07</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -913,13 +913,13 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="D3">
-        <v>-114</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>-109</v>
+        <v>-142</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -931,7 +931,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -943,43 +943,43 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.3095</v>
+        <v>0.3934</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P3">
-        <v>4.01</v>
+        <v>3.79</v>
       </c>
       <c r="Q3">
-        <v>0.3772</v>
+        <v>0.3909</v>
       </c>
       <c r="R3">
-        <v>0.363</v>
+        <v>0.355</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2301</v>
+        <v>0.235</v>
       </c>
       <c r="U3">
-        <v>0.2196</v>
+        <v>0.2294</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2211</v>
+        <v>0.2201</v>
       </c>
       <c r="X3">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y3">
-        <v>0.9358</v>
+        <v>1.0407</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -988,22 +988,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>7.55</v>
+        <v>9.68</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.3341</v>
+        <v>0.3925</v>
       </c>
       <c r="AG3">
-        <v>1.0283</v>
+        <v>1.0355</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>7.55</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1077,7 +1077,7 @@
         <v>0.2216</v>
       </c>
       <c r="X4">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y4">
         <v>0.922</v>
@@ -1089,7 +1089,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AE4" t="s">
         <v>49</v>
@@ -1098,13 +1098,13 @@
         <v>0.2293</v>
       </c>
       <c r="AG4">
-        <v>0.7285</v>
+        <v>0.7183</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1114,32 +1114,65 @@
       <c r="B5" t="s">
         <v>50</v>
       </c>
-      <c r="C5">
-        <v>7.5</v>
-      </c>
-      <c r="D5">
-        <v>115</v>
-      </c>
-      <c r="E5">
-        <v>-125</v>
-      </c>
       <c r="F5" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
-        <v>44</v>
+      <c r="G5">
+        <v>823420</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0.2979</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <v>138</v>
+      </c>
+      <c r="P5">
+        <v>4.13</v>
+      </c>
+      <c r="Q5">
+        <v>0.3043</v>
+      </c>
+      <c r="R5">
+        <v>0.408</v>
       </c>
       <c r="S5" t="s">
-        <v>44</v>
-      </c>
-      <c r="V5" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T5">
+        <v>0.2205</v>
+      </c>
+      <c r="U5">
+        <v>0.1899</v>
+      </c>
+      <c r="V5">
+        <v>9</v>
+      </c>
+      <c r="W5">
+        <v>0.1826</v>
+      </c>
+      <c r="X5">
+        <v>0.2269</v>
+      </c>
+      <c r="Y5">
+        <v>0.9461</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1147,8 +1180,23 @@
       <c r="AC5" t="s">
         <v>44</v>
       </c>
+      <c r="AD5">
+        <v>6.86</v>
+      </c>
       <c r="AE5" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AF5">
+        <v>0.3005</v>
+      </c>
+      <c r="AG5">
+        <v>0.9715</v>
+      </c>
+      <c r="AH5">
+        <v>0.4</v>
+      </c>
+      <c r="AM5">
+        <v>7.26</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1156,76 +1204,67 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6">
-        <v>6.5</v>
-      </c>
-      <c r="D6">
-        <v>-111</v>
-      </c>
-      <c r="E6">
-        <v>-108</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>823510</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I6">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0.314</v>
+        <v>0.2629</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="P6">
-        <v>3.96</v>
+        <v>4.18</v>
       </c>
       <c r="Q6">
-        <v>0.3894</v>
+        <v>0.2353</v>
       </c>
       <c r="R6">
-        <v>0.361</v>
+        <v>0.078</v>
       </c>
       <c r="S6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2061</v>
+        <v>0.2789</v>
       </c>
       <c r="U6">
-        <v>0.1922</v>
+        <v>0.2767</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.1899</v>
+        <v>0.2489</v>
       </c>
       <c r="X6">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y6">
-        <v>0.9895</v>
+        <v>1.0045</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1234,22 +1273,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>7.2</v>
+        <v>1.64</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF6">
-        <v>0.3412</v>
+        <v>0.2607</v>
       </c>
       <c r="AG6">
-        <v>0.9211</v>
+        <v>1.229</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>7.2</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1257,22 +1296,22 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D7">
-        <v>-104</v>
+        <v>-111</v>
       </c>
       <c r="E7">
-        <v>-116</v>
+        <v>-108</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>824721</v>
+        <v>823510</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
@@ -1290,43 +1329,43 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>0.2183</v>
+        <v>0.314</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="P7">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="Q7">
-        <v>0.2109</v>
+        <v>0.3894</v>
       </c>
       <c r="R7">
-        <v>0.39</v>
+        <v>0.361</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2111</v>
+        <v>0.214</v>
       </c>
       <c r="U7">
-        <v>0.2135</v>
+        <v>0.193</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2042</v>
+        <v>0.1899</v>
       </c>
       <c r="X7">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y7">
-        <v>0.9508</v>
+        <v>0.98</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1335,22 +1374,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="AE7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.2154</v>
+        <v>0.3412</v>
       </c>
       <c r="AG7">
-        <v>0.9436</v>
+        <v>0.9429</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1370,7 +1409,7 @@
         <v>-108</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>824721</v>
@@ -1424,7 +1463,7 @@
         <v>0.2153</v>
       </c>
       <c r="X8">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y8">
         <v>0.9943</v>
@@ -1436,7 +1475,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="AE8" t="s">
         <v>49</v>
@@ -1445,13 +1484,13 @@
         <v>0.1996</v>
       </c>
       <c r="AG8">
-        <v>0.8639</v>
+        <v>0.8519</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1459,76 +1498,76 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>5.5</v>
+      </c>
+      <c r="D9">
+        <v>-104</v>
+      </c>
+      <c r="E9">
+        <v>-116</v>
+      </c>
+      <c r="F9" t="s">
         <v>57</v>
       </c>
-      <c r="C9">
-        <v>2.5</v>
-      </c>
-      <c r="D9">
-        <v>-106</v>
-      </c>
-      <c r="E9">
-        <v>-110</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
       <c r="G9">
-        <v>823830</v>
+        <v>824721</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9">
+        <v>6</v>
+      </c>
+      <c r="M9">
+        <v>0.2183</v>
+      </c>
+      <c r="N9">
         <v>5</v>
       </c>
-      <c r="M9">
-        <v>0.2119</v>
-      </c>
-      <c r="N9">
-        <v>3</v>
-      </c>
       <c r="O9">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="P9">
-        <v>4.32</v>
+        <v>4.04</v>
       </c>
       <c r="Q9">
-        <v>0.2069</v>
+        <v>0.2109</v>
       </c>
       <c r="R9">
-        <v>0.127</v>
+        <v>0.39</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2444</v>
+        <v>0.2111</v>
       </c>
       <c r="U9">
-        <v>0.2296</v>
+        <v>0.2135</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2126</v>
+        <v>0.2042</v>
       </c>
       <c r="X9">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y9">
-        <v>0.8899</v>
+        <v>0.9508</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1537,22 +1576,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>1.67</v>
+        <v>4.44</v>
       </c>
       <c r="AE9" t="s">
         <v>49</v>
       </c>
       <c r="AF9">
-        <v>0.2113</v>
+        <v>0.2154</v>
       </c>
       <c r="AG9">
-        <v>1.0923</v>
+        <v>0.9304</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.67</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1560,76 +1599,76 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>2.5</v>
+      </c>
+      <c r="D10">
+        <v>-106</v>
+      </c>
+      <c r="E10">
+        <v>-110</v>
+      </c>
+      <c r="F10" t="s">
         <v>60</v>
-      </c>
-      <c r="C10">
-        <v>4.5</v>
-      </c>
-      <c r="D10">
-        <v>122</v>
-      </c>
-      <c r="E10">
-        <v>-152</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
       </c>
       <c r="G10">
         <v>823830</v>
       </c>
       <c r="H10" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>0.2068</v>
+        <v>0.2119</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="P10">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="Q10">
-        <v>0.2222</v>
+        <v>0.2069</v>
       </c>
       <c r="R10">
-        <v>0.331</v>
+        <v>0.127</v>
       </c>
       <c r="S10" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2145</v>
+        <v>0.2444</v>
       </c>
       <c r="U10">
-        <v>0.2181</v>
+        <v>0.2296</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2085</v>
+        <v>0.2126</v>
       </c>
       <c r="X10">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y10">
-        <v>0.9883</v>
+        <v>0.8899</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1638,22 +1677,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="s">
         <v>49</v>
       </c>
       <c r="AF10">
-        <v>0.2119</v>
+        <v>0.2113</v>
       </c>
       <c r="AG10">
-        <v>0.9588</v>
+        <v>1.0771</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.57</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1661,28 +1700,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11">
+        <v>4.5</v>
+      </c>
+      <c r="D11">
+        <v>122</v>
+      </c>
+      <c r="E11">
+        <v>-152</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11">
+        <v>823830</v>
+      </c>
+      <c r="H11" t="s">
         <v>62</v>
       </c>
-      <c r="C11">
-        <v>5.5</v>
-      </c>
-      <c r="D11">
-        <v>112</v>
-      </c>
-      <c r="E11">
-        <v>-133</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <v>824800</v>
-      </c>
-      <c r="H11" t="s">
-        <v>42</v>
-      </c>
       <c r="I11">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1691,46 +1730,46 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2147</v>
+        <v>0.2068</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="P11">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="Q11">
-        <v>0.1776</v>
+        <v>0.2222</v>
       </c>
       <c r="R11">
-        <v>0.349</v>
+        <v>0.331</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.266</v>
+        <v>0.2071</v>
       </c>
       <c r="U11">
-        <v>0.2421</v>
+        <v>0.2083</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2383</v>
+        <v>0.2085</v>
       </c>
       <c r="X11">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y11">
-        <v>1.0527</v>
+        <v>0.9397</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1739,22 +1778,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.79</v>
+        <v>3.23</v>
       </c>
       <c r="AE11" t="s">
         <v>49</v>
       </c>
       <c r="AF11">
-        <v>0.2017</v>
+        <v>0.2119</v>
       </c>
       <c r="AG11">
-        <v>1.1886</v>
+        <v>0.9126</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.79</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1762,19 +1801,19 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12">
+        <v>5.5</v>
+      </c>
+      <c r="D12">
+        <v>112</v>
+      </c>
+      <c r="E12">
+        <v>-133</v>
+      </c>
+      <c r="F12" t="s">
         <v>64</v>
-      </c>
-      <c r="C12">
-        <v>4.5</v>
-      </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
-      <c r="E12">
-        <v>-115</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
       </c>
       <c r="G12">
         <v>824800</v>
@@ -1783,7 +1822,7 @@
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1795,43 +1834,43 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>0.2042</v>
+        <v>0.2147</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="P12">
-        <v>4.21</v>
+        <v>4.48</v>
       </c>
       <c r="Q12">
-        <v>0.2583</v>
+        <v>0.1776</v>
       </c>
       <c r="R12">
-        <v>0.375</v>
+        <v>0.349</v>
       </c>
       <c r="S12" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1703</v>
+        <v>0.266</v>
       </c>
       <c r="U12">
-        <v>0.1698</v>
+        <v>0.2421</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.1849</v>
+        <v>0.2383</v>
       </c>
       <c r="X12">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y12">
-        <v>0.9069</v>
+        <v>1.0527</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1840,22 +1879,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.56</v>
+        <v>5.71</v>
       </c>
       <c r="AE12" t="s">
         <v>49</v>
       </c>
       <c r="AF12">
-        <v>0.2245</v>
+        <v>0.2017</v>
       </c>
       <c r="AG12">
-        <v>0.7608</v>
+        <v>1.1721</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.56</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1866,19 +1905,19 @@
         <v>65</v>
       </c>
       <c r="C13">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D13">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E13">
-        <v>-135</v>
+        <v>-115</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G13">
-        <v>824559</v>
+        <v>824800</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
@@ -1896,67 +1935,67 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>0.2697</v>
+        <v>0.2042</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="P13">
-        <v>4.08</v>
+        <v>4.21</v>
       </c>
       <c r="Q13">
-        <v>0.3009</v>
+        <v>0.2583</v>
       </c>
       <c r="R13">
-        <v>0.361</v>
+        <v>0.375</v>
       </c>
       <c r="S13" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2328</v>
+        <v>0.1581</v>
       </c>
       <c r="U13">
-        <v>0.2359</v>
+        <v>0.1607</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
+        <v>0.1849</v>
+      </c>
+      <c r="X13">
+        <v>0.2269</v>
+      </c>
+      <c r="Y13">
+        <v>0.88</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD13">
+        <v>3.16</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF13">
         <v>0.2245</v>
       </c>
-      <c r="X13">
-        <v>0.2238</v>
-      </c>
-      <c r="Y13">
-        <v>0.9824</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD13">
-        <v>6.41</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF13">
-        <v>0.281</v>
-      </c>
       <c r="AG13">
-        <v>1.0405</v>
+        <v>0.6966</v>
       </c>
       <c r="AH13">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>6.81</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1964,7 +2003,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -1976,7 +2015,7 @@
         <v>115</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>824559</v>
@@ -2030,7 +2069,7 @@
         <v>0.2467</v>
       </c>
       <c r="X14">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y14">
         <v>1.1</v>
@@ -2042,7 +2081,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2051,13 +2090,13 @@
         <v>0.2408</v>
       </c>
       <c r="AG14">
-        <v>1.13</v>
+        <v>1.1143</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>7.35</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2065,28 +2104,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D15">
-        <v>-114</v>
+        <v>112</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>-135</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G15">
-        <v>824152</v>
+        <v>824559</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2098,43 +2137,43 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>0.1895</v>
+        <v>0.2697</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="P15">
-        <v>4.19</v>
+        <v>4.08</v>
       </c>
       <c r="Q15">
-        <v>0.1895</v>
+        <v>0.3009</v>
       </c>
       <c r="R15">
-        <v>0.322</v>
+        <v>0.361</v>
       </c>
       <c r="S15" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2428</v>
+        <v>0.2512</v>
       </c>
       <c r="U15">
-        <v>0.2166</v>
+        <v>0.2436</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2117</v>
+        <v>0.2245</v>
       </c>
       <c r="X15">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y15">
-        <v>1.0315</v>
+        <v>0.9737</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2143,22 +2182,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.04</v>
+        <v>6.77</v>
       </c>
       <c r="AE15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF15">
-        <v>0.1895</v>
+        <v>0.281</v>
       </c>
       <c r="AG15">
-        <v>1.0849</v>
+        <v>1.1072</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM15">
-        <v>5.04</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2166,34 +2205,76 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C16">
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>-119</v>
+        <v>-102</v>
       </c>
       <c r="E16">
-        <v>-102</v>
+        <v>-118</v>
       </c>
       <c r="F16" t="s">
         <v>70</v>
       </c>
-      <c r="G16" t="s">
-        <v>44</v>
+      <c r="G16">
+        <v>824072</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
       </c>
       <c r="L16">
+        <v>6</v>
+      </c>
+      <c r="M16">
+        <v>0.2219</v>
+      </c>
+      <c r="N16">
         <v>5</v>
       </c>
+      <c r="O16">
+        <v>117</v>
+      </c>
+      <c r="P16">
+        <v>3.9</v>
+      </c>
+      <c r="Q16">
+        <v>0.1966</v>
+      </c>
+      <c r="R16">
+        <v>0.369</v>
+      </c>
       <c r="S16" t="s">
-        <v>44</v>
-      </c>
-      <c r="V16" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T16">
+        <v>0.1922</v>
+      </c>
+      <c r="U16">
+        <v>0.196</v>
+      </c>
+      <c r="V16">
+        <v>9</v>
+      </c>
+      <c r="W16">
+        <v>0.2092</v>
+      </c>
+      <c r="X16">
+        <v>0.2269</v>
+      </c>
+      <c r="Y16">
+        <v>0.9306</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2201,8 +2282,23 @@
       <c r="AC16" t="s">
         <v>44</v>
       </c>
+      <c r="AD16">
+        <v>3.94</v>
+      </c>
       <c r="AE16" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF16">
+        <v>0.2125</v>
+      </c>
+      <c r="AG16">
+        <v>0.847</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>3.94</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2210,7 +2306,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17">
         <v>5.5</v>
@@ -2222,7 +2318,7 @@
         <v>-136</v>
       </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G17">
         <v>824072</v>
@@ -2261,13 +2357,13 @@
         <v>0.399</v>
       </c>
       <c r="S17" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.188</v>
+        <v>0.2058</v>
       </c>
       <c r="U17">
-        <v>0.1962</v>
+        <v>0.2085</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2276,10 +2372,10 @@
         <v>0.2305</v>
       </c>
       <c r="X17">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y17">
-        <v>0.9878</v>
+        <v>1.0031</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2288,7 +2384,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.2</v>
+        <v>4.61</v>
       </c>
       <c r="AE17" t="s">
         <v>49</v>
@@ -2297,13 +2393,13 @@
         <v>0.2116</v>
       </c>
       <c r="AG17">
-        <v>0.8402</v>
+        <v>0.9069</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.2</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2311,28 +2407,19 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18">
-        <v>4.5</v>
-      </c>
-      <c r="D18">
-        <v>-102</v>
-      </c>
-      <c r="E18">
-        <v>-118</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
         <v>73</v>
       </c>
       <c r="G18">
-        <v>824072</v>
+        <v>824152</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2341,46 +2428,46 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>0.2219</v>
+        <v>0.2139</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="P18">
-        <v>3.9</v>
+        <v>4.19</v>
       </c>
       <c r="Q18">
-        <v>0.1966</v>
+        <v>0.2295</v>
       </c>
       <c r="R18">
-        <v>0.369</v>
+        <v>0.379</v>
       </c>
       <c r="S18" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T18">
-        <v>0.1823</v>
+        <v>0.2096</v>
       </c>
       <c r="U18">
-        <v>0.1931</v>
+        <v>0.1755</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2092</v>
+        <v>0.2184</v>
       </c>
       <c r="X18">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y18">
-        <v>0.958</v>
+        <v>0.8828</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2389,22 +2476,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AE18" t="s">
         <v>49</v>
       </c>
       <c r="AF18">
-        <v>0.2125</v>
+        <v>0.2198</v>
       </c>
       <c r="AG18">
-        <v>0.8148</v>
+        <v>0.9237</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2412,28 +2499,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>-120</v>
+        <v>-114</v>
       </c>
       <c r="E19">
-        <v>-103</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G19">
-        <v>822857</v>
+        <v>824152</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2442,46 +2529,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>0.258</v>
+        <v>0.1895</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="P19">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="Q19">
-        <v>0.2623</v>
+        <v>0.1895</v>
       </c>
       <c r="R19">
-        <v>0.379</v>
+        <v>0.322</v>
       </c>
       <c r="S19" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T19">
-        <v>0.268</v>
+        <v>0.1949</v>
       </c>
       <c r="U19">
-        <v>0.2523</v>
+        <v>0.1897</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2537</v>
+        <v>0.2117</v>
       </c>
       <c r="X19">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y19">
-        <v>1.0378</v>
+        <v>1.0194</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2490,22 +2577,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>7.41</v>
+        <v>3.94</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF19">
-        <v>0.2596</v>
+        <v>0.1895</v>
       </c>
       <c r="AG19">
-        <v>1.1979</v>
+        <v>0.8591</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>7.41</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2513,7 +2600,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>6.5</v>
@@ -2564,13 +2651,13 @@
         <v>0.344</v>
       </c>
       <c r="S20" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2098</v>
+        <v>0.2445</v>
       </c>
       <c r="U20">
-        <v>0.237</v>
+        <v>0.2455</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2579,10 +2666,10 @@
         <v>0.2456</v>
       </c>
       <c r="X20">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y20">
-        <v>1.0269</v>
+        <v>1.0791</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2591,22 +2678,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>6.92</v>
+        <v>8.36</v>
       </c>
       <c r="AE20" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AF20">
         <v>0.3104</v>
       </c>
       <c r="AG20">
-        <v>0.9377</v>
+        <v>1.0773</v>
       </c>
       <c r="AH20">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>7.32</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2614,28 +2701,28 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="D21">
-        <v>-165</v>
+        <v>-120</v>
       </c>
       <c r="E21">
-        <v>138</v>
+        <v>-103</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G21">
-        <v>824317</v>
+        <v>822857</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2644,46 +2731,46 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>0.1987</v>
+        <v>0.258</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="P21">
-        <v>4.37</v>
+        <v>4.27</v>
       </c>
       <c r="Q21">
-        <v>0.1574</v>
+        <v>0.2623</v>
       </c>
       <c r="R21">
-        <v>0.351</v>
+        <v>0.379</v>
       </c>
       <c r="S21" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2103</v>
+        <v>0.3053</v>
       </c>
       <c r="U21">
-        <v>0.1891</v>
+        <v>0.2866</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2149</v>
+        <v>0.2537</v>
       </c>
       <c r="X21">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y21">
-        <v>0.9358</v>
+        <v>1.1182</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2692,22 +2779,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>3.26</v>
+        <v>8.97</v>
       </c>
       <c r="AE21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.1842</v>
+        <v>0.2596</v>
       </c>
       <c r="AG21">
-        <v>0.9397</v>
+        <v>1.3453</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>3.26</v>
+        <v>8.97</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2715,7 +2802,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2766,13 +2853,13 @@
         <v>0.303</v>
       </c>
       <c r="S22" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2332</v>
+        <v>0.2761</v>
       </c>
       <c r="U22">
-        <v>0.2269</v>
+        <v>0.2214</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2781,10 +2868,10 @@
         <v>0.2484</v>
       </c>
       <c r="X22">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y22">
-        <v>1.0211</v>
+        <v>1.0239</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2793,22 +2880,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>6.05</v>
+        <v>7.09</v>
       </c>
       <c r="AE22" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AF22">
         <v>0.2728</v>
       </c>
       <c r="AG22">
-        <v>1.042</v>
+        <v>1.2169</v>
       </c>
       <c r="AH22">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>6.45</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2816,28 +2903,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="D23">
-        <v>116</v>
+        <v>-165</v>
       </c>
       <c r="E23">
-        <v>-139</v>
+        <v>138</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G23">
-        <v>825045</v>
+        <v>824317</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2846,46 +2933,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>0.1729</v>
+        <v>0.1987</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="P23">
-        <v>4.1</v>
+        <v>4.37</v>
       </c>
       <c r="Q23">
-        <v>0.1778</v>
+        <v>0.1574</v>
       </c>
       <c r="R23">
-        <v>0.403</v>
+        <v>0.351</v>
       </c>
       <c r="S23" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2792</v>
+        <v>0.1697</v>
       </c>
       <c r="U23">
-        <v>0.2791</v>
+        <v>0.1722</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2527</v>
+        <v>0.2149</v>
       </c>
       <c r="X23">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y23">
-        <v>1.0529</v>
+        <v>0.88</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2894,22 +2981,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.63</v>
+        <v>2.44</v>
       </c>
       <c r="AE23" t="s">
         <v>49</v>
       </c>
       <c r="AF23">
-        <v>0.1749</v>
+        <v>0.1842</v>
       </c>
       <c r="AG23">
-        <v>1.2479</v>
+        <v>0.7477</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>5.63</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2917,7 +3004,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -2983,7 +3070,7 @@
         <v>0.1766</v>
       </c>
       <c r="X24">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y24">
         <v>0.88</v>
@@ -2995,7 +3082,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="AE24" t="s">
         <v>49</v>
@@ -3004,13 +3091,13 @@
         <v>0.1806</v>
       </c>
       <c r="AG24">
-        <v>0.9541</v>
+        <v>0.9408</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3018,28 +3105,28 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25">
         <v>5.5</v>
       </c>
       <c r="D25">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E25">
-        <v>-143</v>
+        <v>-139</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G25">
-        <v>823262</v>
+        <v>825045</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3051,43 +3138,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.2461</v>
+        <v>0.1729</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="P25">
-        <v>4.36</v>
+        <v>4.1</v>
       </c>
       <c r="Q25">
-        <v>0.2661</v>
+        <v>0.1778</v>
       </c>
       <c r="R25">
-        <v>0.353</v>
+        <v>0.403</v>
       </c>
       <c r="S25" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="T25">
-        <v>0.1886</v>
+        <v>0.2946</v>
       </c>
       <c r="U25">
-        <v>0.191</v>
+        <v>0.2815</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2218</v>
+        <v>0.2527</v>
       </c>
       <c r="X25">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y25">
-        <v>0.9876</v>
+        <v>1.113</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3096,22 +3183,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.73</v>
+        <v>6.2</v>
       </c>
       <c r="AE25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF25">
-        <v>0.2531</v>
+        <v>0.1749</v>
       </c>
       <c r="AG25">
-        <v>0.8428</v>
+        <v>1.2984</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM25">
-        <v>4.73</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3119,34 +3206,76 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C26">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="D26">
-        <v>-160</v>
+        <v>126</v>
       </c>
       <c r="E26">
-        <v>129</v>
+        <v>-143</v>
       </c>
       <c r="F26" t="s">
         <v>85</v>
       </c>
-      <c r="G26" t="s">
-        <v>44</v>
+      <c r="G26">
+        <v>823262</v>
       </c>
       <c r="H26" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I26">
+        <v>5.2</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M26">
+        <v>0.2461</v>
+      </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26">
+        <v>109</v>
+      </c>
+      <c r="P26">
+        <v>4.36</v>
+      </c>
+      <c r="Q26">
+        <v>0.2661</v>
+      </c>
+      <c r="R26">
+        <v>0.353</v>
       </c>
       <c r="S26" t="s">
-        <v>44</v>
-      </c>
-      <c r="V26" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T26">
+        <v>0.1954</v>
+      </c>
+      <c r="U26">
+        <v>0.1949</v>
+      </c>
+      <c r="V26">
+        <v>9</v>
+      </c>
+      <c r="W26">
+        <v>0.2218</v>
+      </c>
+      <c r="X26">
+        <v>0.2269</v>
+      </c>
+      <c r="Y26">
+        <v>1.0141</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3154,8 +3283,23 @@
       <c r="AC26" t="s">
         <v>44</v>
       </c>
+      <c r="AD26">
+        <v>4.97</v>
+      </c>
       <c r="AE26" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF26">
+        <v>0.2531</v>
+      </c>
+      <c r="AG26">
+        <v>0.8612</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>4.97</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3163,28 +3307,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27">
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>-135</v>
+        <v>125</v>
       </c>
       <c r="E27">
-        <v>108</v>
+        <v>-143</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G27">
-        <v>823101</v>
+        <v>823911</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3196,43 +3340,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1921</v>
+        <v>0.2045</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="P27">
-        <v>4.16</v>
+        <v>4.35</v>
       </c>
       <c r="Q27">
-        <v>0.1241</v>
+        <v>0.215</v>
       </c>
       <c r="R27">
-        <v>0.407</v>
+        <v>0.349</v>
       </c>
       <c r="S27" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="T27">
-        <v>0.2335</v>
+        <v>0.3045</v>
       </c>
       <c r="U27">
-        <v>0.2096</v>
+        <v>0.2034</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2425</v>
+        <v>0.2057</v>
       </c>
       <c r="X27">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y27">
-        <v>0.9904</v>
+        <v>1.0045</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3241,22 +3385,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>4.01</v>
+        <v>6.16</v>
       </c>
       <c r="AE27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF27">
-        <v>0.1644</v>
+        <v>0.2082</v>
       </c>
       <c r="AG27">
-        <v>1.0433</v>
+        <v>1.3418</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM27">
-        <v>4.01</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3267,25 +3411,25 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="D28">
-        <v>-157</v>
+        <v>125</v>
       </c>
       <c r="E28">
-        <v>126</v>
+        <v>-143</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G28">
-        <v>823101</v>
+        <v>823911</v>
       </c>
       <c r="H28" t="s">
         <v>42</v>
       </c>
       <c r="I28">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3297,43 +3441,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.2306</v>
+        <v>0.2446</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="P28">
-        <v>4.03</v>
+        <v>3.83</v>
       </c>
       <c r="Q28">
-        <v>0.1984</v>
+        <v>0.229</v>
       </c>
       <c r="R28">
-        <v>0.387</v>
+        <v>0.396</v>
       </c>
       <c r="S28" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="T28">
-        <v>0.2255</v>
+        <v>0.2148</v>
       </c>
       <c r="U28">
-        <v>0.2231</v>
+        <v>0.2153</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2183</v>
+        <v>0.2346</v>
       </c>
       <c r="X28">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y28">
-        <v>0.9568</v>
+        <v>1.0324</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3342,22 +3486,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>4.72</v>
+        <v>5.89</v>
       </c>
       <c r="AE28" t="s">
         <v>49</v>
       </c>
       <c r="AF28">
-        <v>0.2182</v>
+        <v>0.2384</v>
       </c>
       <c r="AG28">
-        <v>1.0078</v>
+        <v>0.9464</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>4.72</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3368,25 +3512,25 @@
         <v>90</v>
       </c>
       <c r="C29">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="D29">
-        <v>125</v>
+        <v>-135</v>
       </c>
       <c r="E29">
-        <v>-143</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s">
         <v>91</v>
       </c>
       <c r="G29">
-        <v>823911</v>
+        <v>823101</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3398,43 +3542,43 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>0.2446</v>
+        <v>0.1921</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="P29">
-        <v>3.83</v>
+        <v>4.16</v>
       </c>
       <c r="Q29">
-        <v>0.229</v>
+        <v>0.1241</v>
       </c>
       <c r="R29">
-        <v>0.396</v>
+        <v>0.407</v>
       </c>
       <c r="S29" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="T29">
-        <v>0.2148</v>
+        <v>0.2335</v>
       </c>
       <c r="U29">
-        <v>0.2153</v>
+        <v>0.2096</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2346</v>
+        <v>0.2425</v>
       </c>
       <c r="X29">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y29">
-        <v>1.0324</v>
+        <v>0.9904</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3443,22 +3587,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>5.97</v>
+        <v>3.95</v>
       </c>
       <c r="AE29" t="s">
         <v>49</v>
       </c>
       <c r="AF29">
-        <v>0.2384</v>
+        <v>0.1644</v>
       </c>
       <c r="AG29">
-        <v>0.9598</v>
+        <v>1.0288</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>5.97</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3472,22 +3616,22 @@
         <v>4.5</v>
       </c>
       <c r="D30">
-        <v>125</v>
+        <v>-157</v>
       </c>
       <c r="E30">
-        <v>-143</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s">
         <v>91</v>
       </c>
       <c r="G30">
-        <v>823911</v>
+        <v>823101</v>
       </c>
       <c r="H30" t="s">
         <v>42</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3499,43 +3643,43 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>0.2045</v>
+        <v>0.2306</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="P30">
-        <v>4.35</v>
+        <v>4.03</v>
       </c>
       <c r="Q30">
-        <v>0.215</v>
+        <v>0.1984</v>
       </c>
       <c r="R30">
-        <v>0.349</v>
+        <v>0.387</v>
       </c>
       <c r="S30" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="T30">
-        <v>0.3045</v>
+        <v>0.2255</v>
       </c>
       <c r="U30">
-        <v>0.2034</v>
+        <v>0.2231</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2057</v>
+        <v>0.2183</v>
       </c>
       <c r="X30">
-        <v>0.2238</v>
+        <v>0.2269</v>
       </c>
       <c r="Y30">
-        <v>1.0045</v>
+        <v>0.9568</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3544,22 +3688,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>6.24</v>
+        <v>4.65</v>
       </c>
       <c r="AE30" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="AF30">
-        <v>0.2082</v>
+        <v>0.2182</v>
       </c>
       <c r="AG30">
-        <v>1.3607</v>
+        <v>0.9938</v>
       </c>
       <c r="AH30">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>6.64</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3569,65 +3713,32 @@
       <c r="B31" t="s">
         <v>93</v>
       </c>
+      <c r="C31">
+        <v>7.5</v>
+      </c>
+      <c r="D31">
+        <v>115</v>
+      </c>
+      <c r="E31">
+        <v>-125</v>
+      </c>
       <c r="F31" t="s">
         <v>48</v>
       </c>
-      <c r="G31">
-        <v>823420</v>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
-      </c>
-      <c r="I31">
+        <v>44</v>
+      </c>
+      <c r="L31">
         <v>6</v>
       </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0.2979</v>
-      </c>
-      <c r="N31">
-        <v>5</v>
-      </c>
-      <c r="O31">
-        <v>138</v>
-      </c>
-      <c r="P31">
-        <v>4.13</v>
-      </c>
-      <c r="Q31">
-        <v>0.3043</v>
-      </c>
-      <c r="R31">
-        <v>0.408</v>
-      </c>
       <c r="S31" t="s">
-        <v>43</v>
-      </c>
-      <c r="T31">
-        <v>0.2205</v>
-      </c>
-      <c r="U31">
-        <v>0.1899</v>
-      </c>
-      <c r="V31">
-        <v>9</v>
-      </c>
-      <c r="W31">
-        <v>0.1826</v>
-      </c>
-      <c r="X31">
-        <v>0.2238</v>
-      </c>
-      <c r="Y31">
-        <v>0.9461</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3635,23 +3746,8 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
-      <c r="AD31">
-        <v>6.96</v>
-      </c>
       <c r="AE31" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF31">
-        <v>0.3005</v>
-      </c>
-      <c r="AG31">
-        <v>0.9852</v>
-      </c>
-      <c r="AH31">
-        <v>0.4</v>
-      </c>
-      <c r="AM31">
-        <v>7.36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3661,65 +3757,32 @@
       <c r="B32" t="s">
         <v>94</v>
       </c>
+      <c r="C32">
+        <v>4.5</v>
+      </c>
+      <c r="D32">
+        <v>-119</v>
+      </c>
+      <c r="E32">
+        <v>-102</v>
+      </c>
       <c r="F32" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32">
-        <v>823510</v>
+        <v>73</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>59</v>
-      </c>
-      <c r="I32">
-        <v>1.2</v>
-      </c>
-      <c r="J32" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.2629</v>
-      </c>
-      <c r="N32">
-        <v>3</v>
-      </c>
-      <c r="O32">
-        <v>17</v>
-      </c>
-      <c r="P32">
-        <v>4.18</v>
-      </c>
-      <c r="Q32">
-        <v>0.2353</v>
-      </c>
-      <c r="R32">
-        <v>0.078</v>
+        <v>5</v>
       </c>
       <c r="S32" t="s">
-        <v>53</v>
-      </c>
-      <c r="T32">
-        <v>0.2707</v>
-      </c>
-      <c r="U32">
-        <v>0.269</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2489</v>
-      </c>
-      <c r="X32">
-        <v>0.2238</v>
-      </c>
-      <c r="Y32">
-        <v>1.0065</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3727,23 +3790,8 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
-      <c r="AD32">
-        <v>1.62</v>
-      </c>
       <c r="AE32" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF32">
-        <v>0.2607</v>
-      </c>
-      <c r="AG32">
-        <v>1.2098</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>1.62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3753,65 +3801,32 @@
       <c r="B33" t="s">
         <v>95</v>
       </c>
+      <c r="C33">
+        <v>2.5</v>
+      </c>
+      <c r="D33">
+        <v>-160</v>
+      </c>
+      <c r="E33">
+        <v>129</v>
+      </c>
       <c r="F33" t="s">
-        <v>70</v>
-      </c>
-      <c r="G33">
-        <v>824152</v>
+        <v>85</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
       </c>
       <c r="H33" t="s">
-        <v>42</v>
-      </c>
-      <c r="I33">
-        <v>5.5</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0.2139</v>
-      </c>
-      <c r="N33">
-        <v>5</v>
-      </c>
-      <c r="O33">
-        <v>122</v>
-      </c>
-      <c r="P33">
-        <v>4.19</v>
-      </c>
-      <c r="Q33">
-        <v>0.2295</v>
-      </c>
-      <c r="R33">
-        <v>0.379</v>
+        <v>3</v>
       </c>
       <c r="S33" t="s">
-        <v>53</v>
-      </c>
-      <c r="T33">
-        <v>0.21</v>
-      </c>
-      <c r="U33">
-        <v>0.2016</v>
-      </c>
-      <c r="V33">
-        <v>8</v>
-      </c>
-      <c r="W33">
-        <v>0.2184</v>
-      </c>
-      <c r="X33">
-        <v>0.2238</v>
-      </c>
-      <c r="Y33">
-        <v>0.956</v>
+        <v>44</v>
+      </c>
+      <c r="V33" t="s">
+        <v>44</v>
       </c>
       <c r="AA33" t="s">
         <v>44</v>
@@ -3819,23 +3834,8 @@
       <c r="AC33" t="s">
         <v>44</v>
       </c>
-      <c r="AD33">
-        <v>4.51</v>
-      </c>
       <c r="AE33" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF33">
-        <v>0.2198</v>
-      </c>
-      <c r="AG33">
-        <v>0.9383</v>
-      </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>4.51</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-21.xlsx
+++ b/data/k-props/2026-08-21.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="97">
   <si>
     <t>date</t>
   </si>
@@ -133,172 +133,175 @@
     <t>08/21/2026</t>
   </si>
   <si>
+    <t>Hunter Dobbins</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Jesus Luzardo</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ New York Yankees</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>Brad Lord</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Freddy Peralta</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Trevor Rogers</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>New York Mets @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Sean Manaea</t>
+  </si>
+  <si>
+    <t>Hayden Wesneski</t>
+  </si>
+  <si>
+    <t>Athletics @ Houston Astros</t>
+  </si>
+  <si>
+    <t>JT Ginn</t>
+  </si>
+  <si>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Troy Melton</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>Tanner Gordon</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Randy Vasquez</t>
+  </si>
+  <si>
+    <t>Matthew Boyd</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Emerson Hancock</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Yoshinobu Yamamoto</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
     <t>Chris Sale</t>
   </si>
   <si>
     <t>Atlanta Braves @ Milwaukee Brewers</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
     <t>Jacob Misiorowski</t>
   </si>
   <si>
-    <t>Hunter Dobbins</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Jesús Luzardo</t>
   </si>
   <si>
-    <t>6-7</t>
-  </si>
-  <si>
     <t>Mason Fluharty</t>
   </si>
   <si>
-    <t>Toronto Blue Jays @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>Brad Lord</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Freddy Peralta</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Trevor Rogers</t>
-  </si>
-  <si>
-    <t>Sean Manaea</t>
-  </si>
-  <si>
-    <t>New York Mets @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>Troy Melton</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Noah Cameron</t>
-  </si>
-  <si>
     <t>J.T. Ginn</t>
   </si>
   <si>
-    <t>Athletics @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Hayden Wesneski</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Joey Cantillo</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Tanner Gordon</t>
-  </si>
-  <si>
-    <t>Nick Lodolo</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Eduardo Rodriguez</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Yoshinobu Yamamoto</t>
-  </si>
-  <si>
-    <t>Matthew Boyd</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Emerson Hancock</t>
-  </si>
-  <si>
-    <t>Jesus Luzardo</t>
-  </si>
-  <si>
-    <t>JT Ginn</t>
-  </si>
-  <si>
-    <t>Randy Vasquez</t>
+    <t>Randy Vásquez</t>
   </si>
 </sst>
 </file>
@@ -679,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM33"/>
+  <dimension ref="A1:AM34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -812,25 +815,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="D2">
-        <v>-114</v>
+        <v>-125</v>
       </c>
       <c r="E2">
-        <v>-109</v>
+        <v>123</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823746</v>
+        <v>823420</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -842,43 +845,43 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.3061</v>
+        <v>0.2311</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P2">
-        <v>4.02</v>
+        <v>4.24</v>
       </c>
       <c r="Q2">
-        <v>0.3717</v>
+        <v>0.2261</v>
       </c>
       <c r="R2">
-        <v>0.361</v>
+        <v>0.365</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2301</v>
+        <v>0.163</v>
       </c>
       <c r="U2">
-        <v>0.2196</v>
+        <v>0.1638</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2211</v>
+        <v>0.2216</v>
       </c>
       <c r="X2">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y2">
-        <v>0.9358</v>
+        <v>0.922</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -887,22 +890,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>7.33</v>
+        <v>3.37</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.3298</v>
+        <v>0.2293</v>
       </c>
       <c r="AG2">
-        <v>1.014</v>
+        <v>0.7314</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>7.33</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -913,73 +916,31 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E3">
-        <v>-142</v>
+        <v>-130</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3">
-        <v>823746</v>
+      <c r="G3" t="s">
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L3">
         <v>6</v>
       </c>
-      <c r="M3">
-        <v>0.3934</v>
-      </c>
-      <c r="N3">
-        <v>5</v>
-      </c>
-      <c r="O3">
-        <v>110</v>
-      </c>
-      <c r="P3">
-        <v>3.79</v>
-      </c>
-      <c r="Q3">
-        <v>0.3909</v>
-      </c>
-      <c r="R3">
-        <v>0.355</v>
-      </c>
       <c r="S3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3">
-        <v>0.235</v>
-      </c>
-      <c r="U3">
-        <v>0.2294</v>
-      </c>
-      <c r="V3">
-        <v>9</v>
-      </c>
-      <c r="W3">
-        <v>0.2201</v>
-      </c>
-      <c r="X3">
-        <v>0.2269</v>
-      </c>
-      <c r="Y3">
-        <v>1.0407</v>
+        <v>44</v>
+      </c>
+      <c r="V3" t="s">
+        <v>44</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -987,23 +948,8 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
-      <c r="AD3">
-        <v>9.68</v>
-      </c>
       <c r="AE3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF3">
-        <v>0.3925</v>
-      </c>
-      <c r="AG3">
-        <v>1.0355</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>9.68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1014,25 +960,25 @@
         <v>47</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D4">
-        <v>-127</v>
+        <v>-111</v>
       </c>
       <c r="E4">
-        <v>110</v>
+        <v>-105</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
       </c>
       <c r="G4">
-        <v>823420</v>
+        <v>823510</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1044,43 +990,43 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.2311</v>
+        <v>0.314</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P4">
-        <v>4.24</v>
+        <v>3.96</v>
       </c>
       <c r="Q4">
-        <v>0.2261</v>
+        <v>0.3894</v>
       </c>
       <c r="R4">
-        <v>0.365</v>
+        <v>0.361</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.163</v>
+        <v>0.214</v>
       </c>
       <c r="U4">
-        <v>0.1638</v>
+        <v>0.193</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2216</v>
+        <v>0.1899</v>
       </c>
       <c r="X4">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y4">
-        <v>0.922</v>
+        <v>0.98</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1089,22 +1035,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.31</v>
+        <v>7.43</v>
       </c>
       <c r="AE4" t="s">
         <v>49</v>
       </c>
       <c r="AF4">
-        <v>0.2293</v>
+        <v>0.3412</v>
       </c>
       <c r="AG4">
-        <v>0.7183</v>
+        <v>0.9601</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.31</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1114,65 +1060,74 @@
       <c r="B5" t="s">
         <v>50</v>
       </c>
+      <c r="C5">
+        <v>5.5</v>
+      </c>
+      <c r="D5">
+        <v>-102</v>
+      </c>
+      <c r="E5">
+        <v>-104</v>
+      </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5">
-        <v>823420</v>
+        <v>824721</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
+        <v>5.8</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>6</v>
       </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
       <c r="M5">
-        <v>0.2979</v>
+        <v>0.2183</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="P5">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="Q5">
-        <v>0.3043</v>
+        <v>0.2109</v>
       </c>
       <c r="R5">
-        <v>0.408</v>
+        <v>0.39</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2205</v>
+        <v>0.2111</v>
       </c>
       <c r="U5">
-        <v>0.1899</v>
+        <v>0.2135</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.1826</v>
+        <v>0.2042</v>
       </c>
       <c r="X5">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y5">
-        <v>0.9461</v>
+        <v>0.9508</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1181,22 +1136,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.86</v>
+        <v>4.52</v>
       </c>
       <c r="AE5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.3005</v>
+        <v>0.2154</v>
       </c>
       <c r="AG5">
-        <v>0.9715</v>
+        <v>0.9474</v>
       </c>
       <c r="AH5">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>7.26</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1206,65 +1161,74 @@
       <c r="B6" t="s">
         <v>52</v>
       </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+      <c r="D6">
+        <v>112</v>
+      </c>
+      <c r="E6">
+        <v>-125</v>
+      </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>823510</v>
+        <v>824721</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I6">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>0.2629</v>
+        <v>0.1964</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="P6">
-        <v>4.18</v>
+        <v>4.03</v>
       </c>
       <c r="Q6">
-        <v>0.2353</v>
+        <v>0.2049</v>
       </c>
       <c r="R6">
-        <v>0.078</v>
+        <v>0.379</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2789</v>
+        <v>0.1933</v>
       </c>
       <c r="U6">
-        <v>0.2767</v>
+        <v>0.1976</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2489</v>
+        <v>0.2153</v>
       </c>
       <c r="X6">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y6">
-        <v>1.0045</v>
+        <v>0.9943</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1273,22 +1237,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>1.64</v>
+        <v>4.38</v>
       </c>
       <c r="AE6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2607</v>
+        <v>0.1996</v>
       </c>
       <c r="AG6">
-        <v>1.229</v>
+        <v>0.8675</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>1.64</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1296,76 +1260,76 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7">
+        <v>2.5</v>
+      </c>
+      <c r="D7">
+        <v>-105</v>
+      </c>
+      <c r="E7">
+        <v>-105</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>823830</v>
+      </c>
+      <c r="H7" t="s">
         <v>55</v>
       </c>
-      <c r="C7">
-        <v>6.5</v>
-      </c>
-      <c r="D7">
-        <v>-111</v>
-      </c>
-      <c r="E7">
-        <v>-108</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>823510</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
       <c r="I7">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>0.314</v>
+        <v>0.2119</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="P7">
-        <v>3.96</v>
+        <v>4.32</v>
       </c>
       <c r="Q7">
-        <v>0.3894</v>
+        <v>0.2069</v>
       </c>
       <c r="R7">
-        <v>0.361</v>
+        <v>0.127</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.214</v>
+        <v>0.2444</v>
       </c>
       <c r="U7">
-        <v>0.193</v>
+        <v>0.2296</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.1899</v>
+        <v>0.2126</v>
       </c>
       <c r="X7">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y7">
-        <v>0.98</v>
+        <v>0.8899</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1374,22 +1338,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>7.3</v>
+        <v>1.68</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.3412</v>
+        <v>0.2113</v>
       </c>
       <c r="AG7">
-        <v>0.9429</v>
+        <v>1.0968</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>7.3</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1400,25 +1364,25 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>-105</v>
+        <v>-154</v>
       </c>
       <c r="E8">
-        <v>-108</v>
+        <v>135</v>
       </c>
       <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>823830</v>
+      </c>
+      <c r="H8" t="s">
         <v>57</v>
       </c>
-      <c r="G8">
-        <v>824721</v>
-      </c>
-      <c r="H8" t="s">
-        <v>42</v>
-      </c>
       <c r="I8">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1430,43 +1394,43 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1964</v>
+        <v>0.2068</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="P8">
-        <v>4.03</v>
+        <v>4.42</v>
       </c>
       <c r="Q8">
-        <v>0.2049</v>
+        <v>0.2222</v>
       </c>
       <c r="R8">
-        <v>0.379</v>
+        <v>0.331</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.1933</v>
+        <v>0.2071</v>
       </c>
       <c r="U8">
-        <v>0.1976</v>
+        <v>0.2083</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2153</v>
+        <v>0.2085</v>
       </c>
       <c r="X8">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y8">
-        <v>0.9943</v>
+        <v>0.9397</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1475,22 +1439,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.3</v>
+        <v>3.29</v>
       </c>
       <c r="AE8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1996</v>
+        <v>0.2119</v>
       </c>
       <c r="AG8">
-        <v>0.8519</v>
+        <v>0.9293</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.3</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1504,22 +1468,22 @@
         <v>5.5</v>
       </c>
       <c r="D9">
-        <v>-104</v>
+        <v>120</v>
       </c>
       <c r="E9">
-        <v>-116</v>
+        <v>-146</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G9">
-        <v>824721</v>
+        <v>824800</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1528,46 +1492,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>0.2183</v>
+        <v>0.2147</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="P9">
-        <v>4.04</v>
+        <v>4.48</v>
       </c>
       <c r="Q9">
-        <v>0.2109</v>
+        <v>0.1776</v>
       </c>
       <c r="R9">
-        <v>0.39</v>
+        <v>0.349</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2111</v>
+        <v>0.266</v>
       </c>
       <c r="U9">
-        <v>0.2135</v>
+        <v>0.2421</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2042</v>
+        <v>0.2383</v>
       </c>
       <c r="X9">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y9">
-        <v>0.9508</v>
+        <v>1.0527</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1576,22 +1540,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.44</v>
+        <v>5.81</v>
       </c>
       <c r="AE9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.2154</v>
+        <v>0.2017</v>
       </c>
       <c r="AG9">
-        <v>0.9304</v>
+        <v>1.1935</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.44</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1599,31 +1563,31 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="D10">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="E10">
         <v>-110</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
-        <v>823830</v>
+        <v>824800</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1632,43 +1596,43 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>0.2119</v>
+        <v>0.2042</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="P10">
-        <v>4.32</v>
+        <v>4.21</v>
       </c>
       <c r="Q10">
-        <v>0.2069</v>
+        <v>0.2583</v>
       </c>
       <c r="R10">
-        <v>0.127</v>
+        <v>0.375</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2444</v>
+        <v>0.1581</v>
       </c>
       <c r="U10">
-        <v>0.2296</v>
+        <v>0.1607</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2126</v>
+        <v>0.1849</v>
       </c>
       <c r="X10">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y10">
-        <v>0.8899</v>
+        <v>0.88</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1677,22 +1641,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>1.65</v>
+        <v>3.22</v>
       </c>
       <c r="AE10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2113</v>
+        <v>0.2245</v>
       </c>
       <c r="AG10">
-        <v>1.0771</v>
+        <v>0.7093</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.65</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1703,25 +1667,25 @@
         <v>61</v>
       </c>
       <c r="C11">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D11">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E11">
-        <v>-152</v>
+        <v>-137</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G11">
-        <v>823830</v>
+        <v>824559</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1730,46 +1694,46 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>0.2068</v>
+        <v>0.2697</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="P11">
-        <v>4.42</v>
+        <v>4.08</v>
       </c>
       <c r="Q11">
-        <v>0.2222</v>
+        <v>0.3009</v>
       </c>
       <c r="R11">
-        <v>0.331</v>
+        <v>0.361</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2071</v>
+        <v>0.2512</v>
       </c>
       <c r="U11">
-        <v>0.2083</v>
+        <v>0.2436</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2085</v>
+        <v>0.2245</v>
       </c>
       <c r="X11">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y11">
-        <v>0.9397</v>
+        <v>0.9737</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1778,22 +1742,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.23</v>
+        <v>6.89</v>
       </c>
       <c r="AE11" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="AF11">
-        <v>0.2119</v>
+        <v>0.281</v>
       </c>
       <c r="AG11">
-        <v>0.9126</v>
+        <v>1.1274</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM11">
-        <v>3.23</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1801,28 +1765,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <v>5.5</v>
       </c>
       <c r="D12">
-        <v>112</v>
+        <v>-138</v>
       </c>
       <c r="E12">
-        <v>-133</v>
+        <v>120</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G12">
-        <v>824800</v>
+        <v>824559</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1834,43 +1798,43 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>0.2147</v>
+        <v>0.2349</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="P12">
-        <v>4.48</v>
+        <v>4.33</v>
       </c>
       <c r="Q12">
-        <v>0.1776</v>
+        <v>0.25</v>
       </c>
       <c r="R12">
-        <v>0.349</v>
+        <v>0.39</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.266</v>
+        <v>0.2529</v>
       </c>
       <c r="U12">
-        <v>0.2421</v>
+        <v>0.2556</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2383</v>
+        <v>0.2467</v>
       </c>
       <c r="X12">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y12">
-        <v>1.0527</v>
+        <v>1.1</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1879,22 +1843,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>5.71</v>
+        <v>7.38</v>
       </c>
       <c r="AE12" t="s">
         <v>49</v>
       </c>
       <c r="AF12">
-        <v>0.2017</v>
+        <v>0.2408</v>
       </c>
       <c r="AG12">
-        <v>1.1721</v>
+        <v>1.1346</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>5.71</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1908,22 +1872,22 @@
         <v>4.5</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="E13">
-        <v>-115</v>
+        <v>102</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G13">
-        <v>824800</v>
+        <v>824152</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1935,43 +1899,43 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>0.2042</v>
+        <v>0.1895</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="P13">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="Q13">
-        <v>0.2583</v>
+        <v>0.1895</v>
       </c>
       <c r="R13">
-        <v>0.375</v>
+        <v>0.322</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.1581</v>
+        <v>0.1949</v>
       </c>
       <c r="U13">
-        <v>0.1607</v>
+        <v>0.1897</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.1849</v>
+        <v>0.2117</v>
       </c>
       <c r="X13">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y13">
-        <v>0.88</v>
+        <v>1.0194</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1980,22 +1944,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.16</v>
+        <v>4.01</v>
       </c>
       <c r="AE13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2245</v>
+        <v>0.1895</v>
       </c>
       <c r="AG13">
-        <v>0.6966</v>
+        <v>0.8748</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>3.16</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2003,76 +1967,34 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14">
+        <v>4.5</v>
+      </c>
+      <c r="D14">
+        <v>-103</v>
+      </c>
+      <c r="E14">
+        <v>-102</v>
+      </c>
+      <c r="F14" t="s">
         <v>66</v>
       </c>
-      <c r="C14">
-        <v>5.5</v>
-      </c>
-      <c r="D14">
-        <v>-132</v>
-      </c>
-      <c r="E14">
-        <v>115</v>
-      </c>
-      <c r="F14" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14">
-        <v>824559</v>
+      <c r="G14" t="s">
+        <v>44</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14">
-        <v>5.7</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
-      <c r="M14">
-        <v>0.2349</v>
-      </c>
-      <c r="N14">
-        <v>5</v>
-      </c>
-      <c r="O14">
-        <v>128</v>
-      </c>
-      <c r="P14">
-        <v>4.33</v>
-      </c>
-      <c r="Q14">
-        <v>0.25</v>
-      </c>
-      <c r="R14">
-        <v>0.39</v>
-      </c>
       <c r="S14" t="s">
-        <v>43</v>
-      </c>
-      <c r="T14">
-        <v>0.2529</v>
-      </c>
-      <c r="U14">
-        <v>0.2556</v>
-      </c>
-      <c r="V14">
-        <v>9</v>
-      </c>
-      <c r="W14">
-        <v>0.2467</v>
-      </c>
-      <c r="X14">
-        <v>0.2269</v>
-      </c>
-      <c r="Y14">
-        <v>1.1</v>
+        <v>44</v>
+      </c>
+      <c r="V14" t="s">
+        <v>44</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2080,23 +2002,8 @@
       <c r="AC14" t="s">
         <v>44</v>
       </c>
-      <c r="AD14">
-        <v>7.25</v>
-      </c>
       <c r="AE14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF14">
-        <v>0.2408</v>
-      </c>
-      <c r="AG14">
-        <v>1.1143</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>7.25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2107,25 +2014,25 @@
         <v>68</v>
       </c>
       <c r="C15">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D15">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E15">
-        <v>-135</v>
+        <v>-137</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G15">
-        <v>824559</v>
+        <v>824072</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2134,46 +2041,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2697</v>
+        <v>0.2172</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="P15">
-        <v>4.08</v>
+        <v>4.19</v>
       </c>
       <c r="Q15">
-        <v>0.3009</v>
+        <v>0.203</v>
       </c>
       <c r="R15">
-        <v>0.361</v>
+        <v>0.399</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2512</v>
+        <v>0.2058</v>
       </c>
       <c r="U15">
-        <v>0.2436</v>
+        <v>0.2085</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2245</v>
+        <v>0.2305</v>
       </c>
       <c r="X15">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y15">
-        <v>0.9737</v>
+        <v>1.0031</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2182,22 +2089,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>6.77</v>
+        <v>4.69</v>
       </c>
       <c r="AE15" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.281</v>
+        <v>0.2116</v>
       </c>
       <c r="AG15">
-        <v>1.1072</v>
+        <v>0.9234</v>
       </c>
       <c r="AH15">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>7.17</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2205,19 +2112,19 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16">
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="E16">
-        <v>-118</v>
+        <v>-120</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G16">
         <v>824072</v>
@@ -2271,7 +2178,7 @@
         <v>0.2092</v>
       </c>
       <c r="X16">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y16">
         <v>0.9306</v>
@@ -2283,22 +2190,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="AE16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF16">
         <v>0.2125</v>
       </c>
       <c r="AG16">
-        <v>0.847</v>
+        <v>0.8624</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2309,25 +2216,25 @@
         <v>71</v>
       </c>
       <c r="C17">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D17">
-        <v>110</v>
+        <v>-150</v>
       </c>
       <c r="E17">
-        <v>-136</v>
+        <v>118</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G17">
-        <v>824072</v>
+        <v>822857</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2339,43 +2246,43 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.2172</v>
+        <v>0.258</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="P17">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="Q17">
-        <v>0.203</v>
+        <v>0.2623</v>
       </c>
       <c r="R17">
-        <v>0.399</v>
+        <v>0.379</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2058</v>
+        <v>0.3053</v>
       </c>
       <c r="U17">
-        <v>0.2085</v>
+        <v>0.2866</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2305</v>
+        <v>0.2537</v>
       </c>
       <c r="X17">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y17">
-        <v>1.0031</v>
+        <v>1.1182</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2384,22 +2291,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.61</v>
+        <v>9.13</v>
       </c>
       <c r="AE17" t="s">
         <v>49</v>
       </c>
       <c r="AF17">
-        <v>0.2116</v>
+        <v>0.2596</v>
       </c>
       <c r="AG17">
-        <v>0.9069</v>
+        <v>1.3698</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.61</v>
+        <v>9.13</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2407,19 +2314,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18">
+        <v>6.5</v>
+      </c>
+      <c r="D18">
+        <v>105</v>
+      </c>
+      <c r="E18">
+        <v>-116</v>
+      </c>
+      <c r="F18" t="s">
         <v>72</v>
       </c>
-      <c r="F18" t="s">
-        <v>73</v>
-      </c>
       <c r="G18">
-        <v>824152</v>
+        <v>822857</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2428,46 +2344,46 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2139</v>
+        <v>0.2884</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="P18">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="Q18">
-        <v>0.2295</v>
+        <v>0.3524</v>
       </c>
       <c r="R18">
-        <v>0.379</v>
+        <v>0.344</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2096</v>
+        <v>0.2445</v>
       </c>
       <c r="U18">
-        <v>0.1755</v>
+        <v>0.2455</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2184</v>
+        <v>0.2456</v>
       </c>
       <c r="X18">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y18">
-        <v>0.8828</v>
+        <v>1.0791</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2476,22 +2392,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.1</v>
+        <v>8.51</v>
       </c>
       <c r="AE18" t="s">
         <v>49</v>
       </c>
       <c r="AF18">
-        <v>0.2198</v>
+        <v>0.3104</v>
       </c>
       <c r="AG18">
-        <v>0.9237</v>
+        <v>1.097</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.1</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2502,25 +2418,25 @@
         <v>74</v>
       </c>
       <c r="C19">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D19">
-        <v>-114</v>
+        <v>140</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>-162</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G19">
-        <v>824152</v>
+        <v>824317</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2529,46 +2445,46 @@
         <v>0</v>
       </c>
       <c r="L19">
+        <v>6</v>
+      </c>
+      <c r="M19">
+        <v>0.1987</v>
+      </c>
+      <c r="N19">
         <v>5</v>
       </c>
-      <c r="M19">
-        <v>0.1895</v>
-      </c>
-      <c r="N19">
-        <v>4</v>
-      </c>
       <c r="O19">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="P19">
-        <v>4.19</v>
+        <v>4.37</v>
       </c>
       <c r="Q19">
-        <v>0.1895</v>
+        <v>0.1574</v>
       </c>
       <c r="R19">
-        <v>0.322</v>
+        <v>0.351</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.1949</v>
+        <v>0.1697</v>
       </c>
       <c r="U19">
-        <v>0.1897</v>
+        <v>0.1722</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2117</v>
+        <v>0.2149</v>
       </c>
       <c r="X19">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y19">
-        <v>1.0194</v>
+        <v>0.88</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2577,22 +2493,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>3.94</v>
+        <v>2.48</v>
       </c>
       <c r="AE19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.1895</v>
+        <v>0.1842</v>
       </c>
       <c r="AG19">
-        <v>0.8591</v>
+        <v>0.7614</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>3.94</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2600,28 +2516,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20">
+        <v>5.5</v>
+      </c>
+      <c r="D20">
+        <v>-115</v>
+      </c>
+      <c r="E20">
+        <v>-105</v>
+      </c>
+      <c r="F20" t="s">
         <v>75</v>
       </c>
-      <c r="C20">
-        <v>6.5</v>
-      </c>
-      <c r="D20">
-        <v>102</v>
-      </c>
-      <c r="E20">
-        <v>-120</v>
-      </c>
-      <c r="F20" t="s">
-        <v>76</v>
-      </c>
       <c r="G20">
-        <v>822857</v>
+        <v>824317</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2633,43 +2549,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2884</v>
+        <v>0.2565</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="P20">
-        <v>4.05</v>
+        <v>4.31</v>
       </c>
       <c r="Q20">
-        <v>0.3524</v>
+        <v>0.3103</v>
       </c>
       <c r="R20">
-        <v>0.344</v>
+        <v>0.303</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2445</v>
+        <v>0.2761</v>
       </c>
       <c r="U20">
-        <v>0.2455</v>
+        <v>0.2214</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2456</v>
+        <v>0.2484</v>
       </c>
       <c r="X20">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y20">
-        <v>1.0791</v>
+        <v>1.0239</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2678,22 +2594,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>8.36</v>
+        <v>7.21</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF20">
-        <v>0.3104</v>
+        <v>0.2728</v>
       </c>
       <c r="AG20">
-        <v>1.0773</v>
+        <v>1.2391</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>8.36</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2704,25 +2620,25 @@
         <v>77</v>
       </c>
       <c r="C21">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D21">
-        <v>-120</v>
+        <v>126</v>
       </c>
       <c r="E21">
-        <v>-103</v>
+        <v>-146</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G21">
-        <v>822857</v>
+        <v>825045</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2734,43 +2650,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.258</v>
+        <v>0.1729</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="P21">
-        <v>4.27</v>
+        <v>4.1</v>
       </c>
       <c r="Q21">
-        <v>0.2623</v>
+        <v>0.1778</v>
       </c>
       <c r="R21">
-        <v>0.379</v>
+        <v>0.403</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.3053</v>
+        <v>0.2946</v>
       </c>
       <c r="U21">
-        <v>0.2866</v>
+        <v>0.2815</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2537</v>
+        <v>0.2527</v>
       </c>
       <c r="X21">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y21">
-        <v>1.1182</v>
+        <v>1.113</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2779,22 +2695,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>8.97</v>
+        <v>6.31</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="AF21">
-        <v>0.2596</v>
+        <v>0.1749</v>
       </c>
       <c r="AG21">
-        <v>1.3453</v>
+        <v>1.3221</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM21">
-        <v>8.97</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2802,28 +2718,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22">
+        <v>3.5</v>
+      </c>
+      <c r="D22">
+        <v>-118</v>
+      </c>
+      <c r="E22">
+        <v>105</v>
+      </c>
+      <c r="F22" t="s">
         <v>78</v>
       </c>
-      <c r="C22">
-        <v>5.5</v>
-      </c>
-      <c r="D22">
-        <v>-115</v>
-      </c>
-      <c r="E22">
-        <v>-103</v>
-      </c>
-      <c r="F22" t="s">
-        <v>79</v>
-      </c>
       <c r="G22">
-        <v>824317</v>
+        <v>825045</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2835,43 +2751,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2565</v>
+        <v>0.1804</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="P22">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
       <c r="Q22">
-        <v>0.3103</v>
+        <v>0.181</v>
       </c>
       <c r="R22">
-        <v>0.303</v>
+        <v>0.344</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2761</v>
+        <v>0.2135</v>
       </c>
       <c r="U22">
-        <v>0.2214</v>
+        <v>0.1753</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2484</v>
+        <v>0.1766</v>
       </c>
       <c r="X22">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y22">
-        <v>1.0239</v>
+        <v>0.88</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2880,22 +2796,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>7.09</v>
+        <v>3.44</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2728</v>
+        <v>0.1806</v>
       </c>
       <c r="AG22">
-        <v>1.2169</v>
+        <v>0.958</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>7.09</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2906,25 +2822,25 @@
         <v>80</v>
       </c>
       <c r="C23">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="D23">
-        <v>-165</v>
+        <v>120</v>
       </c>
       <c r="E23">
-        <v>138</v>
+        <v>-148</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G23">
-        <v>824317</v>
+        <v>823262</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2933,46 +2849,46 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>0.1987</v>
+        <v>0.2461</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P23">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="Q23">
-        <v>0.1574</v>
+        <v>0.2661</v>
       </c>
       <c r="R23">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
       </c>
       <c r="T23">
-        <v>0.1697</v>
+        <v>0.1954</v>
       </c>
       <c r="U23">
-        <v>0.1722</v>
+        <v>0.1949</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2149</v>
+        <v>0.2218</v>
       </c>
       <c r="X23">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y23">
-        <v>0.88</v>
+        <v>1.0141</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2981,22 +2897,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>2.44</v>
+        <v>5.06</v>
       </c>
       <c r="AE23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.1842</v>
+        <v>0.2531</v>
       </c>
       <c r="AG23">
-        <v>0.7477</v>
+        <v>0.8769</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>2.44</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3004,76 +2920,34 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24">
+        <v>2.5</v>
+      </c>
+      <c r="D24">
+        <v>-160</v>
+      </c>
+      <c r="E24">
+        <v>127</v>
+      </c>
+      <c r="F24" t="s">
         <v>81</v>
       </c>
-      <c r="C24">
-        <v>3.5</v>
-      </c>
-      <c r="D24">
-        <v>-122</v>
-      </c>
-      <c r="E24">
-        <v>105</v>
-      </c>
-      <c r="F24" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24">
-        <v>825045</v>
+      <c r="G24" t="s">
+        <v>44</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24">
-        <v>5.1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L24">
-        <v>6</v>
-      </c>
-      <c r="M24">
-        <v>0.1804</v>
-      </c>
-      <c r="N24">
-        <v>5</v>
-      </c>
-      <c r="O24">
-        <v>105</v>
-      </c>
-      <c r="P24">
-        <v>4.41</v>
-      </c>
-      <c r="Q24">
-        <v>0.181</v>
-      </c>
-      <c r="R24">
-        <v>0.344</v>
+        <v>3</v>
       </c>
       <c r="S24" t="s">
-        <v>43</v>
-      </c>
-      <c r="T24">
-        <v>0.2135</v>
-      </c>
-      <c r="U24">
-        <v>0.1753</v>
-      </c>
-      <c r="V24">
-        <v>9</v>
-      </c>
-      <c r="W24">
-        <v>0.1766</v>
-      </c>
-      <c r="X24">
-        <v>0.2269</v>
-      </c>
-      <c r="Y24">
-        <v>0.88</v>
+        <v>44</v>
+      </c>
+      <c r="V24" t="s">
+        <v>44</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3081,23 +2955,8 @@
       <c r="AC24" t="s">
         <v>44</v>
       </c>
-      <c r="AD24">
-        <v>3.37</v>
-      </c>
       <c r="AE24" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF24">
-        <v>0.1806</v>
-      </c>
-      <c r="AG24">
-        <v>0.9408</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>3.37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3108,25 +2967,25 @@
         <v>83</v>
       </c>
       <c r="C25">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D25">
-        <v>116</v>
+        <v>-135</v>
       </c>
       <c r="E25">
-        <v>-139</v>
+        <v>110</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G25">
-        <v>825045</v>
+        <v>823101</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3138,43 +2997,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.1729</v>
+        <v>0.1921</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="P25">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="Q25">
-        <v>0.1778</v>
+        <v>0.1241</v>
       </c>
       <c r="R25">
-        <v>0.403</v>
+        <v>0.407</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2946</v>
+        <v>0.2237</v>
       </c>
       <c r="U25">
-        <v>0.2815</v>
+        <v>0.2069</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2527</v>
+        <v>0.2425</v>
       </c>
       <c r="X25">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y25">
-        <v>1.113</v>
+        <v>0.958</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3183,22 +3042,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.2</v>
+        <v>3.73</v>
       </c>
       <c r="AE25" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.1749</v>
+        <v>0.1644</v>
       </c>
       <c r="AG25">
-        <v>1.2984</v>
+        <v>1.0038</v>
       </c>
       <c r="AH25">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>6.6</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3206,28 +3065,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26">
+        <v>4.5</v>
+      </c>
+      <c r="D26">
+        <v>-155</v>
+      </c>
+      <c r="E26">
+        <v>126</v>
+      </c>
+      <c r="F26" t="s">
         <v>84</v>
       </c>
-      <c r="C26">
-        <v>5.5</v>
-      </c>
-      <c r="D26">
-        <v>126</v>
-      </c>
-      <c r="E26">
-        <v>-143</v>
-      </c>
-      <c r="F26" t="s">
-        <v>85</v>
-      </c>
       <c r="G26">
-        <v>823262</v>
+        <v>823101</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3239,43 +3098,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2461</v>
+        <v>0.2306</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="P26">
-        <v>4.36</v>
+        <v>4.03</v>
       </c>
       <c r="Q26">
-        <v>0.2661</v>
+        <v>0.1984</v>
       </c>
       <c r="R26">
-        <v>0.353</v>
+        <v>0.387</v>
       </c>
       <c r="S26" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="T26">
-        <v>0.1954</v>
+        <v>0.2255</v>
       </c>
       <c r="U26">
-        <v>0.1949</v>
+        <v>0.2231</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2218</v>
+        <v>0.2183</v>
       </c>
       <c r="X26">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y26">
-        <v>1.0141</v>
+        <v>0.9568</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3284,22 +3143,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.97</v>
+        <v>4.74</v>
       </c>
       <c r="AE26" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF26">
-        <v>0.2531</v>
+        <v>0.2182</v>
       </c>
       <c r="AG26">
-        <v>0.8612</v>
+        <v>1.0119</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.97</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3307,19 +3166,19 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="D27">
         <v>125</v>
       </c>
       <c r="E27">
-        <v>-143</v>
+        <v>-155</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G27">
         <v>823911</v>
@@ -3328,7 +3187,7 @@
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3340,43 +3199,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.2045</v>
+        <v>0.2446</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="P27">
-        <v>4.35</v>
+        <v>3.83</v>
       </c>
       <c r="Q27">
-        <v>0.215</v>
+        <v>0.229</v>
       </c>
       <c r="R27">
-        <v>0.349</v>
+        <v>0.396</v>
       </c>
       <c r="S27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T27">
-        <v>0.3045</v>
+        <v>0.2148</v>
       </c>
       <c r="U27">
-        <v>0.2034</v>
+        <v>0.2153</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2057</v>
+        <v>0.2346</v>
       </c>
       <c r="X27">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y27">
-        <v>1.0045</v>
+        <v>1.0324</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3385,22 +3244,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>6.16</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="AF27">
-        <v>0.2082</v>
+        <v>0.2384</v>
       </c>
       <c r="AG27">
-        <v>1.3418</v>
+        <v>0.9637</v>
       </c>
       <c r="AH27">
         <v>0.4</v>
       </c>
       <c r="AM27">
-        <v>6.56</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3411,16 +3270,16 @@
         <v>89</v>
       </c>
       <c r="C28">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="D28">
         <v>125</v>
       </c>
       <c r="E28">
-        <v>-143</v>
+        <v>-147</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G28">
         <v>823911</v>
@@ -3429,7 +3288,7 @@
         <v>42</v>
       </c>
       <c r="I28">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3441,43 +3300,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.2446</v>
+        <v>0.2045</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="P28">
-        <v>3.83</v>
+        <v>4.35</v>
       </c>
       <c r="Q28">
-        <v>0.229</v>
+        <v>0.215</v>
       </c>
       <c r="R28">
-        <v>0.396</v>
+        <v>0.349</v>
       </c>
       <c r="S28" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="T28">
-        <v>0.2148</v>
+        <v>0.1922</v>
       </c>
       <c r="U28">
-        <v>0.2153</v>
+        <v>0.1947</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2346</v>
+        <v>0.2057</v>
       </c>
       <c r="X28">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y28">
-        <v>1.0324</v>
+        <v>0.9717</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3486,22 +3345,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>5.89</v>
+        <v>3.83</v>
       </c>
       <c r="AE28" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.2384</v>
+        <v>0.2082</v>
       </c>
       <c r="AG28">
-        <v>0.9464</v>
+        <v>0.8625</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>5.89</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3512,25 +3371,25 @@
         <v>90</v>
       </c>
       <c r="C29">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="D29">
-        <v>-135</v>
+        <v>-114</v>
       </c>
       <c r="E29">
-        <v>108</v>
+        <v>-109</v>
       </c>
       <c r="F29" t="s">
         <v>91</v>
       </c>
       <c r="G29">
-        <v>823101</v>
+        <v>823746</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3542,43 +3401,43 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>0.1921</v>
+        <v>0.3063</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="P29">
-        <v>4.16</v>
+        <v>4.01</v>
       </c>
       <c r="Q29">
-        <v>0.1241</v>
+        <v>0.3707</v>
       </c>
       <c r="R29">
-        <v>0.407</v>
+        <v>0.367</v>
       </c>
       <c r="S29" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.2335</v>
+        <v>0.2301</v>
       </c>
       <c r="U29">
-        <v>0.2096</v>
+        <v>0.2196</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2425</v>
+        <v>0.2211</v>
       </c>
       <c r="X29">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y29">
-        <v>0.9904</v>
+        <v>0.9358</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3587,22 +3446,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>3.95</v>
+        <v>7.51</v>
       </c>
       <c r="AE29" t="s">
         <v>49</v>
       </c>
       <c r="AF29">
-        <v>0.1644</v>
+        <v>0.3299</v>
       </c>
       <c r="AG29">
-        <v>1.0288</v>
+        <v>1.0325</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>3.95</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3613,25 +3472,25 @@
         <v>92</v>
       </c>
       <c r="C30">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="D30">
-        <v>-157</v>
+        <v>120</v>
       </c>
       <c r="E30">
-        <v>126</v>
+        <v>-142</v>
       </c>
       <c r="F30" t="s">
         <v>91</v>
       </c>
       <c r="G30">
-        <v>823101</v>
+        <v>823746</v>
       </c>
       <c r="H30" t="s">
         <v>42</v>
       </c>
       <c r="I30">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3643,43 +3502,43 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>0.2306</v>
+        <v>0.3927</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="P30">
-        <v>4.03</v>
+        <v>3.79</v>
       </c>
       <c r="Q30">
-        <v>0.1984</v>
+        <v>0.3874</v>
       </c>
       <c r="R30">
-        <v>0.387</v>
+        <v>0.357</v>
       </c>
       <c r="S30" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="T30">
-        <v>0.2255</v>
+        <v>0.235</v>
       </c>
       <c r="U30">
-        <v>0.2231</v>
+        <v>0.2294</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2183</v>
+        <v>0.2201</v>
       </c>
       <c r="X30">
-        <v>0.2269</v>
+        <v>0.2229</v>
       </c>
       <c r="Y30">
-        <v>0.9568</v>
+        <v>1.0407</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3688,22 +3547,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>4.65</v>
+        <v>9.83</v>
       </c>
       <c r="AE30" t="s">
         <v>49</v>
       </c>
       <c r="AF30">
-        <v>0.2182</v>
+        <v>0.3908</v>
       </c>
       <c r="AG30">
-        <v>0.9938</v>
+        <v>1.0544</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>4.65</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3713,32 +3572,65 @@
       <c r="B31" t="s">
         <v>93</v>
       </c>
-      <c r="C31">
-        <v>7.5</v>
-      </c>
-      <c r="D31">
-        <v>115</v>
-      </c>
-      <c r="E31">
-        <v>-125</v>
-      </c>
       <c r="F31" t="s">
-        <v>48</v>
-      </c>
-      <c r="G31" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="G31">
+        <v>823420</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I31">
+        <v>6</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0.2979</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31">
+        <v>138</v>
+      </c>
+      <c r="P31">
+        <v>4.13</v>
+      </c>
+      <c r="Q31">
+        <v>0.3043</v>
+      </c>
+      <c r="R31">
+        <v>0.408</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
-      </c>
-      <c r="V31" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T31">
+        <v>0.2205</v>
+      </c>
+      <c r="U31">
+        <v>0.1899</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.1826</v>
+      </c>
+      <c r="X31">
+        <v>0.2229</v>
+      </c>
+      <c r="Y31">
+        <v>0.9461</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3746,8 +3638,23 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
+      <c r="AD31">
+        <v>6.99</v>
+      </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>63</v>
+      </c>
+      <c r="AF31">
+        <v>0.3005</v>
+      </c>
+      <c r="AG31">
+        <v>0.9892</v>
+      </c>
+      <c r="AH31">
+        <v>0.4</v>
+      </c>
+      <c r="AM31">
+        <v>7.39</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3757,32 +3664,65 @@
       <c r="B32" t="s">
         <v>94</v>
       </c>
-      <c r="C32">
-        <v>4.5</v>
-      </c>
-      <c r="D32">
-        <v>-119</v>
-      </c>
-      <c r="E32">
-        <v>-102</v>
-      </c>
       <c r="F32" t="s">
-        <v>73</v>
-      </c>
-      <c r="G32" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="G32">
+        <v>823510</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="I32">
+        <v>1.2</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0.2629</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32">
+        <v>17</v>
+      </c>
+      <c r="P32">
+        <v>4.18</v>
+      </c>
+      <c r="Q32">
+        <v>0.2353</v>
+      </c>
+      <c r="R32">
+        <v>0.078</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
-      </c>
-      <c r="V32" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T32">
+        <v>0.2789</v>
+      </c>
+      <c r="U32">
+        <v>0.2767</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
+        <v>0.2489</v>
+      </c>
+      <c r="X32">
+        <v>0.2229</v>
+      </c>
+      <c r="Y32">
+        <v>1.0045</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3790,8 +3730,23 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
+      <c r="AD32">
+        <v>1.67</v>
+      </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF32">
+        <v>0.2607</v>
+      </c>
+      <c r="AG32">
+        <v>1.2515</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>1.67</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3801,32 +3756,65 @@
       <c r="B33" t="s">
         <v>95</v>
       </c>
-      <c r="C33">
-        <v>2.5</v>
-      </c>
-      <c r="D33">
-        <v>-160</v>
-      </c>
-      <c r="E33">
-        <v>129</v>
-      </c>
       <c r="F33" t="s">
-        <v>85</v>
-      </c>
-      <c r="G33" t="s">
-        <v>44</v>
+        <v>66</v>
+      </c>
+      <c r="G33">
+        <v>824152</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I33">
+        <v>5.5</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0.2139</v>
+      </c>
+      <c r="N33">
+        <v>5</v>
+      </c>
+      <c r="O33">
+        <v>122</v>
+      </c>
+      <c r="P33">
+        <v>4.19</v>
+      </c>
+      <c r="Q33">
+        <v>0.2295</v>
+      </c>
+      <c r="R33">
+        <v>0.379</v>
       </c>
       <c r="S33" t="s">
-        <v>44</v>
-      </c>
-      <c r="V33" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T33">
+        <v>0.2096</v>
+      </c>
+      <c r="U33">
+        <v>0.1755</v>
+      </c>
+      <c r="V33">
+        <v>9</v>
+      </c>
+      <c r="W33">
+        <v>0.2184</v>
+      </c>
+      <c r="X33">
+        <v>0.2229</v>
+      </c>
+      <c r="Y33">
+        <v>0.8828</v>
       </c>
       <c r="AA33" t="s">
         <v>44</v>
@@ -3834,8 +3822,115 @@
       <c r="AC33" t="s">
         <v>44</v>
       </c>
+      <c r="AD33">
+        <v>4.18</v>
+      </c>
       <c r="AE33" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF33">
+        <v>0.2198</v>
+      </c>
+      <c r="AG33">
+        <v>0.9406</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34">
+        <v>823262</v>
+      </c>
+      <c r="H34" t="s">
+        <v>42</v>
+      </c>
+      <c r="I34">
+        <v>5</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0.1498</v>
+      </c>
+      <c r="N34">
+        <v>5</v>
+      </c>
+      <c r="O34">
+        <v>84</v>
+      </c>
+      <c r="P34">
+        <v>4.27</v>
+      </c>
+      <c r="Q34">
+        <v>0.0357</v>
+      </c>
+      <c r="R34">
+        <v>0.296</v>
+      </c>
+      <c r="S34" t="s">
+        <v>43</v>
+      </c>
+      <c r="T34">
+        <v>0.2023</v>
+      </c>
+      <c r="U34">
+        <v>0.1954</v>
+      </c>
+      <c r="V34">
+        <v>9</v>
+      </c>
+      <c r="W34">
+        <v>0.2099</v>
+      </c>
+      <c r="X34">
+        <v>0.2229</v>
+      </c>
+      <c r="Y34">
+        <v>0.9599</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD34">
+        <v>2.35</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF34">
+        <v>0.1273</v>
+      </c>
+      <c r="AG34">
+        <v>0.9077</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>2.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-21.xlsx
+++ b/data/k-props/2026-08-21.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="96">
   <si>
     <t>date</t>
   </si>
@@ -133,175 +133,172 @@
     <t>08/21/2026</t>
   </si>
   <si>
+    <t>Chris Sale</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Jacob Misiorowski</t>
+  </si>
+  <si>
     <t>Hunter Dobbins</t>
   </si>
   <si>
     <t>St. Louis Cardinals @ Philadelphia Phillies</t>
   </si>
   <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>&lt;6</t>
   </si>
   <si>
+    <t>Jesús Luzardo</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Mason Fluharty</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Cam Schlittler</t>
+  </si>
+  <si>
+    <t>Logan Webb</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Sonny Gray</t>
+  </si>
+  <si>
+    <t>Brad Lord</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Ryan Gusto</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Freddy Peralta</t>
+  </si>
+  <si>
+    <t>Tampa Bay Rays @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Trevor Rogers</t>
+  </si>
+  <si>
+    <t>Sean Manaea</t>
+  </si>
+  <si>
+    <t>New York Mets @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Troy Melton</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>J.T. Ginn</t>
+  </si>
+  <si>
+    <t>Athletics @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Hayden Wesneski</t>
+  </si>
+  <si>
+    <t>Reid Detmers</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>MacKenzie Gore</t>
+  </si>
+  <si>
+    <t>Joey Cantillo</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Tanner Gordon</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Eduardo Rodriguez</t>
+  </si>
+  <si>
+    <t>Connor Prielipp</t>
+  </si>
+  <si>
+    <t>Minnesota Twins @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Randy Vásquez</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Yoshinobu Yamamoto</t>
+  </si>
+  <si>
+    <t>Matthew Boyd</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Seattle Mariners</t>
+  </si>
+  <si>
+    <t>Emerson Hancock</t>
+  </si>
+  <si>
     <t>Jesus Luzardo</t>
   </si>
   <si>
-    <t>Cam Schlittler</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ New York Yankees</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Sonny Gray</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Logan Webb</t>
-  </si>
-  <si>
-    <t>Brad Lord</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Ryan Gusto</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Freddy Peralta</t>
-  </si>
-  <si>
-    <t>Tampa Bay Rays @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Trevor Rogers</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>New York Mets @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Sean Manaea</t>
-  </si>
-  <si>
-    <t>Hayden Wesneski</t>
-  </si>
-  <si>
-    <t>Athletics @ Houston Astros</t>
-  </si>
-  <si>
     <t>JT Ginn</t>
   </si>
   <si>
-    <t>Noah Cameron</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Troy Melton</t>
-  </si>
-  <si>
-    <t>MacKenzie Gore</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Reid Detmers</t>
-  </si>
-  <si>
-    <t>Tanner Gordon</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Joey Cantillo</t>
-  </si>
-  <si>
-    <t>Eduardo Rodriguez</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Nick Lodolo</t>
-  </si>
-  <si>
-    <t>Connor Prielipp</t>
-  </si>
-  <si>
-    <t>Minnesota Twins @ San Diego Padres</t>
-  </si>
-  <si>
     <t>Randy Vasquez</t>
-  </si>
-  <si>
-    <t>Matthew Boyd</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Seattle Mariners</t>
-  </si>
-  <si>
-    <t>Emerson Hancock</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Yoshinobu Yamamoto</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Chris Sale</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Jacob Misiorowski</t>
-  </si>
-  <si>
-    <t>Jesús Luzardo</t>
-  </si>
-  <si>
-    <t>Mason Fluharty</t>
-  </si>
-  <si>
-    <t>J.T. Ginn</t>
-  </si>
-  <si>
-    <t>Randy Vásquez</t>
   </si>
 </sst>
 </file>
@@ -815,25 +812,25 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="D2">
-        <v>-125</v>
+        <v>-114</v>
       </c>
       <c r="E2">
-        <v>123</v>
+        <v>-109</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
       <c r="G2">
-        <v>823420</v>
+        <v>823746</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -845,43 +842,43 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.2311</v>
+        <v>0.3063</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P2">
-        <v>4.24</v>
+        <v>4.01</v>
       </c>
       <c r="Q2">
-        <v>0.2261</v>
+        <v>0.3707</v>
       </c>
       <c r="R2">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.163</v>
+        <v>0.2301</v>
       </c>
       <c r="U2">
-        <v>0.1638</v>
+        <v>0.2196</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2216</v>
+        <v>0.2223</v>
       </c>
       <c r="X2">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y2">
-        <v>0.922</v>
+        <v>0.9358</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -890,22 +887,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.37</v>
+        <v>7.49</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2293</v>
+        <v>0.3299</v>
       </c>
       <c r="AG2">
-        <v>0.7314</v>
+        <v>1.0292</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>3.37</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -916,31 +913,73 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="D3">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>-130</v>
+        <v>-142</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" t="s">
-        <v>44</v>
+      <c r="G3">
+        <v>823746</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
       </c>
       <c r="L3">
         <v>6</v>
       </c>
+      <c r="M3">
+        <v>0.3927</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>111</v>
+      </c>
+      <c r="P3">
+        <v>3.79</v>
+      </c>
+      <c r="Q3">
+        <v>0.3874</v>
+      </c>
+      <c r="R3">
+        <v>0.357</v>
+      </c>
       <c r="S3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T3">
+        <v>0.235</v>
+      </c>
+      <c r="U3">
+        <v>0.2294</v>
+      </c>
+      <c r="V3">
+        <v>9</v>
+      </c>
+      <c r="W3">
+        <v>0.2201</v>
+      </c>
+      <c r="X3">
+        <v>0.2236</v>
+      </c>
+      <c r="Y3">
+        <v>1.0407</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -948,8 +987,23 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
+      <c r="AD3">
+        <v>9.8</v>
+      </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF3">
+        <v>0.3908</v>
+      </c>
+      <c r="AG3">
+        <v>1.051</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>9.8</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -960,25 +1014,25 @@
         <v>47</v>
       </c>
       <c r="C4">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-111</v>
+        <v>-125</v>
       </c>
       <c r="E4">
-        <v>-105</v>
+        <v>123</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
       </c>
       <c r="G4">
-        <v>823510</v>
+        <v>823420</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -990,43 +1044,43 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.314</v>
+        <v>0.2247</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="P4">
-        <v>3.96</v>
+        <v>4.28</v>
       </c>
       <c r="Q4">
-        <v>0.3894</v>
+        <v>0.2264</v>
       </c>
       <c r="R4">
-        <v>0.361</v>
+        <v>0.346</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.214</v>
+        <v>0.163</v>
       </c>
       <c r="U4">
-        <v>0.193</v>
+        <v>0.1638</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.1899</v>
+        <v>0.2216</v>
       </c>
       <c r="X4">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y4">
-        <v>0.98</v>
+        <v>0.922</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1035,22 +1089,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>7.43</v>
+        <v>3.11</v>
       </c>
       <c r="AE4" t="s">
         <v>49</v>
       </c>
       <c r="AF4">
-        <v>0.3412</v>
+        <v>0.2253</v>
       </c>
       <c r="AG4">
-        <v>0.9601</v>
+        <v>0.7291</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>7.43</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1060,26 +1114,17 @@
       <c r="B5" t="s">
         <v>50</v>
       </c>
-      <c r="C5">
-        <v>5.5</v>
-      </c>
-      <c r="D5">
-        <v>-102</v>
-      </c>
-      <c r="E5">
-        <v>-104</v>
-      </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G5">
-        <v>824721</v>
+        <v>823420</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1088,46 +1133,46 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.2183</v>
+        <v>0.2997</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P5">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="Q5">
-        <v>0.2109</v>
+        <v>0.304</v>
       </c>
       <c r="R5">
-        <v>0.39</v>
+        <v>0.385</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2111</v>
+        <v>0.2205</v>
       </c>
       <c r="U5">
-        <v>0.2135</v>
+        <v>0.1899</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2042</v>
+        <v>0.1826</v>
       </c>
       <c r="X5">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y5">
-        <v>0.9508</v>
+        <v>0.9461</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1136,22 +1181,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.52</v>
+        <v>6.86</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF5">
-        <v>0.2154</v>
+        <v>0.3013</v>
       </c>
       <c r="AG5">
-        <v>0.9474</v>
+        <v>0.9861</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM5">
-        <v>4.52</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1161,74 +1206,65 @@
       <c r="B6" t="s">
         <v>52</v>
       </c>
-      <c r="C6">
-        <v>4.5</v>
-      </c>
-      <c r="D6">
-        <v>112</v>
-      </c>
-      <c r="E6">
-        <v>-125</v>
-      </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6">
-        <v>824721</v>
+        <v>823510</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I6">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0.1964</v>
+        <v>0.2581</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O6">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="P6">
-        <v>4.03</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
-        <v>0.2049</v>
+        <v>0.1905</v>
       </c>
       <c r="R6">
-        <v>0.379</v>
+        <v>0.095</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.1933</v>
+        <v>0.2789</v>
       </c>
       <c r="U6">
-        <v>0.1976</v>
+        <v>0.2767</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2153</v>
+        <v>0.2489</v>
       </c>
       <c r="X6">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y6">
-        <v>0.9943</v>
+        <v>1.0045</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1237,22 +1273,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF6">
-        <v>0.1996</v>
+        <v>0.2516</v>
       </c>
       <c r="AG6">
-        <v>0.8675</v>
+        <v>1.2475</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.38</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1260,76 +1296,76 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="D7">
-        <v>-105</v>
+        <v>-111</v>
       </c>
       <c r="E7">
         <v>-105</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>823830</v>
+        <v>823510</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="I7">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7">
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <v>0.3098</v>
+      </c>
+      <c r="N7">
         <v>5</v>
       </c>
-      <c r="M7">
-        <v>0.2119</v>
-      </c>
-      <c r="N7">
-        <v>3</v>
-      </c>
       <c r="O7">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="P7">
-        <v>4.32</v>
+        <v>3.96</v>
       </c>
       <c r="Q7">
-        <v>0.2069</v>
+        <v>0.3441</v>
       </c>
       <c r="R7">
-        <v>0.127</v>
+        <v>0.317</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2444</v>
+        <v>0.214</v>
       </c>
       <c r="U7">
-        <v>0.2296</v>
+        <v>0.193</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2126</v>
+        <v>0.1899</v>
       </c>
       <c r="X7">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y7">
-        <v>0.8899</v>
+        <v>0.98</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1338,22 +1374,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>1.68</v>
+        <v>6.8</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF7">
-        <v>0.2113</v>
+        <v>0.3207</v>
       </c>
       <c r="AG7">
-        <v>1.0968</v>
+        <v>0.9571</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM7">
-        <v>1.68</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1364,25 +1400,25 @@
         <v>56</v>
       </c>
       <c r="C8">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D8">
-        <v>-154</v>
+        <v>112</v>
       </c>
       <c r="E8">
-        <v>135</v>
+        <v>-125</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G8">
-        <v>823830</v>
+        <v>824721</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1394,43 +1430,43 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.2068</v>
+        <v>0.195</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P8">
-        <v>4.42</v>
+        <v>4.03</v>
       </c>
       <c r="Q8">
-        <v>0.2222</v>
+        <v>0.2079</v>
       </c>
       <c r="R8">
-        <v>0.331</v>
+        <v>0.336</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2071</v>
+        <v>0.1933</v>
       </c>
       <c r="U8">
-        <v>0.2083</v>
+        <v>0.1976</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2085</v>
+        <v>0.2153</v>
       </c>
       <c r="X8">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y8">
-        <v>0.9397</v>
+        <v>0.9943</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1439,22 +1475,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF8">
-        <v>0.2119</v>
+        <v>0.1994</v>
       </c>
       <c r="AG8">
-        <v>0.9293</v>
+        <v>0.8647</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1468,22 +1504,22 @@
         <v>5.5</v>
       </c>
       <c r="D9">
-        <v>120</v>
+        <v>-102</v>
       </c>
       <c r="E9">
-        <v>-146</v>
+        <v>-104</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G9">
-        <v>824800</v>
+        <v>824721</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1492,46 +1528,46 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>0.2147</v>
+        <v>0.2188</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P9">
-        <v>4.48</v>
+        <v>4.04</v>
       </c>
       <c r="Q9">
-        <v>0.1776</v>
+        <v>0.2301</v>
       </c>
       <c r="R9">
-        <v>0.349</v>
+        <v>0.361</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.266</v>
+        <v>0.2111</v>
       </c>
       <c r="U9">
-        <v>0.2421</v>
+        <v>0.2135</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2383</v>
+        <v>0.2042</v>
       </c>
       <c r="X9">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y9">
-        <v>1.0527</v>
+        <v>0.9508</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1540,22 +1576,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>5.81</v>
+        <v>4.54</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF9">
-        <v>0.2017</v>
+        <v>0.2228</v>
       </c>
       <c r="AG9">
-        <v>1.1935</v>
+        <v>0.9444</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>5.81</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1563,31 +1599,31 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D10">
         <v>-105</v>
       </c>
       <c r="E10">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>824800</v>
+        <v>823830</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1596,43 +1632,43 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>0.2042</v>
+        <v>0.2073</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="P10">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
       <c r="Q10">
-        <v>0.2583</v>
+        <v>0.1818</v>
       </c>
       <c r="R10">
-        <v>0.375</v>
+        <v>0.142</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.1581</v>
+        <v>0.2444</v>
       </c>
       <c r="U10">
-        <v>0.1607</v>
+        <v>0.2296</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.1849</v>
+        <v>0.2126</v>
       </c>
       <c r="X10">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y10">
-        <v>0.88</v>
+        <v>0.8899</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1641,22 +1677,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.22</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF10">
-        <v>0.2245</v>
+        <v>0.2037</v>
       </c>
       <c r="AG10">
-        <v>0.7093</v>
+        <v>1.0933</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.22</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1667,25 +1703,25 @@
         <v>61</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="D11">
-        <v>112</v>
+        <v>-154</v>
       </c>
       <c r="E11">
-        <v>-137</v>
+        <v>135</v>
       </c>
       <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11">
+        <v>823830</v>
+      </c>
+      <c r="H11" t="s">
         <v>62</v>
       </c>
-      <c r="G11">
-        <v>824559</v>
-      </c>
-      <c r="H11" t="s">
-        <v>42</v>
-      </c>
       <c r="I11">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1694,46 +1730,46 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2697</v>
+        <v>0.2033</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="P11">
-        <v>4.08</v>
+        <v>4.42</v>
       </c>
       <c r="Q11">
-        <v>0.3009</v>
+        <v>0.2021</v>
       </c>
       <c r="R11">
-        <v>0.361</v>
+        <v>0.32</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2512</v>
+        <v>0.2071</v>
       </c>
       <c r="U11">
-        <v>0.2436</v>
+        <v>0.2083</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2245</v>
+        <v>0.2085</v>
       </c>
       <c r="X11">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y11">
-        <v>0.9737</v>
+        <v>0.9397</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1742,22 +1778,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>6.89</v>
+        <v>2.99</v>
       </c>
       <c r="AE11" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="AF11">
-        <v>0.281</v>
+        <v>0.2029</v>
       </c>
       <c r="AG11">
-        <v>1.1274</v>
+        <v>0.9263</v>
       </c>
       <c r="AH11">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>7.29</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1765,28 +1801,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>5.5</v>
       </c>
       <c r="D12">
-        <v>-138</v>
+        <v>120</v>
       </c>
       <c r="E12">
-        <v>120</v>
+        <v>-146</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G12">
-        <v>824559</v>
+        <v>824800</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1798,43 +1834,43 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>0.2349</v>
+        <v>0.2145</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="P12">
-        <v>4.33</v>
+        <v>4.48</v>
       </c>
       <c r="Q12">
-        <v>0.25</v>
+        <v>0.1628</v>
       </c>
       <c r="R12">
-        <v>0.39</v>
+        <v>0.301</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2529</v>
+        <v>0.266</v>
       </c>
       <c r="U12">
-        <v>0.2556</v>
+        <v>0.2421</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2467</v>
+        <v>0.2383</v>
       </c>
       <c r="X12">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y12">
-        <v>1.1</v>
+        <v>1.0527</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1843,22 +1879,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>7.38</v>
+        <v>5.54</v>
       </c>
       <c r="AE12" t="s">
         <v>49</v>
       </c>
       <c r="AF12">
-        <v>0.2408</v>
+        <v>0.199</v>
       </c>
       <c r="AG12">
-        <v>1.1346</v>
+        <v>1.1897</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>7.38</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1872,22 +1908,22 @@
         <v>4.5</v>
       </c>
       <c r="D13">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="E13">
-        <v>102</v>
+        <v>-110</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G13">
-        <v>824152</v>
+        <v>824800</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1899,43 +1935,43 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>0.1895</v>
+        <v>0.2019</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="P13">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="Q13">
-        <v>0.1895</v>
+        <v>0.2525</v>
       </c>
       <c r="R13">
-        <v>0.322</v>
+        <v>0.331</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.1949</v>
+        <v>0.1581</v>
       </c>
       <c r="U13">
-        <v>0.1897</v>
+        <v>0.1607</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2117</v>
+        <v>0.1849</v>
       </c>
       <c r="X13">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y13">
-        <v>1.0194</v>
+        <v>0.88</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1944,22 +1980,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.01</v>
+        <v>3.03</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF13">
-        <v>0.1895</v>
+        <v>0.2186</v>
       </c>
       <c r="AG13">
-        <v>0.8748</v>
+        <v>0.7071</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.01</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1967,34 +2003,76 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14">
+        <v>5.5</v>
+      </c>
+      <c r="D14">
+        <v>-138</v>
+      </c>
+      <c r="E14">
+        <v>120</v>
+      </c>
+      <c r="F14" t="s">
         <v>67</v>
       </c>
-      <c r="C14">
-        <v>4.5</v>
-      </c>
-      <c r="D14">
-        <v>-103</v>
-      </c>
-      <c r="E14">
-        <v>-102</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" t="s">
-        <v>44</v>
+      <c r="G14">
+        <v>824559</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I14">
+        <v>5.7</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
+      <c r="M14">
+        <v>0.2349</v>
+      </c>
+      <c r="N14">
+        <v>5</v>
+      </c>
+      <c r="O14">
+        <v>128</v>
+      </c>
+      <c r="P14">
+        <v>4.33</v>
+      </c>
+      <c r="Q14">
+        <v>0.25</v>
+      </c>
+      <c r="R14">
+        <v>0.39</v>
+      </c>
       <c r="S14" t="s">
-        <v>44</v>
-      </c>
-      <c r="V14" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T14">
+        <v>0.2529</v>
+      </c>
+      <c r="U14">
+        <v>0.2556</v>
+      </c>
+      <c r="V14">
+        <v>9</v>
+      </c>
+      <c r="W14">
+        <v>0.2467</v>
+      </c>
+      <c r="X14">
+        <v>0.2236</v>
+      </c>
+      <c r="Y14">
+        <v>1.1</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2002,8 +2080,23 @@
       <c r="AC14" t="s">
         <v>44</v>
       </c>
+      <c r="AD14">
+        <v>7.36</v>
+      </c>
       <c r="AE14" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF14">
+        <v>0.2408</v>
+      </c>
+      <c r="AG14">
+        <v>1.131</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>7.36</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2014,25 +2107,25 @@
         <v>68</v>
       </c>
       <c r="C15">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D15">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E15">
         <v>-137</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G15">
-        <v>824072</v>
+        <v>824559</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2041,46 +2134,46 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>0.2172</v>
+        <v>0.2697</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="P15">
-        <v>4.19</v>
+        <v>4.08</v>
       </c>
       <c r="Q15">
-        <v>0.203</v>
+        <v>0.3009</v>
       </c>
       <c r="R15">
-        <v>0.399</v>
+        <v>0.361</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2058</v>
+        <v>0.2512</v>
       </c>
       <c r="U15">
-        <v>0.2085</v>
+        <v>0.2436</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2305</v>
+        <v>0.2245</v>
       </c>
       <c r="X15">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y15">
-        <v>1.0031</v>
+        <v>0.9737</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2089,22 +2182,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.69</v>
+        <v>6.87</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF15">
-        <v>0.2116</v>
+        <v>0.281</v>
       </c>
       <c r="AG15">
-        <v>0.9234</v>
+        <v>1.1238</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM15">
-        <v>4.69</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2112,7 +2205,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2124,7 +2217,7 @@
         <v>-120</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16">
         <v>824072</v>
@@ -2178,7 +2271,7 @@
         <v>0.2092</v>
       </c>
       <c r="X16">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y16">
         <v>0.9306</v>
@@ -2190,22 +2283,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF16">
         <v>0.2125</v>
       </c>
       <c r="AG16">
-        <v>0.8624</v>
+        <v>0.8597</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>4.01</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2216,25 +2309,25 @@
         <v>71</v>
       </c>
       <c r="C17">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D17">
-        <v>-150</v>
+        <v>120</v>
       </c>
       <c r="E17">
-        <v>118</v>
+        <v>-137</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G17">
-        <v>822857</v>
+        <v>824072</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2246,43 +2339,43 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.258</v>
+        <v>0.2172</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="P17">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="Q17">
-        <v>0.2623</v>
+        <v>0.203</v>
       </c>
       <c r="R17">
-        <v>0.379</v>
+        <v>0.399</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.3053</v>
+        <v>0.2058</v>
       </c>
       <c r="U17">
-        <v>0.2866</v>
+        <v>0.2085</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2537</v>
+        <v>0.2305</v>
       </c>
       <c r="X17">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y17">
-        <v>1.1182</v>
+        <v>1.0031</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2291,22 +2384,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>9.13</v>
+        <v>4.68</v>
       </c>
       <c r="AE17" t="s">
         <v>49</v>
       </c>
       <c r="AF17">
-        <v>0.2596</v>
+        <v>0.2116</v>
       </c>
       <c r="AG17">
-        <v>1.3698</v>
+        <v>0.9205</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>9.13</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2314,28 +2407,19 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" t="s">
         <v>73</v>
       </c>
-      <c r="C18">
-        <v>6.5</v>
-      </c>
-      <c r="D18">
-        <v>105</v>
-      </c>
-      <c r="E18">
-        <v>-116</v>
-      </c>
-      <c r="F18" t="s">
-        <v>72</v>
-      </c>
       <c r="G18">
-        <v>822857</v>
+        <v>824152</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2344,46 +2428,46 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>0.2884</v>
+        <v>0.2139</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="P18">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="Q18">
-        <v>0.3524</v>
+        <v>0.2295</v>
       </c>
       <c r="R18">
-        <v>0.344</v>
+        <v>0.379</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2445</v>
+        <v>0.2096</v>
       </c>
       <c r="U18">
-        <v>0.2455</v>
+        <v>0.1755</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2456</v>
+        <v>0.2184</v>
       </c>
       <c r="X18">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y18">
-        <v>1.0791</v>
+        <v>0.8828</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2392,22 +2476,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>8.51</v>
+        <v>4.17</v>
       </c>
       <c r="AE18" t="s">
         <v>49</v>
       </c>
       <c r="AF18">
-        <v>0.3104</v>
+        <v>0.2198</v>
       </c>
       <c r="AG18">
-        <v>1.097</v>
+        <v>0.9376</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>8.51</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2418,25 +2502,25 @@
         <v>74</v>
       </c>
       <c r="C19">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>140</v>
+        <v>-108</v>
       </c>
       <c r="E19">
-        <v>-162</v>
+        <v>102</v>
       </c>
       <c r="F19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G19">
-        <v>824317</v>
+        <v>824152</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2445,46 +2529,46 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>0.1987</v>
+        <v>0.1895</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="P19">
-        <v>4.37</v>
+        <v>4.19</v>
       </c>
       <c r="Q19">
-        <v>0.1574</v>
+        <v>0.1895</v>
       </c>
       <c r="R19">
-        <v>0.351</v>
+        <v>0.322</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.1697</v>
+        <v>0.1949</v>
       </c>
       <c r="U19">
-        <v>0.1722</v>
+        <v>0.1897</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2149</v>
+        <v>0.2117</v>
       </c>
       <c r="X19">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y19">
-        <v>0.88</v>
+        <v>1.0194</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2493,22 +2577,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF19">
-        <v>0.1842</v>
+        <v>0.1895</v>
       </c>
       <c r="AG19">
-        <v>0.7614</v>
+        <v>0.872</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>2.48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2516,28 +2600,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20">
+        <v>6.5</v>
+      </c>
+      <c r="D20">
+        <v>105</v>
+      </c>
+      <c r="E20">
+        <v>-116</v>
+      </c>
+      <c r="F20" t="s">
         <v>76</v>
       </c>
-      <c r="C20">
-        <v>5.5</v>
-      </c>
-      <c r="D20">
-        <v>-115</v>
-      </c>
-      <c r="E20">
-        <v>-105</v>
-      </c>
-      <c r="F20" t="s">
-        <v>75</v>
-      </c>
       <c r="G20">
-        <v>824317</v>
+        <v>822857</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2549,43 +2633,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2565</v>
+        <v>0.2884</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="P20">
-        <v>4.31</v>
+        <v>4.05</v>
       </c>
       <c r="Q20">
-        <v>0.3103</v>
+        <v>0.3524</v>
       </c>
       <c r="R20">
-        <v>0.303</v>
+        <v>0.344</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2761</v>
+        <v>0.2445</v>
       </c>
       <c r="U20">
-        <v>0.2214</v>
+        <v>0.2455</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2484</v>
+        <v>0.2456</v>
       </c>
       <c r="X20">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y20">
-        <v>1.0239</v>
+        <v>1.0791</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2594,22 +2678,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>7.21</v>
+        <v>8.48</v>
       </c>
       <c r="AE20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.2728</v>
+        <v>0.3104</v>
       </c>
       <c r="AG20">
-        <v>1.2391</v>
+        <v>1.0935</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>7.21</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2620,25 +2704,25 @@
         <v>77</v>
       </c>
       <c r="C21">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D21">
-        <v>126</v>
+        <v>-150</v>
       </c>
       <c r="E21">
-        <v>-146</v>
+        <v>118</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G21">
-        <v>825045</v>
+        <v>822857</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2650,43 +2734,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.1729</v>
+        <v>0.258</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="P21">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="Q21">
-        <v>0.1778</v>
+        <v>0.2623</v>
       </c>
       <c r="R21">
-        <v>0.403</v>
+        <v>0.379</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2946</v>
+        <v>0.3053</v>
       </c>
       <c r="U21">
-        <v>0.2815</v>
+        <v>0.2866</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2527</v>
+        <v>0.2537</v>
       </c>
       <c r="X21">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y21">
-        <v>1.113</v>
+        <v>1.1182</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2695,22 +2779,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>6.31</v>
+        <v>9.1</v>
       </c>
       <c r="AE21" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.1749</v>
+        <v>0.2596</v>
       </c>
       <c r="AG21">
-        <v>1.3221</v>
+        <v>1.3655</v>
       </c>
       <c r="AH21">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>6.71</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2718,28 +2802,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22">
+        <v>5.5</v>
+      </c>
+      <c r="D22">
+        <v>-115</v>
+      </c>
+      <c r="E22">
+        <v>-105</v>
+      </c>
+      <c r="F22" t="s">
         <v>79</v>
       </c>
-      <c r="C22">
-        <v>3.5</v>
-      </c>
-      <c r="D22">
-        <v>-118</v>
-      </c>
-      <c r="E22">
-        <v>105</v>
-      </c>
-      <c r="F22" t="s">
-        <v>78</v>
-      </c>
       <c r="G22">
-        <v>825045</v>
+        <v>824317</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2751,43 +2835,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.1804</v>
+        <v>0.2565</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="P22">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="Q22">
-        <v>0.181</v>
+        <v>0.3103</v>
       </c>
       <c r="R22">
-        <v>0.344</v>
+        <v>0.303</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2135</v>
+        <v>0.2761</v>
       </c>
       <c r="U22">
-        <v>0.1753</v>
+        <v>0.2214</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.1766</v>
+        <v>0.2484</v>
       </c>
       <c r="X22">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y22">
-        <v>0.88</v>
+        <v>1.0239</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2796,22 +2880,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>3.44</v>
+        <v>7.19</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.1806</v>
+        <v>0.2728</v>
       </c>
       <c r="AG22">
-        <v>0.958</v>
+        <v>1.2352</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>3.44</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2822,25 +2906,25 @@
         <v>80</v>
       </c>
       <c r="C23">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D23">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E23">
-        <v>-148</v>
+        <v>-162</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G23">
-        <v>823262</v>
+        <v>824317</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2852,43 +2936,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2461</v>
+        <v>0.1987</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P23">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="Q23">
-        <v>0.2661</v>
+        <v>0.1574</v>
       </c>
       <c r="R23">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
       </c>
       <c r="T23">
-        <v>0.1954</v>
+        <v>0.1697</v>
       </c>
       <c r="U23">
-        <v>0.1949</v>
+        <v>0.1722</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2218</v>
+        <v>0.2149</v>
       </c>
       <c r="X23">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y23">
-        <v>1.0141</v>
+        <v>0.88</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2897,22 +2981,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.06</v>
+        <v>2.48</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF23">
-        <v>0.2531</v>
+        <v>0.1842</v>
       </c>
       <c r="AG23">
-        <v>0.8769</v>
+        <v>0.7589</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>5.06</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2920,34 +3004,76 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24">
+        <v>3.5</v>
+      </c>
+      <c r="D24">
+        <v>-118</v>
+      </c>
+      <c r="E24">
+        <v>105</v>
+      </c>
+      <c r="F24" t="s">
         <v>82</v>
       </c>
-      <c r="C24">
-        <v>2.5</v>
-      </c>
-      <c r="D24">
-        <v>-160</v>
-      </c>
-      <c r="E24">
-        <v>127</v>
-      </c>
-      <c r="F24" t="s">
-        <v>81</v>
-      </c>
-      <c r="G24" t="s">
-        <v>44</v>
+      <c r="G24">
+        <v>825045</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I24">
+        <v>5.1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="M24">
+        <v>0.1804</v>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>105</v>
+      </c>
+      <c r="P24">
+        <v>4.41</v>
+      </c>
+      <c r="Q24">
+        <v>0.181</v>
+      </c>
+      <c r="R24">
+        <v>0.344</v>
       </c>
       <c r="S24" t="s">
-        <v>44</v>
-      </c>
-      <c r="V24" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T24">
+        <v>0.2135</v>
+      </c>
+      <c r="U24">
+        <v>0.1753</v>
+      </c>
+      <c r="V24">
+        <v>9</v>
+      </c>
+      <c r="W24">
+        <v>0.1766</v>
+      </c>
+      <c r="X24">
+        <v>0.2236</v>
+      </c>
+      <c r="Y24">
+        <v>0.88</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2955,8 +3081,23 @@
       <c r="AC24" t="s">
         <v>44</v>
       </c>
+      <c r="AD24">
+        <v>3.43</v>
+      </c>
       <c r="AE24" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF24">
+        <v>0.1806</v>
+      </c>
+      <c r="AG24">
+        <v>0.9549</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>3.43</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2967,25 +3108,25 @@
         <v>83</v>
       </c>
       <c r="C25">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D25">
-        <v>-135</v>
+        <v>126</v>
       </c>
       <c r="E25">
-        <v>110</v>
+        <v>-146</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G25">
-        <v>823101</v>
+        <v>825045</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -2997,43 +3138,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.1921</v>
+        <v>0.1729</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P25">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="Q25">
-        <v>0.1241</v>
+        <v>0.1778</v>
       </c>
       <c r="R25">
-        <v>0.407</v>
+        <v>0.403</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2237</v>
+        <v>0.2946</v>
       </c>
       <c r="U25">
-        <v>0.2069</v>
+        <v>0.2815</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2425</v>
+        <v>0.2527</v>
       </c>
       <c r="X25">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y25">
-        <v>0.958</v>
+        <v>1.113</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3042,22 +3183,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>3.73</v>
+        <v>6.29</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF25">
-        <v>0.1644</v>
+        <v>0.1749</v>
       </c>
       <c r="AG25">
-        <v>1.0038</v>
+        <v>1.3178</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM25">
-        <v>3.73</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3065,28 +3206,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26">
+        <v>5.5</v>
+      </c>
+      <c r="D26">
+        <v>120</v>
+      </c>
+      <c r="E26">
+        <v>-148</v>
+      </c>
+      <c r="F26" t="s">
         <v>85</v>
       </c>
-      <c r="C26">
-        <v>4.5</v>
-      </c>
-      <c r="D26">
-        <v>-155</v>
-      </c>
-      <c r="E26">
-        <v>126</v>
-      </c>
-      <c r="F26" t="s">
-        <v>84</v>
-      </c>
       <c r="G26">
-        <v>823101</v>
+        <v>823262</v>
       </c>
       <c r="H26" t="s">
         <v>42</v>
       </c>
       <c r="I26">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3098,43 +3239,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2306</v>
+        <v>0.2461</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="P26">
-        <v>4.03</v>
+        <v>4.36</v>
       </c>
       <c r="Q26">
-        <v>0.1984</v>
+        <v>0.2661</v>
       </c>
       <c r="R26">
-        <v>0.387</v>
+        <v>0.353</v>
       </c>
       <c r="S26" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2255</v>
+        <v>0.1954</v>
       </c>
       <c r="U26">
-        <v>0.2231</v>
+        <v>0.1949</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2183</v>
+        <v>0.2218</v>
       </c>
       <c r="X26">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y26">
-        <v>0.9568</v>
+        <v>1.0141</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3143,22 +3284,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.74</v>
+        <v>5.04</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF26">
-        <v>0.2182</v>
+        <v>0.2531</v>
       </c>
       <c r="AG26">
-        <v>1.0119</v>
+        <v>0.8741</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.74</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3166,28 +3307,19 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27">
-        <v>7.5</v>
-      </c>
-      <c r="D27">
-        <v>125</v>
-      </c>
-      <c r="E27">
-        <v>-155</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G27">
-        <v>823911</v>
+        <v>823262</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3196,46 +3328,46 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>0.2446</v>
+        <v>0.1498</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="P27">
-        <v>3.83</v>
+        <v>4.27</v>
       </c>
       <c r="Q27">
-        <v>0.229</v>
+        <v>0.0357</v>
       </c>
       <c r="R27">
-        <v>0.396</v>
+        <v>0.296</v>
       </c>
       <c r="S27" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2148</v>
+        <v>0.2023</v>
       </c>
       <c r="U27">
-        <v>0.2153</v>
+        <v>0.1954</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2346</v>
+        <v>0.2099</v>
       </c>
       <c r="X27">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y27">
-        <v>1.0324</v>
+        <v>0.9599</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3244,22 +3376,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>6</v>
+        <v>2.34</v>
       </c>
       <c r="AE27" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="AF27">
-        <v>0.2384</v>
+        <v>0.1273</v>
       </c>
       <c r="AG27">
-        <v>0.9637</v>
+        <v>0.9048</v>
       </c>
       <c r="AH27">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>6.4</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3267,7 +3399,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C28">
         <v>4.5</v>
@@ -3333,7 +3465,7 @@
         <v>0.2057</v>
       </c>
       <c r="X28">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y28">
         <v>0.9717</v>
@@ -3345,22 +3477,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF28">
         <v>0.2082</v>
       </c>
       <c r="AG28">
-        <v>0.8625</v>
+        <v>0.8597</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3368,28 +3500,28 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C29">
         <v>7.5</v>
       </c>
       <c r="D29">
-        <v>-114</v>
+        <v>125</v>
       </c>
       <c r="E29">
-        <v>-109</v>
+        <v>-155</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G29">
-        <v>823746</v>
+        <v>823911</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3401,28 +3533,28 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>0.3063</v>
+        <v>0.2446</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="P29">
-        <v>4.01</v>
+        <v>3.83</v>
       </c>
       <c r="Q29">
-        <v>0.3707</v>
+        <v>0.229</v>
       </c>
       <c r="R29">
-        <v>0.367</v>
+        <v>0.396</v>
       </c>
       <c r="S29" t="s">
         <v>43</v>
       </c>
       <c r="T29">
-        <v>0.2301</v>
+        <v>0.2357</v>
       </c>
       <c r="U29">
         <v>0.2196</v>
@@ -3431,13 +3563,13 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2211</v>
+        <v>0.2346</v>
       </c>
       <c r="X29">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y29">
-        <v>0.9358</v>
+        <v>1.0736</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3446,22 +3578,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>7.51</v>
+        <v>6.82</v>
       </c>
       <c r="AE29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF29">
-        <v>0.3299</v>
+        <v>0.2384</v>
       </c>
       <c r="AG29">
-        <v>1.0325</v>
+        <v>1.0544</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM29">
-        <v>7.51</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3469,28 +3601,28 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C30">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="D30">
-        <v>120</v>
+        <v>-135</v>
       </c>
       <c r="E30">
-        <v>-142</v>
+        <v>110</v>
       </c>
       <c r="F30" t="s">
         <v>91</v>
       </c>
       <c r="G30">
-        <v>823746</v>
+        <v>823101</v>
       </c>
       <c r="H30" t="s">
         <v>42</v>
       </c>
       <c r="I30">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3502,43 +3634,43 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>0.3927</v>
+        <v>0.1921</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="P30">
-        <v>3.79</v>
+        <v>4.16</v>
       </c>
       <c r="Q30">
-        <v>0.3874</v>
+        <v>0.1241</v>
       </c>
       <c r="R30">
-        <v>0.357</v>
+        <v>0.407</v>
       </c>
       <c r="S30" t="s">
         <v>43</v>
       </c>
       <c r="T30">
-        <v>0.235</v>
+        <v>0.2237</v>
       </c>
       <c r="U30">
-        <v>0.2294</v>
+        <v>0.2069</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2201</v>
+        <v>0.2425</v>
       </c>
       <c r="X30">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y30">
-        <v>1.0407</v>
+        <v>0.958</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3547,22 +3679,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>9.83</v>
+        <v>3.72</v>
       </c>
       <c r="AE30" t="s">
         <v>49</v>
       </c>
       <c r="AF30">
-        <v>0.3908</v>
+        <v>0.1644</v>
       </c>
       <c r="AG30">
-        <v>1.0544</v>
+        <v>1.0006</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>9.83</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3570,67 +3702,76 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="C31">
+        <v>4.5</v>
+      </c>
+      <c r="D31">
+        <v>-155</v>
+      </c>
+      <c r="E31">
+        <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="G31">
-        <v>823420</v>
+        <v>823101</v>
       </c>
       <c r="H31" t="s">
         <v>42</v>
       </c>
       <c r="I31">
+        <v>5.6</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31">
         <v>6</v>
       </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
       <c r="M31">
-        <v>0.2979</v>
+        <v>0.2306</v>
       </c>
       <c r="N31">
         <v>5</v>
       </c>
       <c r="O31">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="P31">
-        <v>4.13</v>
+        <v>4.03</v>
       </c>
       <c r="Q31">
-        <v>0.3043</v>
+        <v>0.1984</v>
       </c>
       <c r="R31">
-        <v>0.408</v>
+        <v>0.387</v>
       </c>
       <c r="S31" t="s">
         <v>43</v>
       </c>
       <c r="T31">
-        <v>0.2205</v>
+        <v>0.226</v>
       </c>
       <c r="U31">
-        <v>0.1899</v>
+        <v>0.2233</v>
       </c>
       <c r="V31">
         <v>9</v>
       </c>
       <c r="W31">
-        <v>0.1826</v>
+        <v>0.2183</v>
       </c>
       <c r="X31">
-        <v>0.2229</v>
+        <v>0.2236</v>
       </c>
       <c r="Y31">
-        <v>0.9461</v>
+        <v>0.889</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3639,22 +3780,22 @@
         <v>44</v>
       </c>
       <c r="AD31">
-        <v>6.99</v>
+        <v>4.4</v>
       </c>
       <c r="AE31" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="AF31">
-        <v>0.3005</v>
+        <v>0.2182</v>
       </c>
       <c r="AG31">
-        <v>0.9892</v>
+        <v>1.0108</v>
       </c>
       <c r="AH31">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>7.39</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3662,67 +3803,34 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="C32">
+        <v>7.5</v>
+      </c>
+      <c r="D32">
+        <v>115</v>
+      </c>
+      <c r="E32">
+        <v>-130</v>
       </c>
       <c r="F32" t="s">
         <v>48</v>
       </c>
-      <c r="G32">
-        <v>823510</v>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>55</v>
-      </c>
-      <c r="I32">
-        <v>1.2</v>
-      </c>
-      <c r="J32" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.2629</v>
-      </c>
-      <c r="N32">
-        <v>3</v>
-      </c>
-      <c r="O32">
-        <v>17</v>
-      </c>
-      <c r="P32">
-        <v>4.18</v>
-      </c>
-      <c r="Q32">
-        <v>0.2353</v>
-      </c>
-      <c r="R32">
-        <v>0.078</v>
+        <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>43</v>
-      </c>
-      <c r="T32">
-        <v>0.2789</v>
-      </c>
-      <c r="U32">
-        <v>0.2767</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2489</v>
-      </c>
-      <c r="X32">
-        <v>0.2229</v>
-      </c>
-      <c r="Y32">
-        <v>1.0045</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3730,23 +3838,8 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
-      <c r="AD32">
-        <v>1.67</v>
-      </c>
       <c r="AE32" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF32">
-        <v>0.2607</v>
-      </c>
-      <c r="AG32">
-        <v>1.2515</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>1.67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3754,67 +3847,34 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="C33">
+        <v>4.5</v>
+      </c>
+      <c r="D33">
+        <v>-103</v>
+      </c>
+      <c r="E33">
+        <v>-102</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
-      </c>
-      <c r="G33">
-        <v>824152</v>
+        <v>73</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
       </c>
       <c r="H33" t="s">
-        <v>42</v>
-      </c>
-      <c r="I33">
-        <v>5.5</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0.2139</v>
-      </c>
-      <c r="N33">
         <v>5</v>
       </c>
-      <c r="O33">
-        <v>122</v>
-      </c>
-      <c r="P33">
-        <v>4.19</v>
-      </c>
-      <c r="Q33">
-        <v>0.2295</v>
-      </c>
-      <c r="R33">
-        <v>0.379</v>
-      </c>
       <c r="S33" t="s">
-        <v>43</v>
-      </c>
-      <c r="T33">
-        <v>0.2096</v>
-      </c>
-      <c r="U33">
-        <v>0.1755</v>
-      </c>
-      <c r="V33">
-        <v>9</v>
-      </c>
-      <c r="W33">
-        <v>0.2184</v>
-      </c>
-      <c r="X33">
-        <v>0.2229</v>
-      </c>
-      <c r="Y33">
-        <v>0.8828</v>
+        <v>44</v>
+      </c>
+      <c r="V33" t="s">
+        <v>44</v>
       </c>
       <c r="AA33" t="s">
         <v>44</v>
@@ -3822,23 +3882,8 @@
       <c r="AC33" t="s">
         <v>44</v>
       </c>
-      <c r="AD33">
-        <v>4.18</v>
-      </c>
       <c r="AE33" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF33">
-        <v>0.2198</v>
-      </c>
-      <c r="AG33">
-        <v>0.9406</v>
-      </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>4.18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
@@ -3846,67 +3891,34 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="C34">
+        <v>2.5</v>
+      </c>
+      <c r="D34">
+        <v>-160</v>
+      </c>
+      <c r="E34">
+        <v>127</v>
       </c>
       <c r="F34" t="s">
-        <v>81</v>
-      </c>
-      <c r="G34">
-        <v>823262</v>
+        <v>85</v>
+      </c>
+      <c r="G34" t="s">
+        <v>44</v>
       </c>
       <c r="H34" t="s">
-        <v>42</v>
-      </c>
-      <c r="I34">
-        <v>5</v>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0.1498</v>
-      </c>
-      <c r="N34">
-        <v>5</v>
-      </c>
-      <c r="O34">
-        <v>84</v>
-      </c>
-      <c r="P34">
-        <v>4.27</v>
-      </c>
-      <c r="Q34">
-        <v>0.0357</v>
-      </c>
-      <c r="R34">
-        <v>0.296</v>
+        <v>3</v>
       </c>
       <c r="S34" t="s">
-        <v>43</v>
-      </c>
-      <c r="T34">
-        <v>0.2023</v>
-      </c>
-      <c r="U34">
-        <v>0.1954</v>
-      </c>
-      <c r="V34">
-        <v>9</v>
-      </c>
-      <c r="W34">
-        <v>0.2099</v>
-      </c>
-      <c r="X34">
-        <v>0.2229</v>
-      </c>
-      <c r="Y34">
-        <v>0.9599</v>
+        <v>44</v>
+      </c>
+      <c r="V34" t="s">
+        <v>44</v>
       </c>
       <c r="AA34" t="s">
         <v>44</v>
@@ -3914,23 +3926,8 @@
       <c r="AC34" t="s">
         <v>44</v>
       </c>
-      <c r="AD34">
-        <v>2.35</v>
-      </c>
       <c r="AE34" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF34">
-        <v>0.1273</v>
-      </c>
-      <c r="AG34">
-        <v>0.9077</v>
-      </c>
-      <c r="AH34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>2.35</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-21.xlsx
+++ b/data/k-props/2026-08-21.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="100">
   <si>
     <t>date</t>
   </si>
@@ -145,6 +145,9 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -181,6 +184,9 @@
     <t>Cam Schlittler</t>
   </si>
   <si>
+    <t>L</t>
+  </si>
+  <si>
     <t>Logan Webb</t>
   </si>
   <si>
@@ -190,10 +196,16 @@
     <t>Sonny Gray</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
     <t>Brad Lord</t>
   </si>
   <si>
     <t>Washington Nationals @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
   <si>
     <t>Ryan Gusto</t>
@@ -880,17 +892,23 @@
       <c r="Y2">
         <v>0.9358</v>
       </c>
+      <c r="Z2">
+        <v>6</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>-0.01</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>7.49</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.3299</v>
@@ -900,6 +918,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>-1.49</v>
+      </c>
+      <c r="AJ2">
+        <v>1.49</v>
+      </c>
+      <c r="AK2">
+        <v>-1.49</v>
+      </c>
+      <c r="AL2">
+        <v>1.49</v>
       </c>
       <c r="AM2">
         <v>7.49</v>
@@ -910,7 +940,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>9.5</v>
@@ -981,17 +1011,23 @@
       <c r="Y3">
         <v>1.0407</v>
       </c>
+      <c r="Z3">
+        <v>6</v>
+      </c>
       <c r="AA3" t="s">
         <v>44</v>
       </c>
+      <c r="AB3">
+        <v>0.3</v>
+      </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD3">
         <v>9.8</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.3908</v>
@@ -1001,6 +1037,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>-3.8</v>
+      </c>
+      <c r="AJ3">
+        <v>3.8</v>
+      </c>
+      <c r="AK3">
+        <v>-3.8</v>
+      </c>
+      <c r="AL3">
+        <v>3.8</v>
       </c>
       <c r="AM3">
         <v>9.8</v>
@@ -1011,7 +1059,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -1023,7 +1071,7 @@
         <v>123</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>823420</v>
@@ -1082,17 +1130,23 @@
       <c r="Y4">
         <v>0.922</v>
       </c>
+      <c r="Z4">
+        <v>3</v>
+      </c>
       <c r="AA4" t="s">
         <v>44</v>
       </c>
+      <c r="AB4">
+        <v>-0.39</v>
+      </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD4">
         <v>3.11</v>
       </c>
       <c r="AE4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF4">
         <v>0.2253</v>
@@ -1102,6 +1156,18 @@
       </c>
       <c r="AH4">
         <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>-0.11</v>
+      </c>
+      <c r="AJ4">
+        <v>0.11</v>
+      </c>
+      <c r="AK4">
+        <v>-0.11</v>
+      </c>
+      <c r="AL4">
+        <v>0.11</v>
       </c>
       <c r="AM4">
         <v>3.11</v>
@@ -1112,10 +1178,10 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>823420</v>
@@ -1175,16 +1241,16 @@
         <v>0.9461</v>
       </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD5">
         <v>6.86</v>
       </c>
       <c r="AE5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF5">
         <v>0.3013</v>
@@ -1204,16 +1270,16 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>823510</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I6">
         <v>1.1</v>
@@ -1267,16 +1333,16 @@
         <v>1.0045</v>
       </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD6">
         <v>1.43</v>
       </c>
       <c r="AE6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF6">
         <v>0.2516</v>
@@ -1296,7 +1362,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7">
         <v>6.5</v>
@@ -1308,7 +1374,7 @@
         <v>-105</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>823510</v>
@@ -1367,17 +1433,23 @@
       <c r="Y7">
         <v>0.98</v>
       </c>
+      <c r="Z7">
+        <v>4</v>
+      </c>
       <c r="AA7" t="s">
         <v>44</v>
       </c>
+      <c r="AB7">
+        <v>0.7</v>
+      </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD7">
         <v>6.8</v>
       </c>
       <c r="AE7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF7">
         <v>0.3207</v>
@@ -1387,6 +1459,18 @@
       </c>
       <c r="AH7">
         <v>0.4</v>
+      </c>
+      <c r="AI7">
+        <v>-2.8</v>
+      </c>
+      <c r="AJ7">
+        <v>2.8</v>
+      </c>
+      <c r="AK7">
+        <v>-3.2</v>
+      </c>
+      <c r="AL7">
+        <v>3.2</v>
       </c>
       <c r="AM7">
         <v>7.2</v>
@@ -1397,7 +1481,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1409,7 +1493,7 @@
         <v>-125</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>824721</v>
@@ -1468,17 +1552,23 @@
       <c r="Y8">
         <v>0.9943</v>
       </c>
+      <c r="Z8">
+        <v>2</v>
+      </c>
       <c r="AA8" t="s">
         <v>44</v>
       </c>
+      <c r="AB8">
+        <v>-0.3</v>
+      </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD8">
         <v>4.2</v>
       </c>
       <c r="AE8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF8">
         <v>0.1994</v>
@@ -1488,6 +1578,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>-2.2</v>
+      </c>
+      <c r="AJ8">
+        <v>2.2</v>
+      </c>
+      <c r="AK8">
+        <v>-2.2</v>
+      </c>
+      <c r="AL8">
+        <v>2.2</v>
       </c>
       <c r="AM8">
         <v>4.2</v>
@@ -1498,7 +1600,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>5.5</v>
@@ -1510,7 +1612,7 @@
         <v>-104</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>824721</v>
@@ -1569,17 +1671,23 @@
       <c r="Y9">
         <v>0.9508</v>
       </c>
+      <c r="Z9">
+        <v>6</v>
+      </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="AB9">
+        <v>-0.96</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD9">
         <v>4.54</v>
       </c>
       <c r="AE9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF9">
         <v>0.2228</v>
@@ -1589,6 +1697,18 @@
       </c>
       <c r="AH9">
         <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>1.46</v>
+      </c>
+      <c r="AJ9">
+        <v>1.46</v>
+      </c>
+      <c r="AK9">
+        <v>1.46</v>
+      </c>
+      <c r="AL9">
+        <v>1.46</v>
       </c>
       <c r="AM9">
         <v>4.54</v>
@@ -1599,7 +1719,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>2.5</v>
@@ -1611,13 +1731,13 @@
         <v>-105</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <v>823830</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I10">
         <v>1.7</v>
@@ -1670,17 +1790,23 @@
       <c r="Y10">
         <v>0.8899</v>
       </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
       <c r="AA10" t="s">
         <v>44</v>
       </c>
+      <c r="AB10">
+        <v>-1.08</v>
+      </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="AD10">
         <v>1.42</v>
       </c>
       <c r="AE10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF10">
         <v>0.2037</v>
@@ -1690,6 +1816,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>-0.42</v>
+      </c>
+      <c r="AJ10">
+        <v>0.42</v>
+      </c>
+      <c r="AK10">
+        <v>-0.42</v>
+      </c>
+      <c r="AL10">
+        <v>0.42</v>
       </c>
       <c r="AM10">
         <v>1.42</v>
@@ -1700,7 +1838,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -1712,13 +1850,13 @@
         <v>135</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>823830</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I11">
         <v>3.8</v>
@@ -1771,17 +1909,23 @@
       <c r="Y11">
         <v>0.9397</v>
       </c>
+      <c r="Z11">
+        <v>2</v>
+      </c>
       <c r="AA11" t="s">
         <v>44</v>
       </c>
+      <c r="AB11">
+        <v>-0.51</v>
+      </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD11">
         <v>2.99</v>
       </c>
       <c r="AE11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF11">
         <v>0.2029</v>
@@ -1791,6 +1935,18 @@
       </c>
       <c r="AH11">
         <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>-0.99</v>
+      </c>
+      <c r="AJ11">
+        <v>0.99</v>
+      </c>
+      <c r="AK11">
+        <v>-0.99</v>
+      </c>
+      <c r="AL11">
+        <v>0.99</v>
       </c>
       <c r="AM11">
         <v>2.99</v>
@@ -1801,7 +1957,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>5.5</v>
@@ -1813,7 +1969,7 @@
         <v>-146</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G12">
         <v>824800</v>
@@ -1872,17 +2028,23 @@
       <c r="Y12">
         <v>1.0527</v>
       </c>
+      <c r="Z12">
+        <v>6</v>
+      </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="AB12">
+        <v>0.04</v>
       </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD12">
         <v>5.54</v>
       </c>
       <c r="AE12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF12">
         <v>0.199</v>
@@ -1892,6 +2054,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0.46</v>
+      </c>
+      <c r="AJ12">
+        <v>0.46</v>
+      </c>
+      <c r="AK12">
+        <v>0.46</v>
+      </c>
+      <c r="AL12">
+        <v>0.46</v>
       </c>
       <c r="AM12">
         <v>5.54</v>
@@ -1902,7 +2076,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -1914,7 +2088,7 @@
         <v>-110</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>824800</v>
@@ -1973,17 +2147,23 @@
       <c r="Y13">
         <v>0.88</v>
       </c>
+      <c r="Z13">
+        <v>6</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="AB13">
+        <v>-1.47</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD13">
         <v>3.03</v>
       </c>
       <c r="AE13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF13">
         <v>0.2186</v>
@@ -1993,6 +2173,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>2.97</v>
+      </c>
+      <c r="AJ13">
+        <v>2.97</v>
+      </c>
+      <c r="AK13">
+        <v>2.97</v>
+      </c>
+      <c r="AL13">
+        <v>2.97</v>
       </c>
       <c r="AM13">
         <v>3.03</v>
@@ -2003,7 +2195,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2015,7 +2207,7 @@
         <v>120</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G14">
         <v>824559</v>
@@ -2074,17 +2266,23 @@
       <c r="Y14">
         <v>1.1</v>
       </c>
+      <c r="Z14">
+        <v>4</v>
+      </c>
       <c r="AA14" t="s">
         <v>44</v>
       </c>
+      <c r="AB14">
+        <v>1.86</v>
+      </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD14">
         <v>7.36</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>0.2408</v>
@@ -2094,6 +2292,18 @@
       </c>
       <c r="AH14">
         <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>-3.36</v>
+      </c>
+      <c r="AJ14">
+        <v>3.36</v>
+      </c>
+      <c r="AK14">
+        <v>-3.36</v>
+      </c>
+      <c r="AL14">
+        <v>3.36</v>
       </c>
       <c r="AM14">
         <v>7.36</v>
@@ -2104,7 +2314,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>6.5</v>
@@ -2116,7 +2326,7 @@
         <v>-137</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G15">
         <v>824559</v>
@@ -2175,17 +2385,23 @@
       <c r="Y15">
         <v>0.9737</v>
       </c>
+      <c r="Z15">
+        <v>4</v>
+      </c>
       <c r="AA15" t="s">
         <v>44</v>
       </c>
+      <c r="AB15">
+        <v>0.77</v>
+      </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD15">
         <v>6.87</v>
       </c>
       <c r="AE15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF15">
         <v>0.281</v>
@@ -2195,6 +2411,18 @@
       </c>
       <c r="AH15">
         <v>0.4</v>
+      </c>
+      <c r="AI15">
+        <v>-2.87</v>
+      </c>
+      <c r="AJ15">
+        <v>2.87</v>
+      </c>
+      <c r="AK15">
+        <v>-3.27</v>
+      </c>
+      <c r="AL15">
+        <v>3.27</v>
       </c>
       <c r="AM15">
         <v>7.27</v>
@@ -2205,7 +2433,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2217,7 +2445,7 @@
         <v>-120</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G16">
         <v>824072</v>
@@ -2276,17 +2504,23 @@
       <c r="Y16">
         <v>0.9306</v>
       </c>
+      <c r="Z16">
+        <v>3</v>
+      </c>
       <c r="AA16" t="s">
         <v>44</v>
       </c>
+      <c r="AB16">
+        <v>-0.5</v>
+      </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD16">
         <v>4</v>
       </c>
       <c r="AE16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF16">
         <v>0.2125</v>
@@ -2296,6 +2530,18 @@
       </c>
       <c r="AH16">
         <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>-1</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>-1</v>
+      </c>
+      <c r="AL16">
+        <v>1</v>
       </c>
       <c r="AM16">
         <v>4</v>
@@ -2306,7 +2552,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>5.5</v>
@@ -2318,7 +2564,7 @@
         <v>-137</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>824072</v>
@@ -2377,17 +2623,23 @@
       <c r="Y17">
         <v>1.0031</v>
       </c>
+      <c r="Z17">
+        <v>2</v>
+      </c>
       <c r="AA17" t="s">
         <v>44</v>
       </c>
+      <c r="AB17">
+        <v>-0.82</v>
+      </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="AD17">
         <v>4.68</v>
       </c>
       <c r="AE17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF17">
         <v>0.2116</v>
@@ -2397,6 +2649,18 @@
       </c>
       <c r="AH17">
         <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>-2.68</v>
+      </c>
+      <c r="AJ17">
+        <v>2.68</v>
+      </c>
+      <c r="AK17">
+        <v>-2.68</v>
+      </c>
+      <c r="AL17">
+        <v>2.68</v>
       </c>
       <c r="AM17">
         <v>4.68</v>
@@ -2407,10 +2671,10 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G18">
         <v>824152</v>
@@ -2470,16 +2734,16 @@
         <v>0.8828</v>
       </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD18">
         <v>4.17</v>
       </c>
       <c r="AE18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF18">
         <v>0.2198</v>
@@ -2499,7 +2763,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2511,7 +2775,7 @@
         <v>102</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>824152</v>
@@ -2570,17 +2834,23 @@
       <c r="Y19">
         <v>1.0194</v>
       </c>
+      <c r="Z19">
+        <v>4</v>
+      </c>
       <c r="AA19" t="s">
         <v>44</v>
       </c>
+      <c r="AB19">
+        <v>-0.5</v>
+      </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD19">
         <v>4</v>
       </c>
       <c r="AE19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF19">
         <v>0.1895</v>
@@ -2589,6 +2859,18 @@
         <v>0.872</v>
       </c>
       <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
@@ -2600,7 +2882,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C20">
         <v>6.5</v>
@@ -2612,7 +2894,7 @@
         <v>-116</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>822857</v>
@@ -2671,17 +2953,23 @@
       <c r="Y20">
         <v>1.0791</v>
       </c>
+      <c r="Z20">
+        <v>5</v>
+      </c>
       <c r="AA20" t="s">
         <v>44</v>
       </c>
+      <c r="AB20">
+        <v>1.98</v>
+      </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD20">
         <v>8.48</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>0.3104</v>
@@ -2691,6 +2979,18 @@
       </c>
       <c r="AH20">
         <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>-3.48</v>
+      </c>
+      <c r="AJ20">
+        <v>3.48</v>
+      </c>
+      <c r="AK20">
+        <v>-3.48</v>
+      </c>
+      <c r="AL20">
+        <v>3.48</v>
       </c>
       <c r="AM20">
         <v>8.48</v>
@@ -2701,7 +3001,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>6.5</v>
@@ -2713,7 +3013,7 @@
         <v>118</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G21">
         <v>822857</v>
@@ -2772,17 +3072,23 @@
       <c r="Y21">
         <v>1.1182</v>
       </c>
+      <c r="Z21">
+        <v>7</v>
+      </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="AB21">
+        <v>2.6</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="AD21">
         <v>9.1</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF21">
         <v>0.2596</v>
@@ -2792,6 +3098,18 @@
       </c>
       <c r="AH21">
         <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>-2.1</v>
+      </c>
+      <c r="AJ21">
+        <v>2.1</v>
+      </c>
+      <c r="AK21">
+        <v>-2.1</v>
+      </c>
+      <c r="AL21">
+        <v>2.1</v>
       </c>
       <c r="AM21">
         <v>9.1</v>
@@ -2802,7 +3120,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C22">
         <v>5.5</v>
@@ -2814,7 +3132,7 @@
         <v>-105</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G22">
         <v>824317</v>
@@ -2873,17 +3191,23 @@
       <c r="Y22">
         <v>1.0239</v>
       </c>
+      <c r="Z22">
+        <v>5</v>
+      </c>
       <c r="AA22" t="s">
         <v>44</v>
       </c>
+      <c r="AB22">
+        <v>1.69</v>
+      </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD22">
         <v>7.19</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.2728</v>
@@ -2893,6 +3217,18 @@
       </c>
       <c r="AH22">
         <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>-2.19</v>
+      </c>
+      <c r="AJ22">
+        <v>2.19</v>
+      </c>
+      <c r="AK22">
+        <v>-2.19</v>
+      </c>
+      <c r="AL22">
+        <v>2.19</v>
       </c>
       <c r="AM22">
         <v>7.19</v>
@@ -2903,7 +3239,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C23">
         <v>3.5</v>
@@ -2915,7 +3251,7 @@
         <v>-162</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G23">
         <v>824317</v>
@@ -2974,17 +3310,23 @@
       <c r="Y23">
         <v>0.88</v>
       </c>
+      <c r="Z23">
+        <v>2</v>
+      </c>
       <c r="AA23" t="s">
         <v>44</v>
       </c>
+      <c r="AB23">
+        <v>-1.02</v>
+      </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="AD23">
         <v>2.48</v>
       </c>
       <c r="AE23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF23">
         <v>0.1842</v>
@@ -2994,6 +3336,18 @@
       </c>
       <c r="AH23">
         <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>-0.48</v>
+      </c>
+      <c r="AJ23">
+        <v>0.48</v>
+      </c>
+      <c r="AK23">
+        <v>-0.48</v>
+      </c>
+      <c r="AL23">
+        <v>0.48</v>
       </c>
       <c r="AM23">
         <v>2.48</v>
@@ -3004,7 +3358,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>3.5</v>
@@ -3016,7 +3370,7 @@
         <v>105</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G24">
         <v>825045</v>
@@ -3075,17 +3429,23 @@
       <c r="Y24">
         <v>0.88</v>
       </c>
+      <c r="Z24">
+        <v>2</v>
+      </c>
       <c r="AA24" t="s">
         <v>44</v>
       </c>
+      <c r="AB24">
+        <v>-0.07</v>
+      </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD24">
         <v>3.43</v>
       </c>
       <c r="AE24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF24">
         <v>0.1806</v>
@@ -3095,6 +3455,18 @@
       </c>
       <c r="AH24">
         <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>-1.43</v>
+      </c>
+      <c r="AJ24">
+        <v>1.43</v>
+      </c>
+      <c r="AK24">
+        <v>-1.43</v>
+      </c>
+      <c r="AL24">
+        <v>1.43</v>
       </c>
       <c r="AM24">
         <v>3.43</v>
@@ -3105,7 +3477,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C25">
         <v>5.5</v>
@@ -3117,7 +3489,7 @@
         <v>-146</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G25">
         <v>825045</v>
@@ -3176,17 +3548,23 @@
       <c r="Y25">
         <v>1.113</v>
       </c>
+      <c r="Z25">
+        <v>4</v>
+      </c>
       <c r="AA25" t="s">
         <v>44</v>
       </c>
+      <c r="AB25">
+        <v>1.19</v>
+      </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="AD25">
         <v>6.29</v>
       </c>
       <c r="AE25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF25">
         <v>0.1749</v>
@@ -3196,6 +3574,18 @@
       </c>
       <c r="AH25">
         <v>0.4</v>
+      </c>
+      <c r="AI25">
+        <v>-2.29</v>
+      </c>
+      <c r="AJ25">
+        <v>2.29</v>
+      </c>
+      <c r="AK25">
+        <v>-2.69</v>
+      </c>
+      <c r="AL25">
+        <v>2.69</v>
       </c>
       <c r="AM25">
         <v>6.69</v>
@@ -3206,7 +3596,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C26">
         <v>5.5</v>
@@ -3218,7 +3608,7 @@
         <v>-148</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G26">
         <v>823262</v>
@@ -3277,17 +3667,23 @@
       <c r="Y26">
         <v>1.0141</v>
       </c>
+      <c r="Z26">
+        <v>7</v>
+      </c>
       <c r="AA26" t="s">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="AB26">
+        <v>-0.46</v>
       </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD26">
         <v>5.04</v>
       </c>
       <c r="AE26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF26">
         <v>0.2531</v>
@@ -3297,6 +3693,18 @@
       </c>
       <c r="AH26">
         <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>1.96</v>
+      </c>
+      <c r="AJ26">
+        <v>1.96</v>
+      </c>
+      <c r="AK26">
+        <v>1.96</v>
+      </c>
+      <c r="AL26">
+        <v>1.96</v>
       </c>
       <c r="AM26">
         <v>5.04</v>
@@ -3307,10 +3715,10 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G27">
         <v>823262</v>
@@ -3370,16 +3778,16 @@
         <v>0.9599</v>
       </c>
       <c r="AA27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD27">
         <v>2.34</v>
       </c>
       <c r="AE27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF27">
         <v>0.1273</v>
@@ -3399,7 +3807,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C28">
         <v>4.5</v>
@@ -3411,7 +3819,7 @@
         <v>-147</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G28">
         <v>823911</v>
@@ -3470,17 +3878,23 @@
       <c r="Y28">
         <v>0.9717</v>
       </c>
+      <c r="Z28">
+        <v>6</v>
+      </c>
       <c r="AA28" t="s">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="AB28">
+        <v>-0.68</v>
       </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD28">
         <v>3.82</v>
       </c>
       <c r="AE28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF28">
         <v>0.2082</v>
@@ -3490,6 +3904,18 @@
       </c>
       <c r="AH28">
         <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>2.18</v>
+      </c>
+      <c r="AJ28">
+        <v>2.18</v>
+      </c>
+      <c r="AK28">
+        <v>2.18</v>
+      </c>
+      <c r="AL28">
+        <v>2.18</v>
       </c>
       <c r="AM28">
         <v>3.82</v>
@@ -3500,7 +3926,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C29">
         <v>7.5</v>
@@ -3512,7 +3938,7 @@
         <v>-155</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G29">
         <v>823911</v>
@@ -3571,17 +3997,23 @@
       <c r="Y29">
         <v>1.0736</v>
       </c>
+      <c r="Z29">
+        <v>9</v>
+      </c>
       <c r="AA29" t="s">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="AB29">
+        <v>-0.28</v>
       </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD29">
         <v>6.82</v>
       </c>
       <c r="AE29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF29">
         <v>0.2384</v>
@@ -3591,6 +4023,18 @@
       </c>
       <c r="AH29">
         <v>0.4</v>
+      </c>
+      <c r="AI29">
+        <v>2.18</v>
+      </c>
+      <c r="AJ29">
+        <v>2.18</v>
+      </c>
+      <c r="AK29">
+        <v>1.78</v>
+      </c>
+      <c r="AL29">
+        <v>1.78</v>
       </c>
       <c r="AM29">
         <v>7.22</v>
@@ -3601,7 +4045,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C30">
         <v>4.5</v>
@@ -3613,7 +4057,7 @@
         <v>110</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G30">
         <v>823101</v>
@@ -3672,17 +4116,23 @@
       <c r="Y30">
         <v>0.958</v>
       </c>
+      <c r="Z30">
+        <v>3</v>
+      </c>
       <c r="AA30" t="s">
         <v>44</v>
       </c>
+      <c r="AB30">
+        <v>-0.78</v>
+      </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="AD30">
         <v>3.72</v>
       </c>
       <c r="AE30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF30">
         <v>0.1644</v>
@@ -3692,6 +4142,18 @@
       </c>
       <c r="AH30">
         <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>-0.72</v>
+      </c>
+      <c r="AJ30">
+        <v>0.72</v>
+      </c>
+      <c r="AK30">
+        <v>-0.72</v>
+      </c>
+      <c r="AL30">
+        <v>0.72</v>
       </c>
       <c r="AM30">
         <v>3.72</v>
@@ -3702,7 +4164,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>4.5</v>
@@ -3714,7 +4176,7 @@
         <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G31">
         <v>823101</v>
@@ -3773,17 +4235,23 @@
       <c r="Y31">
         <v>0.889</v>
       </c>
+      <c r="Z31">
+        <v>6</v>
+      </c>
       <c r="AA31" t="s">
-        <v>44</v>
+        <v>61</v>
+      </c>
+      <c r="AB31">
+        <v>-0.1</v>
       </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD31">
         <v>4.4</v>
       </c>
       <c r="AE31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF31">
         <v>0.2182</v>
@@ -3793,6 +4261,18 @@
       </c>
       <c r="AH31">
         <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>1.6</v>
+      </c>
+      <c r="AJ31">
+        <v>1.6</v>
+      </c>
+      <c r="AK31">
+        <v>1.6</v>
+      </c>
+      <c r="AL31">
+        <v>1.6</v>
       </c>
       <c r="AM31">
         <v>4.4</v>
@@ -3803,7 +4283,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>7.5</v>
@@ -3815,31 +4295,31 @@
         <v>-130</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3847,7 +4327,7 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C33">
         <v>4.5</v>
@@ -3859,31 +4339,31 @@
         <v>-102</v>
       </c>
       <c r="F33" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L33">
         <v>5</v>
       </c>
       <c r="S33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
@@ -3891,7 +4371,7 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C34">
         <v>2.5</v>
@@ -3903,31 +4383,31 @@
         <v>127</v>
       </c>
       <c r="F34" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L34">
         <v>3</v>
       </c>
       <c r="S34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
